--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 22.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 22.xlsx
@@ -526,8 +526,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -570,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -674,8 +672,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -705,6 +701,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-409.4700000000003</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.7639e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-53.007</v>
+      </c>
+      <c r="F2" t="n">
+        <v/>
+      </c>
+      <c r="G2" t="n">
+        <v/>
+      </c>
+      <c r="H2" t="n">
+        <v/>
+      </c>
+      <c r="I2" t="n">
+        <v/>
+      </c>
+      <c r="J2" t="n">
+        <v>20.46887317211569</v>
+      </c>
+      <c r="K2" t="n">
+        <v>84.31863390628567</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 10.052x + -39534.145</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.244253294594379e-09</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>4625.580325676739</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000961e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8211906604225788</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-360.3799999999997</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.8282e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-54.474</v>
+      </c>
+      <c r="F3" t="n">
+        <v/>
+      </c>
+      <c r="G3" t="n">
+        <v/>
+      </c>
+      <c r="H3" t="n">
+        <v/>
+      </c>
+      <c r="I3" t="n">
+        <v/>
+      </c>
+      <c r="J3" t="n">
+        <v>23.32008240776105</v>
+      </c>
+      <c r="K3" t="n">
+        <v>84.70692971997173</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 10.794x + -40617.942</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>7.377204449657842e-09</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>4433.80859511773</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000001458e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.821584085545892</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-335.9900000000002</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.85578e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-55.067</v>
+      </c>
+      <c r="F4" t="n">
+        <v/>
+      </c>
+      <c r="G4" t="n">
+        <v/>
+      </c>
+      <c r="H4" t="n">
+        <v/>
+      </c>
+      <c r="I4" t="n">
+        <v/>
+      </c>
+      <c r="J4" t="n">
+        <v>24.99290426183501</v>
+      </c>
+      <c r="K4" t="n">
+        <v>84.92317105169997</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 11.256x + -41596.090</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.252944243450047e-10</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>4350.238132513493</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000144e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8217534811141686</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-345.1599999999999</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.87738e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-55.497</v>
+      </c>
+      <c r="F5" t="n">
+        <v/>
+      </c>
+      <c r="G5" t="n">
+        <v/>
+      </c>
+      <c r="H5" t="n">
+        <v/>
+      </c>
+      <c r="I5" t="n">
+        <v/>
+      </c>
+      <c r="J5" t="n">
+        <v>18.00066706890204</v>
+      </c>
+      <c r="K5" t="n">
+        <v>84.37965575076632</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 10.162x + -36761.966</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.306075202763503e-10</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4286.768509053111</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000012766e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8219002916600653</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-313.6300000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.89258e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-55.838</v>
+      </c>
+      <c r="F6" t="n">
+        <v/>
+      </c>
+      <c r="G6" t="n">
+        <v/>
+      </c>
+      <c r="H6" t="n">
+        <v/>
+      </c>
+      <c r="I6" t="n">
+        <v/>
+      </c>
+      <c r="J6" t="n">
+        <v>26.18595355668138</v>
+      </c>
+      <c r="K6" t="n">
+        <v>85.04642743210843</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 11.538x + -41540.417</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>7.584899300526974e-11</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4235.722519837079</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000001277e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8220488379896506</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-297.6399999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.90869e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-56.183</v>
+      </c>
+      <c r="F7" t="n">
+        <v/>
+      </c>
+      <c r="G7" t="n">
+        <v/>
+      </c>
+      <c r="H7" t="n">
+        <v/>
+      </c>
+      <c r="I7" t="n">
+        <v/>
+      </c>
+      <c r="J7" t="n">
+        <v>27.00244478472433</v>
+      </c>
+      <c r="K7" t="n">
+        <v>85.06202487131932</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 11.574x + -41222.579</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>5.117943078847159e-10</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4188.927113410116</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000007216e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8222293172218975</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-290.73</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.92183e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-56.483</v>
+      </c>
+      <c r="F8" t="n">
+        <v/>
+      </c>
+      <c r="G8" t="n">
+        <v/>
+      </c>
+      <c r="H8" t="n">
+        <v/>
+      </c>
+      <c r="I8" t="n">
+        <v/>
+      </c>
+      <c r="J8" t="n">
+        <v>27.0887311722026</v>
+      </c>
+      <c r="K8" t="n">
+        <v>85.06432684311901</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 11.580x + -40809.447</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>8.618493665111624e-10</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4144.905958139941</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000000082e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8224760815639076</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-303.5900000000001</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.93504e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-56.756</v>
+      </c>
+      <c r="F9" t="n">
+        <v/>
+      </c>
+      <c r="G9" t="n">
+        <v/>
+      </c>
+      <c r="H9" t="n">
+        <v/>
+      </c>
+      <c r="I9" t="n">
+        <v/>
+      </c>
+      <c r="J9" t="n">
+        <v>19.37190160916014</v>
+      </c>
+      <c r="K9" t="n">
+        <v>84.70764319241597</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 10.795x + -37476.775</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>3.55756940921727e-09</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>4099.248886566271</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.00000000001205e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8227965679666757</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-273.7900000000004</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.94873e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-57.09</v>
+      </c>
+      <c r="F10" t="n">
+        <v/>
+      </c>
+      <c r="G10" t="n">
+        <v/>
+      </c>
+      <c r="H10" t="n">
+        <v/>
+      </c>
+      <c r="I10" t="n">
+        <v/>
+      </c>
+      <c r="J10" t="n">
+        <v>27.26501472666815</v>
+      </c>
+      <c r="K10" t="n">
+        <v>85.19662133565703</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 11.900x + -41104.675</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.916430614249844e-09</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>4053.947623021833</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000001917e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8231358699255056</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-269.8900000000003</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.96086e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-57.366</v>
+      </c>
+      <c r="F11" t="n">
+        <v/>
+      </c>
+      <c r="G11" t="n">
+        <v/>
+      </c>
+      <c r="H11" t="n">
+        <v/>
+      </c>
+      <c r="I11" t="n">
+        <v/>
+      </c>
+      <c r="J11" t="n">
+        <v>27.63803122368504</v>
+      </c>
+      <c r="K11" t="n">
+        <v>85.24536893564016</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 12.023x + -41096.082</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>6.032241603430068e-10</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>4008.970006005633</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000000006e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8235009329116452</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-281.27</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.97487e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-57.717</v>
+      </c>
+      <c r="F12" t="n">
+        <v/>
+      </c>
+      <c r="G12" t="n">
+        <v/>
+      </c>
+      <c r="H12" t="n">
+        <v/>
+      </c>
+      <c r="I12" t="n">
+        <v/>
+      </c>
+      <c r="J12" t="n">
+        <v>19.10658146349526</v>
+      </c>
+      <c r="K12" t="n">
+        <v>84.74109904396667</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 10.864x + -36516.366</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>5.039679267589776e-09</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3964.680842632226</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.000000000000819e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8238530371569871</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-253.4699999999998</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.98728e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-58</v>
+      </c>
+      <c r="F13" t="n">
+        <v/>
+      </c>
+      <c r="G13" t="n">
+        <v/>
+      </c>
+      <c r="H13" t="n">
+        <v/>
+      </c>
+      <c r="I13" t="n">
+        <v/>
+      </c>
+      <c r="J13" t="n">
+        <v>24.96569872756431</v>
+      </c>
+      <c r="K13" t="n">
+        <v>85.21576715652263</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 11.948x + -39970.979</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.247265051907677e-10</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3921.678424993902</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.000000000000091e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8242156484315452</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-240.7399999999998</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.00064e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-58.285</v>
+      </c>
+      <c r="F14" t="n">
+        <v/>
+      </c>
+      <c r="G14" t="n">
+        <v/>
+      </c>
+      <c r="H14" t="n">
+        <v/>
+      </c>
+      <c r="I14" t="n">
+        <v/>
+      </c>
+      <c r="J14" t="n">
+        <v>24.59039155872832</v>
+      </c>
+      <c r="K14" t="n">
+        <v>85.33063676030532</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 12.243x + -40569.323</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>4.275191088860601e-14</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3877.756669921092</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.000000000000015e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8246252728904193</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-257.02</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.01331e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-58.575</v>
+      </c>
+      <c r="F15" t="n">
+        <v/>
+      </c>
+      <c r="G15" t="n">
+        <v/>
+      </c>
+      <c r="H15" t="n">
+        <v/>
+      </c>
+      <c r="I15" t="n">
+        <v/>
+      </c>
+      <c r="J15" t="n">
+        <v>18.45807011782022</v>
+      </c>
+      <c r="K15" t="n">
+        <v>84.81090471609446</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 11.011x + -35870.756</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.899316326970643e-09</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3834.879772348723</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.000000000000042e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8250280491182989</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-264.25</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.02546e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-58.921</v>
+      </c>
+      <c r="F16" t="n">
+        <v/>
+      </c>
+      <c r="G16" t="n">
+        <v/>
+      </c>
+      <c r="H16" t="n">
+        <v/>
+      </c>
+      <c r="I16" t="n">
+        <v/>
+      </c>
+      <c r="J16" t="n">
+        <v>15.37663702573187</v>
+      </c>
+      <c r="K16" t="n">
+        <v>84.35721180595374</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 10.121x + -32450.866</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>6.575769629793456e-10</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3793.124220174062</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.000000000000565e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8254146570073169</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-224.6799999999998</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.03775e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-59.202</v>
+      </c>
+      <c r="F17" t="n">
+        <v/>
+      </c>
+      <c r="G17" t="n">
+        <v/>
+      </c>
+      <c r="H17" t="n">
+        <v/>
+      </c>
+      <c r="I17" t="n">
+        <v/>
+      </c>
+      <c r="J17" t="n">
+        <v>19.93989117375921</v>
+      </c>
+      <c r="K17" t="n">
+        <v>85.2385804050656</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 12.006x + -38472.166</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>3.19493814588955e-09</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3750.503077605235</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.000000000000007e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8258508770859704</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-235.96</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.05031e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-59.495</v>
+      </c>
+      <c r="F18" t="n">
+        <v/>
+      </c>
+      <c r="G18" t="n">
+        <v/>
+      </c>
+      <c r="H18" t="n">
+        <v/>
+      </c>
+      <c r="I18" t="n">
+        <v/>
+      </c>
+      <c r="J18" t="n">
+        <v>17.7789524961998</v>
+      </c>
+      <c r="K18" t="n">
+        <v>84.82500463227315</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 11.042x + -34815.307</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>3.582871598968226e-10</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3707.690031135591</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.000000000000023e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8262772065442709</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-225.79</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.06361e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-59.824</v>
+      </c>
+      <c r="F19" t="n">
+        <v/>
+      </c>
+      <c r="G19" t="n">
+        <v/>
+      </c>
+      <c r="H19" t="n">
+        <v/>
+      </c>
+      <c r="I19" t="n">
+        <v/>
+      </c>
+      <c r="J19" t="n">
+        <v>15.93720985039044</v>
+      </c>
+      <c r="K19" t="n">
+        <v>84.7160048371845</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 10.813x + -33694.900</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>7.408941785946461e-11</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3666.209999928599</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.00000000000037e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8266897368578817</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-226.0299999999997</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.07254e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-60.076</v>
+      </c>
+      <c r="F20" t="n">
+        <v/>
+      </c>
+      <c r="G20" t="n">
+        <v/>
+      </c>
+      <c r="H20" t="n">
+        <v/>
+      </c>
+      <c r="I20" t="n">
+        <v/>
+      </c>
+      <c r="J20" t="n">
+        <v>16.96394343394542</v>
+      </c>
+      <c r="K20" t="n">
+        <v>84.80918195253294</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 11.008x + -33980.125</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.435818496161628e-10</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3626.471516064093</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.000000000000036e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8271027697182183</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-210.98</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.08796e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-60.395</v>
+      </c>
+      <c r="F21" t="n">
+        <v/>
+      </c>
+      <c r="G21" t="n">
+        <v/>
+      </c>
+      <c r="H21" t="n">
+        <v/>
+      </c>
+      <c r="I21" t="n">
+        <v/>
+      </c>
+      <c r="J21" t="n">
+        <v>14.76867383791989</v>
+      </c>
+      <c r="K21" t="n">
+        <v>84.71265372220327</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 10.806x + -32959.184</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>7.518278689948309e-10</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3584.932522063923</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.000000000001987e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8275227115619795</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-209.3600000000001</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.09799e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-60.693</v>
+      </c>
+      <c r="F22" t="n">
+        <v/>
+      </c>
+      <c r="G22" t="n">
+        <v/>
+      </c>
+      <c r="H22" t="n">
+        <v/>
+      </c>
+      <c r="I22" t="n">
+        <v/>
+      </c>
+      <c r="J22" t="n">
+        <v>14.12385025259246</v>
+      </c>
+      <c r="K22" t="n">
+        <v>84.6746959006757</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 10.728x + -32345.466</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>5.277796362196904e-09</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3543.812075902712</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.000000000000289e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8279766721715116</v>
       </c>
     </row>
   </sheetData>
@@ -822,8 +1910,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -866,7 +1952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -970,8 +2056,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1001,6 +2085,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-605.8199999999997</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.48052e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-46.463</v>
+      </c>
+      <c r="F2" t="n">
+        <v/>
+      </c>
+      <c r="G2" t="n">
+        <v/>
+      </c>
+      <c r="H2" t="n">
+        <v/>
+      </c>
+      <c r="I2" t="n">
+        <v/>
+      </c>
+      <c r="J2" t="n">
+        <v/>
+      </c>
+      <c r="K2" t="n">
+        <v>82.98382619435225</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 8.125x + -38585.075</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>1073.340318774666</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2380.480950607625</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>3.617301330012724e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.6152424952174832</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-435.6900000000001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.72127e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-50.766</v>
+      </c>
+      <c r="F3" t="n">
+        <v/>
+      </c>
+      <c r="G3" t="n">
+        <v/>
+      </c>
+      <c r="H3" t="n">
+        <v/>
+      </c>
+      <c r="I3" t="n">
+        <v/>
+      </c>
+      <c r="J3" t="n">
+        <v>26.95329892419635</v>
+      </c>
+      <c r="K3" t="n">
+        <v>84.3872862644204</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 10.176x + -41718.397</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.050785003349686e-09</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>4805.057663809637</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000000005e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8212147894955127</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-414.4700000000003</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.78213e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-52.109</v>
+      </c>
+      <c r="F4" t="n">
+        <v/>
+      </c>
+      <c r="G4" t="n">
+        <v/>
+      </c>
+      <c r="H4" t="n">
+        <v/>
+      </c>
+      <c r="I4" t="n">
+        <v/>
+      </c>
+      <c r="J4" t="n">
+        <v>19.78350401214608</v>
+      </c>
+      <c r="K4" t="n">
+        <v>84.25376652323321</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 9.938x + -38984.178</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.613962061907532e-10</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>4633.811805503475</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000004e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8215589207615634</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-375.0100000000002</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.81295e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-52.933</v>
+      </c>
+      <c r="F5" t="n">
+        <v/>
+      </c>
+      <c r="G5" t="n">
+        <v/>
+      </c>
+      <c r="H5" t="n">
+        <v/>
+      </c>
+      <c r="I5" t="n">
+        <v/>
+      </c>
+      <c r="J5" t="n">
+        <v>22.0685396920798</v>
+      </c>
+      <c r="K5" t="n">
+        <v>84.52179248102041</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 10.427x + -40188.995</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.080062898592666e-10</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4548.456229770773</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000052e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.821733252221206</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-360.1699999999996</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.83132e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-53.517</v>
+      </c>
+      <c r="F6" t="n">
+        <v/>
+      </c>
+      <c r="G6" t="n">
+        <v/>
+      </c>
+      <c r="H6" t="n">
+        <v/>
+      </c>
+      <c r="I6" t="n">
+        <v/>
+      </c>
+      <c r="J6" t="n">
+        <v>23.53857131885981</v>
+      </c>
+      <c r="K6" t="n">
+        <v>84.70747604893575</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 10.795x + -41046.508</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.060273260654305e-08</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4481.83669330781</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000009808e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8219251373269048</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-344.8600000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.8503e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-54.043</v>
+      </c>
+      <c r="F7" t="n">
+        <v/>
+      </c>
+      <c r="G7" t="n">
+        <v/>
+      </c>
+      <c r="H7" t="n">
+        <v/>
+      </c>
+      <c r="I7" t="n">
+        <v/>
+      </c>
+      <c r="J7" t="n">
+        <v>24.64814990913918</v>
+      </c>
+      <c r="K7" t="n">
+        <v>84.78113512812322</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 10.948x + -41075.083</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>9.994339978598567e-09</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4420.373114729879</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000015099e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8221299115021643</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-331.1700000000001</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.86653e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-54.566</v>
+      </c>
+      <c r="F8" t="n">
+        <v/>
+      </c>
+      <c r="G8" t="n">
+        <v/>
+      </c>
+      <c r="H8" t="n">
+        <v/>
+      </c>
+      <c r="I8" t="n">
+        <v/>
+      </c>
+      <c r="J8" t="n">
+        <v>25.7320794186306</v>
+      </c>
+      <c r="K8" t="n">
+        <v>84.90649324016671</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 11.219x + -41552.923</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.917301806367308e-08</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4359.515578070504</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000000368e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8223800136204853</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-319.9399999999996</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.88258e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-54.993</v>
+      </c>
+      <c r="F9" t="n">
+        <v/>
+      </c>
+      <c r="G9" t="n">
+        <v/>
+      </c>
+      <c r="H9" t="n">
+        <v/>
+      </c>
+      <c r="I9" t="n">
+        <v/>
+      </c>
+      <c r="J9" t="n">
+        <v>26.59128939402575</v>
+      </c>
+      <c r="K9" t="n">
+        <v>84.99801088160652</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 11.425x + -41807.915</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>7.272425296825485e-09</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>4302.387579045705</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000001809e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8226410828205883</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-307.6500000000001</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.899e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-55.461</v>
+      </c>
+      <c r="F10" t="n">
+        <v/>
+      </c>
+      <c r="G10" t="n">
+        <v/>
+      </c>
+      <c r="H10" t="n">
+        <v/>
+      </c>
+      <c r="I10" t="n">
+        <v/>
+      </c>
+      <c r="J10" t="n">
+        <v>26.78021116681009</v>
+      </c>
+      <c r="K10" t="n">
+        <v>85.00741874675249</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 11.447x + -41365.480</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>3.786705163748536e-09</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>4248.92922349523</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000004836e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8229035398860658</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-296.0500000000002</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.91233e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-55.822</v>
+      </c>
+      <c r="F11" t="n">
+        <v/>
+      </c>
+      <c r="G11" t="n">
+        <v/>
+      </c>
+      <c r="H11" t="n">
+        <v/>
+      </c>
+      <c r="I11" t="n">
+        <v/>
+      </c>
+      <c r="J11" t="n">
+        <v>27.10913763618233</v>
+      </c>
+      <c r="K11" t="n">
+        <v>85.13589535915867</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 11.751x + -42023.618</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.501267779284147e-08</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>4198.953644447599</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.00000000000075e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8231605518932167</v>
       </c>
     </row>
   </sheetData>
@@ -1014,7 +2618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1118,8 +2722,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1149,6 +2751,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-497.1500000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.7404e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-51.612</v>
+      </c>
+      <c r="F2" t="n">
+        <v/>
+      </c>
+      <c r="G2" t="n">
+        <v/>
+      </c>
+      <c r="H2" t="n">
+        <v/>
+      </c>
+      <c r="I2" t="n">
+        <v/>
+      </c>
+      <c r="J2" t="n">
+        <v>15.80536756393121</v>
+      </c>
+      <c r="K2" t="n">
+        <v>83.61969474219417</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 8.943x + -35423.976</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.521657633262843e-08</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>4653.890839873927</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000054e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.822009257507645</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-396.6900000000005</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.82955e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-53.772</v>
+      </c>
+      <c r="F3" t="n">
+        <v/>
+      </c>
+      <c r="G3" t="n">
+        <v/>
+      </c>
+      <c r="H3" t="n">
+        <v/>
+      </c>
+      <c r="I3" t="n">
+        <v/>
+      </c>
+      <c r="J3" t="n">
+        <v>21.42429531582308</v>
+      </c>
+      <c r="K3" t="n">
+        <v>84.51476939731096</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 10.414x + -39193.999</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.910658385666193e-09</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>4428.909836046425</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000000407e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8222837118111335</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-361.98</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.85643e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-54.505</v>
+      </c>
+      <c r="F4" t="n">
+        <v/>
+      </c>
+      <c r="G4" t="n">
+        <v/>
+      </c>
+      <c r="H4" t="n">
+        <v/>
+      </c>
+      <c r="I4" t="n">
+        <v/>
+      </c>
+      <c r="J4" t="n">
+        <v>23.6427882330625</v>
+      </c>
+      <c r="K4" t="n">
+        <v>84.77022221196508</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 10.925x + -40420.985</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>6.229554545332458e-10</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>4352.02768845258</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000844e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8223944607923723</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-346.9000000000001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.8734e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-55.023</v>
+      </c>
+      <c r="F5" t="n">
+        <v/>
+      </c>
+      <c r="G5" t="n">
+        <v/>
+      </c>
+      <c r="H5" t="n">
+        <v/>
+      </c>
+      <c r="I5" t="n">
+        <v/>
+      </c>
+      <c r="J5" t="n">
+        <v>24.82058919404955</v>
+      </c>
+      <c r="K5" t="n">
+        <v>84.85761396175705</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 11.112x + -40590.778</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>3.760496163544514e-09</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4296.716262856918</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000816e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8225491826583423</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-338.8599999999997</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.88693e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-55.451</v>
+      </c>
+      <c r="F6" t="n">
+        <v/>
+      </c>
+      <c r="G6" t="n">
+        <v/>
+      </c>
+      <c r="H6" t="n">
+        <v/>
+      </c>
+      <c r="I6" t="n">
+        <v/>
+      </c>
+      <c r="J6" t="n">
+        <v>25.56095439365686</v>
+      </c>
+      <c r="K6" t="n">
+        <v>84.93781898397262</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 11.289x + -40766.216</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>5.185417571141088e-10</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4244.709705821757</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000000715e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8227338753599992</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-325.96</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.90111e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-55.826</v>
+      </c>
+      <c r="F7" t="n">
+        <v/>
+      </c>
+      <c r="G7" t="n">
+        <v/>
+      </c>
+      <c r="H7" t="n">
+        <v/>
+      </c>
+      <c r="I7" t="n">
+        <v/>
+      </c>
+      <c r="J7" t="n">
+        <v>26.53732754120967</v>
+      </c>
+      <c r="K7" t="n">
+        <v>85.0819747048894</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 11.622x + -41526.573</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.617339558873035e-08</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4192.791121687596</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000001757e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8229739510799018</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-314.98</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.91563e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-56.19</v>
+      </c>
+      <c r="F8" t="n">
+        <v/>
+      </c>
+      <c r="G8" t="n">
+        <v/>
+      </c>
+      <c r="H8" t="n">
+        <v/>
+      </c>
+      <c r="I8" t="n">
+        <v/>
+      </c>
+      <c r="J8" t="n">
+        <v>27.23294071201204</v>
+      </c>
+      <c r="K8" t="n">
+        <v>85.17393988620762</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 11.844x + -41860.974</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.847126196992954e-10</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4142.230575826401</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000000057e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8232435876556723</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-313.9400000000001</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.92749e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-56.553</v>
+      </c>
+      <c r="F9" t="n">
+        <v/>
+      </c>
+      <c r="G9" t="n">
+        <v/>
+      </c>
+      <c r="H9" t="n">
+        <v/>
+      </c>
+      <c r="I9" t="n">
+        <v/>
+      </c>
+      <c r="J9" t="n">
+        <v>27.54861211868943</v>
+      </c>
+      <c r="K9" t="n">
+        <v>85.16012248004422</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 11.810x + -41250.466</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.991278277557005e-08</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>4093.828928492236</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000001947e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8235277401353592</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-302.6700000000001</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.94136e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-56.891</v>
+      </c>
+      <c r="F10" t="n">
+        <v/>
+      </c>
+      <c r="G10" t="n">
+        <v/>
+      </c>
+      <c r="H10" t="n">
+        <v/>
+      </c>
+      <c r="I10" t="n">
+        <v/>
+      </c>
+      <c r="J10" t="n">
+        <v>27.02051193580768</v>
+      </c>
+      <c r="K10" t="n">
+        <v>85.21521602354497</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 11.947x + -41277.836</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>7.891125767703922e-09</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>4047.154068088556</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000006667e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.823822863137099</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-315.7999999999997</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.95373e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-57.255</v>
+      </c>
+      <c r="F11" t="n">
+        <v/>
+      </c>
+      <c r="G11" t="n">
+        <v/>
+      </c>
+      <c r="H11" t="n">
+        <v/>
+      </c>
+      <c r="I11" t="n">
+        <v/>
+      </c>
+      <c r="J11" t="n">
+        <v>19.45317885914734</v>
+      </c>
+      <c r="K11" t="n">
+        <v>84.7370648577123</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 10.856x + -36879.855</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>3.299733213975684e-09</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>4001.816873409182</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000005228e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8241204222330815</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-309.4000000000001</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.96646e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-57.575</v>
+      </c>
+      <c r="F12" t="n">
+        <v/>
+      </c>
+      <c r="G12" t="n">
+        <v/>
+      </c>
+      <c r="H12" t="n">
+        <v/>
+      </c>
+      <c r="I12" t="n">
+        <v/>
+      </c>
+      <c r="J12" t="n">
+        <v>19.63696443723968</v>
+      </c>
+      <c r="K12" t="n">
+        <v>84.81127316187894</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 11.012x + -37032.877</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.265069957050443e-11</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3958.889677470831</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.000000000000027e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8244113334389541</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-277.54</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.97745e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-57.895</v>
+      </c>
+      <c r="F13" t="n">
+        <v/>
+      </c>
+      <c r="G13" t="n">
+        <v/>
+      </c>
+      <c r="H13" t="n">
+        <v/>
+      </c>
+      <c r="I13" t="n">
+        <v/>
+      </c>
+      <c r="J13" t="n">
+        <v>29.07873651899439</v>
+      </c>
+      <c r="K13" t="n">
+        <v>85.39710007192203</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 12.421x + -41640.336</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.168556271462451e-08</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3917.910732737846</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.000000000000023e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8247143340065746</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-294.5899999999997</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.98762e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-58.195</v>
+      </c>
+      <c r="F14" t="n">
+        <v/>
+      </c>
+      <c r="G14" t="n">
+        <v/>
+      </c>
+      <c r="H14" t="n">
+        <v/>
+      </c>
+      <c r="I14" t="n">
+        <v/>
+      </c>
+      <c r="J14" t="n">
+        <v>20.23504707766923</v>
+      </c>
+      <c r="K14" t="n">
+        <v>84.92263007399227</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 11.255x + -37119.708</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>4.648870650044301e-10</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3877.639945750469</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.000000000000102e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.825016702540156</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-288.9499999999998</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.99886e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-58.472</v>
+      </c>
+      <c r="F15" t="n">
+        <v/>
+      </c>
+      <c r="G15" t="n">
+        <v/>
+      </c>
+      <c r="H15" t="n">
+        <v/>
+      </c>
+      <c r="I15" t="n">
+        <v/>
+      </c>
+      <c r="J15" t="n">
+        <v>20.8445560842057</v>
+      </c>
+      <c r="K15" t="n">
+        <v>84.93737002792997</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 11.288x + -36871.411</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>3.043708393811753e-10</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3837.930304753713</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.00000000000016e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.825319064533551</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-256.2600000000002</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.01107e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-58.781</v>
+      </c>
+      <c r="F16" t="n">
+        <v/>
+      </c>
+      <c r="G16" t="n">
+        <v/>
+      </c>
+      <c r="H16" t="n">
+        <v/>
+      </c>
+      <c r="I16" t="n">
+        <v/>
+      </c>
+      <c r="J16" t="n">
+        <v>28.09767063202844</v>
+      </c>
+      <c r="K16" t="n">
+        <v>85.46533146925215</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 12.609x + -41045.803</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>3.395595330295504e-11</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3799.431494836769</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8256429642873628</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-273.6300000000001</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.02057e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-59.052</v>
+      </c>
+      <c r="F17" t="n">
+        <v/>
+      </c>
+      <c r="G17" t="n">
+        <v/>
+      </c>
+      <c r="H17" t="n">
+        <v/>
+      </c>
+      <c r="I17" t="n">
+        <v/>
+      </c>
+      <c r="J17" t="n">
+        <v>20.7898205685205</v>
+      </c>
+      <c r="K17" t="n">
+        <v>85.09085296151095</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 11.643x + -37345.720</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>8.747000056007439e-11</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3761.326044031936</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.000000000002902e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8259749772504272</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-270.6599999999999</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.02991e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-59.312</v>
+      </c>
+      <c r="F18" t="n">
+        <v/>
+      </c>
+      <c r="G18" t="n">
+        <v/>
+      </c>
+      <c r="H18" t="n">
+        <v/>
+      </c>
+      <c r="I18" t="n">
+        <v/>
+      </c>
+      <c r="J18" t="n">
+        <v>21.06281228617451</v>
+      </c>
+      <c r="K18" t="n">
+        <v>85.08234391024732</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 11.622x + -36912.860</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>2.857883550239786e-10</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3723.576550417546</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.000000000001416e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8263112472701906</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-261.96</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.04096e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-59.615</v>
+      </c>
+      <c r="F19" t="n">
+        <v/>
+      </c>
+      <c r="G19" t="n">
+        <v/>
+      </c>
+      <c r="H19" t="n">
+        <v/>
+      </c>
+      <c r="I19" t="n">
+        <v/>
+      </c>
+      <c r="J19" t="n">
+        <v>21.19331394613341</v>
+      </c>
+      <c r="K19" t="n">
+        <v>85.11374002852462</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 11.697x + -36789.860</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>5.615926122380126e-09</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3685.61143786212</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.000000000000003e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8266511461515116</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-252.54</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.05255e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-59.917</v>
+      </c>
+      <c r="F20" t="n">
+        <v/>
+      </c>
+      <c r="G20" t="n">
+        <v/>
+      </c>
+      <c r="H20" t="n">
+        <v/>
+      </c>
+      <c r="I20" t="n">
+        <v/>
+      </c>
+      <c r="J20" t="n">
+        <v>20.14949645550572</v>
+      </c>
+      <c r="K20" t="n">
+        <v>85.10782026205494</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 11.683x + -36383.086</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>7.181368074988119e-09</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3648.260515367372</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.000000000000405e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8269918156953366</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-241.21</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.06397e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-60.194</v>
+      </c>
+      <c r="F21" t="n">
+        <v/>
+      </c>
+      <c r="G21" t="n">
+        <v/>
+      </c>
+      <c r="H21" t="n">
+        <v/>
+      </c>
+      <c r="I21" t="n">
+        <v/>
+      </c>
+      <c r="J21" t="n">
+        <v>20.44265190731937</v>
+      </c>
+      <c r="K21" t="n">
+        <v>85.15954364590017</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 11.809x + -36425.825</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.532190754060749e-09</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3610.871663855977</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.000000000001747e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8273418932734479</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-235.9699999999998</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.075e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-60.454</v>
+      </c>
+      <c r="F22" t="n">
+        <v/>
+      </c>
+      <c r="G22" t="n">
+        <v/>
+      </c>
+      <c r="H22" t="n">
+        <v/>
+      </c>
+      <c r="I22" t="n">
+        <v/>
+      </c>
+      <c r="J22" t="n">
+        <v>19.63981274224047</v>
+      </c>
+      <c r="K22" t="n">
+        <v>85.13022644778653</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 11.737x + -35833.967</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>3.959365931943967e-10</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3574.213531026992</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.000000000000061e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8276946885465546</v>
       </c>
     </row>
   </sheetData>
@@ -1162,7 +3856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1266,8 +3960,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1297,6 +3989,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-646.7700000000004</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.48884e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-46.561</v>
+      </c>
+      <c r="F2" t="n">
+        <v/>
+      </c>
+      <c r="G2" t="n">
+        <v/>
+      </c>
+      <c r="H2" t="n">
+        <v/>
+      </c>
+      <c r="I2" t="n">
+        <v/>
+      </c>
+      <c r="J2" t="n">
+        <v>13.95431848200768</v>
+      </c>
+      <c r="K2" t="n">
+        <v>82.26140399246577</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 7.359x + -34424.683</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>1055.080731106669</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2293.908302385268</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.835846168589033e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.6145226704576398</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-437.29</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.73239e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-51.143</v>
+      </c>
+      <c r="F3" t="n">
+        <v/>
+      </c>
+      <c r="G3" t="n">
+        <v/>
+      </c>
+      <c r="H3" t="n">
+        <v/>
+      </c>
+      <c r="I3" t="n">
+        <v/>
+      </c>
+      <c r="J3" t="n">
+        <v>27.86463133640575</v>
+      </c>
+      <c r="K3" t="n">
+        <v>84.34246022243882</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 10.094x + -40963.239</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.623045504896294e-09</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>4753.384423106874</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8229912899343546</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-402.73</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.79275e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-52.575</v>
+      </c>
+      <c r="F4" t="n">
+        <v/>
+      </c>
+      <c r="G4" t="n">
+        <v/>
+      </c>
+      <c r="H4" t="n">
+        <v/>
+      </c>
+      <c r="I4" t="n">
+        <v/>
+      </c>
+      <c r="J4" t="n">
+        <v>20.8952806295109</v>
+      </c>
+      <c r="K4" t="n">
+        <v>84.30001966450594</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 10.019x + -38971.582</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>8.249716657774193e-13</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>4590.643252646193</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000002e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8232579298149726</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-380.4199999999996</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.81596e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-53.34</v>
+      </c>
+      <c r="F5" t="n">
+        <v/>
+      </c>
+      <c r="G5" t="n">
+        <v/>
+      </c>
+      <c r="H5" t="n">
+        <v/>
+      </c>
+      <c r="I5" t="n">
+        <v/>
+      </c>
+      <c r="J5" t="n">
+        <v>22.03984047115442</v>
+      </c>
+      <c r="K5" t="n">
+        <v>84.52616719992889</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 10.435x + -39914.770</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.602638798140937e-09</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4510.666258300266</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000017e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.823360084840128</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-346.2800000000002</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.84015e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-54.021</v>
+      </c>
+      <c r="F6" t="n">
+        <v/>
+      </c>
+      <c r="G6" t="n">
+        <v/>
+      </c>
+      <c r="H6" t="n">
+        <v/>
+      </c>
+      <c r="I6" t="n">
+        <v/>
+      </c>
+      <c r="J6" t="n">
+        <v>24.04207623565517</v>
+      </c>
+      <c r="K6" t="n">
+        <v>84.67154290748921</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 10.722x + -40424.185</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.169127569493476e-10</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4443.624127221153</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000002368e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8235246772451655</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-335.6100000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.85589e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-54.497</v>
+      </c>
+      <c r="F7" t="n">
+        <v/>
+      </c>
+      <c r="G7" t="n">
+        <v/>
+      </c>
+      <c r="H7" t="n">
+        <v/>
+      </c>
+      <c r="I7" t="n">
+        <v/>
+      </c>
+      <c r="J7" t="n">
+        <v>25.2172626751923</v>
+      </c>
+      <c r="K7" t="n">
+        <v>84.80952539062433</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 11.008x + -40989.636</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>3.488492394900494e-10</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4381.919398490669</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.00000000000195e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8237249067440294</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-331.1100000000001</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.87196e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-54.964</v>
+      </c>
+      <c r="F8" t="n">
+        <v/>
+      </c>
+      <c r="G8" t="n">
+        <v/>
+      </c>
+      <c r="H8" t="n">
+        <v/>
+      </c>
+      <c r="I8" t="n">
+        <v/>
+      </c>
+      <c r="J8" t="n">
+        <v>26.20822687858353</v>
+      </c>
+      <c r="K8" t="n">
+        <v>84.88251420967354</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 11.166x + -41023.953</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>5.089663676532676e-09</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4320.782336644716</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000002041e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8239450403728921</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-316.52</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.88975e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-55.377</v>
+      </c>
+      <c r="F9" t="n">
+        <v/>
+      </c>
+      <c r="G9" t="n">
+        <v/>
+      </c>
+      <c r="H9" t="n">
+        <v/>
+      </c>
+      <c r="I9" t="n">
+        <v/>
+      </c>
+      <c r="J9" t="n">
+        <v>26.43314639836931</v>
+      </c>
+      <c r="K9" t="n">
+        <v>84.96493977149893</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 11.350x + -41162.870</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.34267778668352e-10</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>4261.567840336447</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000000184e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8241914609811108</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-308.8400000000001</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.90513e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-55.776</v>
+      </c>
+      <c r="F10" t="n">
+        <v/>
+      </c>
+      <c r="G10" t="n">
+        <v/>
+      </c>
+      <c r="H10" t="n">
+        <v/>
+      </c>
+      <c r="I10" t="n">
+        <v/>
+      </c>
+      <c r="J10" t="n">
+        <v>27.01127220302497</v>
+      </c>
+      <c r="K10" t="n">
+        <v>85.03391924578762</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 11.509x + -41216.367</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>3.533449238697481e-10</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>4205.152332984519</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8244515101577351</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-318.1900000000001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.92177e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-56.155</v>
+      </c>
+      <c r="F11" t="n">
+        <v/>
+      </c>
+      <c r="G11" t="n">
+        <v/>
+      </c>
+      <c r="H11" t="n">
+        <v/>
+      </c>
+      <c r="I11" t="n">
+        <v/>
+      </c>
+      <c r="J11" t="n">
+        <v>19.15166425131052</v>
+      </c>
+      <c r="K11" t="n">
+        <v>84.54892914421082</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 10.479x + -36846.719</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.123019456708511e-09</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>4152.477972393427</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8247106339197313</v>
       </c>
     </row>
   </sheetData>
@@ -1310,7 +4522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1414,8 +4626,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1445,6 +4655,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-442.3800000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.75491e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-51.89</v>
+      </c>
+      <c r="F2" t="n">
+        <v/>
+      </c>
+      <c r="G2" t="n">
+        <v/>
+      </c>
+      <c r="H2" t="n">
+        <v/>
+      </c>
+      <c r="I2" t="n">
+        <v/>
+      </c>
+      <c r="J2" t="n">
+        <v>27.59272978402799</v>
+      </c>
+      <c r="K2" t="n">
+        <v>84.37194995486097</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 10.148x + -40301.795</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.235926572917609e-10</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>4630.804069233268</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000034e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8221048472046478</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-374.9000000000001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.83769e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-54.017</v>
+      </c>
+      <c r="F3" t="n">
+        <v/>
+      </c>
+      <c r="G3" t="n">
+        <v/>
+      </c>
+      <c r="H3" t="n">
+        <v/>
+      </c>
+      <c r="I3" t="n">
+        <v/>
+      </c>
+      <c r="J3" t="n">
+        <v>22.82623251127622</v>
+      </c>
+      <c r="K3" t="n">
+        <v>84.56822515595378</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 10.517x + -39451.086</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>3.108028271526496e-09</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>4417.453442020096</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000004962e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8225563345688474</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-344.0300000000002</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.86394e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-54.725</v>
+      </c>
+      <c r="F4" t="n">
+        <v/>
+      </c>
+      <c r="G4" t="n">
+        <v/>
+      </c>
+      <c r="H4" t="n">
+        <v/>
+      </c>
+      <c r="I4" t="n">
+        <v/>
+      </c>
+      <c r="J4" t="n">
+        <v>24.51287055358055</v>
+      </c>
+      <c r="K4" t="n">
+        <v>84.82002628009154</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 11.031x + -40680.185</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>3.29061613257218e-09</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>4341.507534985692</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000843e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8226257679467391</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-352.1500000000001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.88149e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-55.169</v>
+      </c>
+      <c r="F5" t="n">
+        <v/>
+      </c>
+      <c r="G5" t="n">
+        <v/>
+      </c>
+      <c r="H5" t="n">
+        <v/>
+      </c>
+      <c r="I5" t="n">
+        <v/>
+      </c>
+      <c r="J5" t="n">
+        <v>18.11282648875707</v>
+      </c>
+      <c r="K5" t="n">
+        <v>84.41382556502128</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 10.224x + -37035.445</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>9.156242664486849e-10</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4287.261472372335</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000538e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8226956556291416</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-317.3000000000002</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.89596e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-55.575</v>
+      </c>
+      <c r="F6" t="n">
+        <v/>
+      </c>
+      <c r="G6" t="n">
+        <v/>
+      </c>
+      <c r="H6" t="n">
+        <v/>
+      </c>
+      <c r="I6" t="n">
+        <v/>
+      </c>
+      <c r="J6" t="n">
+        <v>26.45452793241984</v>
+      </c>
+      <c r="K6" t="n">
+        <v>85.04345898647802</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 11.531x + -41565.985</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.702110812891749e-09</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4236.770548968717</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.00000000000441e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8228350793944276</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-302.0599999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.91017e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-55.973</v>
+      </c>
+      <c r="F7" t="n">
+        <v/>
+      </c>
+      <c r="G7" t="n">
+        <v/>
+      </c>
+      <c r="H7" t="n">
+        <v/>
+      </c>
+      <c r="I7" t="n">
+        <v/>
+      </c>
+      <c r="J7" t="n">
+        <v>26.56572692187813</v>
+      </c>
+      <c r="K7" t="n">
+        <v>85.06295837070962</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 11.577x + -41291.753</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.017413315847881e-08</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4191.244207467593</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000018746e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8229938002867007</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-298.8500000000004</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.92212e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-56.199</v>
+      </c>
+      <c r="F8" t="n">
+        <v/>
+      </c>
+      <c r="G8" t="n">
+        <v/>
+      </c>
+      <c r="H8" t="n">
+        <v/>
+      </c>
+      <c r="I8" t="n">
+        <v/>
+      </c>
+      <c r="J8" t="n">
+        <v>27.64669491980051</v>
+      </c>
+      <c r="K8" t="n">
+        <v>85.16472102842944</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 11.821x + -41786.273</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.135560371762622e-08</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4150.409573333377</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000000954e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8231822725271206</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-313.2399999999998</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.93405e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-56.525</v>
+      </c>
+      <c r="F9" t="n">
+        <v/>
+      </c>
+      <c r="G9" t="n">
+        <v/>
+      </c>
+      <c r="H9" t="n">
+        <v/>
+      </c>
+      <c r="I9" t="n">
+        <v/>
+      </c>
+      <c r="J9" t="n">
+        <v>19.30858730449951</v>
+      </c>
+      <c r="K9" t="n">
+        <v>84.63053671236834</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 10.639x + -37016.404</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>9.005111509448654e-09</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>4109.546372580284</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.00000000000022e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8234282708077202</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-288.8299999999999</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.94314e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-56.788</v>
+      </c>
+      <c r="F10" t="n">
+        <v/>
+      </c>
+      <c r="G10" t="n">
+        <v/>
+      </c>
+      <c r="H10" t="n">
+        <v/>
+      </c>
+      <c r="I10" t="n">
+        <v/>
+      </c>
+      <c r="J10" t="n">
+        <v>28.36106753744489</v>
+      </c>
+      <c r="K10" t="n">
+        <v>85.25099179818707</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 12.037x + -41782.158</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>8.968435402752091e-09</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>4069.647770720112</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.00000000000632e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8236899122693221</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-277.3600000000001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.95722e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-57.079</v>
+      </c>
+      <c r="F11" t="n">
+        <v/>
+      </c>
+      <c r="G11" t="n">
+        <v/>
+      </c>
+      <c r="H11" t="n">
+        <v/>
+      </c>
+      <c r="I11" t="n">
+        <v/>
+      </c>
+      <c r="J11" t="n">
+        <v>27.92042645438121</v>
+      </c>
+      <c r="K11" t="n">
+        <v>85.24754351245532</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 12.028x + -41345.471</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.649035460946066e-08</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>4030.907290418277</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000000046e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8239733101540355</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-287.6700000000001</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.96823e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-57.347</v>
+      </c>
+      <c r="F12" t="n">
+        <v/>
+      </c>
+      <c r="G12" t="n">
+        <v/>
+      </c>
+      <c r="H12" t="n">
+        <v/>
+      </c>
+      <c r="I12" t="n">
+        <v/>
+      </c>
+      <c r="J12" t="n">
+        <v>19.98037230259835</v>
+      </c>
+      <c r="K12" t="n">
+        <v>84.81800580983017</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 11.027x + -37364.129</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.284098864596018e-08</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3993.970859178094</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.000000000001263e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8242834479309225</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-282.02</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.97715e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-57.624</v>
+      </c>
+      <c r="F13" t="n">
+        <v/>
+      </c>
+      <c r="G13" t="n">
+        <v/>
+      </c>
+      <c r="H13" t="n">
+        <v/>
+      </c>
+      <c r="I13" t="n">
+        <v/>
+      </c>
+      <c r="J13" t="n">
+        <v>19.98402491702364</v>
+      </c>
+      <c r="K13" t="n">
+        <v>84.83859398258224</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 11.071x + -37195.101</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>8.622869047033051e-09</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3957.811488573836</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.000000000000254e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8245971474306878</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-254.0799999999999</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.98851e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-57.901</v>
+      </c>
+      <c r="F14" t="n">
+        <v/>
+      </c>
+      <c r="G14" t="n">
+        <v/>
+      </c>
+      <c r="H14" t="n">
+        <v/>
+      </c>
+      <c r="I14" t="n">
+        <v/>
+      </c>
+      <c r="J14" t="n">
+        <v>28.44972669221585</v>
+      </c>
+      <c r="K14" t="n">
+        <v>85.39142285893249</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 12.406x + -41572.932</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>5.380529307457898e-09</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3921.772438603268</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.000000000001409e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.824929133047656</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-264.77</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.99831e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-58.177</v>
+      </c>
+      <c r="F15" t="n">
+        <v/>
+      </c>
+      <c r="G15" t="n">
+        <v/>
+      </c>
+      <c r="H15" t="n">
+        <v/>
+      </c>
+      <c r="I15" t="n">
+        <v/>
+      </c>
+      <c r="J15" t="n">
+        <v>19.56378384075881</v>
+      </c>
+      <c r="K15" t="n">
+        <v>84.88020865647478</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 11.161x + -36859.368</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.31898092160703e-08</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3886.490196109462</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.000000000000254e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8252696574222939</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-242.3099999999999</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.00891e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-58.424</v>
+      </c>
+      <c r="F16" t="n">
+        <v/>
+      </c>
+      <c r="G16" t="n">
+        <v/>
+      </c>
+      <c r="H16" t="n">
+        <v/>
+      </c>
+      <c r="I16" t="n">
+        <v/>
+      </c>
+      <c r="J16" t="n">
+        <v>25.89321945754013</v>
+      </c>
+      <c r="K16" t="n">
+        <v>85.36840923792033</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 12.344x + -40623.664</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>3.887219174510559e-10</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3850.310176161137</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.000000000000003e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.825628827317609</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-236.7600000000002</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.01834e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-58.697</v>
+      </c>
+      <c r="F17" t="n">
+        <v/>
+      </c>
+      <c r="G17" t="n">
+        <v/>
+      </c>
+      <c r="H17" t="n">
+        <v/>
+      </c>
+      <c r="I17" t="n">
+        <v/>
+      </c>
+      <c r="J17" t="n">
+        <v>25.05047363362567</v>
+      </c>
+      <c r="K17" t="n">
+        <v>85.38427135282539</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 12.386x + -40396.953</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>3.847306411100364e-13</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3813.412746061818</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.000000000000934e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8260062046316344</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-248.9699999999998</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.02906e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-58.99</v>
+      </c>
+      <c r="F18" t="n">
+        <v/>
+      </c>
+      <c r="G18" t="n">
+        <v/>
+      </c>
+      <c r="H18" t="n">
+        <v/>
+      </c>
+      <c r="I18" t="n">
+        <v/>
+      </c>
+      <c r="J18" t="n">
+        <v>19.23217504524397</v>
+      </c>
+      <c r="K18" t="n">
+        <v>84.92813358557217</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 11.267x + -36189.511</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>2.319893135992098e-10</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3775.852345068222</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.000000000002044e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8263648821343076</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-240</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.04115e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-59.283</v>
+      </c>
+      <c r="F19" t="n">
+        <v/>
+      </c>
+      <c r="G19" t="n">
+        <v/>
+      </c>
+      <c r="H19" t="n">
+        <v/>
+      </c>
+      <c r="I19" t="n">
+        <v/>
+      </c>
+      <c r="J19" t="n">
+        <v>18.46915933280407</v>
+      </c>
+      <c r="K19" t="n">
+        <v>84.89451430268149</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 11.193x + -35593.802</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>6.150625741378004e-10</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3736.967588206503</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.000000000000714e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8267412714764809</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-237.8499999999999</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.05174e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-59.531</v>
+      </c>
+      <c r="F20" t="n">
+        <v/>
+      </c>
+      <c r="G20" t="n">
+        <v/>
+      </c>
+      <c r="H20" t="n">
+        <v/>
+      </c>
+      <c r="I20" t="n">
+        <v/>
+      </c>
+      <c r="J20" t="n">
+        <v>18.53077271825167</v>
+      </c>
+      <c r="K20" t="n">
+        <v>84.91390576830854</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 11.236x + -35380.260</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.772094132424919e-11</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3699.112071811785</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.000000000000024e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8271133211563122</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-230.1399999999999</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.06385e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-59.815</v>
+      </c>
+      <c r="F21" t="n">
+        <v/>
+      </c>
+      <c r="G21" t="n">
+        <v/>
+      </c>
+      <c r="H21" t="n">
+        <v/>
+      </c>
+      <c r="I21" t="n">
+        <v/>
+      </c>
+      <c r="J21" t="n">
+        <v>17.83589165864721</v>
+      </c>
+      <c r="K21" t="n">
+        <v>84.83976307364459</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 11.073x + -34508.166</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>3.085022071799043e-10</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3661.643515416152</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.000000000001086e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8274980305933948</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-236.3099999999999</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.07473e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-60.114</v>
+      </c>
+      <c r="F22" t="n">
+        <v/>
+      </c>
+      <c r="G22" t="n">
+        <v/>
+      </c>
+      <c r="H22" t="n">
+        <v/>
+      </c>
+      <c r="I22" t="n">
+        <v/>
+      </c>
+      <c r="J22" t="n">
+        <v>14.96460868481587</v>
+      </c>
+      <c r="K22" t="n">
+        <v>84.391455818899</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 10.183x + -31263.076</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>5.122970399824468e-10</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3624.657915364857</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.00000000000025e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8278679086827951</v>
       </c>
     </row>
   </sheetData>
@@ -1458,7 +5760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1562,8 +5864,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1593,6 +5893,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-705.1000000000004</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.52123e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-47.428</v>
+      </c>
+      <c r="F2" t="n">
+        <v/>
+      </c>
+      <c r="G2" t="n">
+        <v/>
+      </c>
+      <c r="H2" t="n">
+        <v/>
+      </c>
+      <c r="I2" t="n">
+        <v/>
+      </c>
+      <c r="J2" t="n">
+        <v>11.8411255528722</v>
+      </c>
+      <c r="K2" t="n">
+        <v>81.81875342185096</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 6.956x + -31236.518</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>934.1838519358612</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2385.730023543495</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>5.80745350768789e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.7363421459057979</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-486.6899999999996</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.76576e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-53.124</v>
+      </c>
+      <c r="F3" t="n">
+        <v/>
+      </c>
+      <c r="G3" t="n">
+        <v/>
+      </c>
+      <c r="H3" t="n">
+        <v/>
+      </c>
+      <c r="I3" t="n">
+        <v/>
+      </c>
+      <c r="J3" t="n">
+        <v>16.62453970166457</v>
+      </c>
+      <c r="K3" t="n">
+        <v>83.93441480572473</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 9.411x + -36215.349</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>6.272320891073169e-09</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>4524.855126340347</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000000235e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8234124332634237</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-411.7999999999997</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.8188e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-55.067</v>
+      </c>
+      <c r="F4" t="n">
+        <v/>
+      </c>
+      <c r="G4" t="n">
+        <v/>
+      </c>
+      <c r="H4" t="n">
+        <v/>
+      </c>
+      <c r="I4" t="n">
+        <v/>
+      </c>
+      <c r="J4" t="n">
+        <v>21.10830254596925</v>
+      </c>
+      <c r="K4" t="n">
+        <v>84.67557237840853</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 10.730x + -39782.669</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>6.204547895892845e-10</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>4358.934873678555</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.00000000000358e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8237604055654809</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-399.8800000000001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.83869e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-56.128</v>
+      </c>
+      <c r="F5" t="n">
+        <v/>
+      </c>
+      <c r="G5" t="n">
+        <v/>
+      </c>
+      <c r="H5" t="n">
+        <v/>
+      </c>
+      <c r="I5" t="n">
+        <v/>
+      </c>
+      <c r="J5" t="n">
+        <v>17.57522717460053</v>
+      </c>
+      <c r="K5" t="n">
+        <v>84.50587999348703</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 10.397x + -37610.762</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>8.426656367275097e-10</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4276.393863301896</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.00000000000093e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8239580991425192</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-362.1199999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.8523e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-56.826</v>
+      </c>
+      <c r="F6" t="n">
+        <v/>
+      </c>
+      <c r="G6" t="n">
+        <v/>
+      </c>
+      <c r="H6" t="n">
+        <v/>
+      </c>
+      <c r="I6" t="n">
+        <v/>
+      </c>
+      <c r="J6" t="n">
+        <v>24.86129651925934</v>
+      </c>
+      <c r="K6" t="n">
+        <v>85.16510080591267</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 11.822x + -42398.091</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>5.687449380712621e-09</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4207.704869634666</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000000369e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8241605078711838</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-368.5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.86485e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-57.484</v>
+      </c>
+      <c r="F7" t="n">
+        <v/>
+      </c>
+      <c r="G7" t="n">
+        <v/>
+      </c>
+      <c r="H7" t="n">
+        <v/>
+      </c>
+      <c r="I7" t="n">
+        <v/>
+      </c>
+      <c r="J7" t="n">
+        <v>18.92770380093925</v>
+      </c>
+      <c r="K7" t="n">
+        <v>84.81679480537839</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 11.024x + -38723.295</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>9.464932124904462e-10</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4143.848226298488</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000000707e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8244163783822376</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-327.96</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.87917e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-58.051</v>
+      </c>
+      <c r="F8" t="n">
+        <v/>
+      </c>
+      <c r="G8" t="n">
+        <v/>
+      </c>
+      <c r="H8" t="n">
+        <v/>
+      </c>
+      <c r="I8" t="n">
+        <v/>
+      </c>
+      <c r="J8" t="n">
+        <v>27.65202975452043</v>
+      </c>
+      <c r="K8" t="n">
+        <v>85.47121552740533</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 12.625x + -44019.348</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>5.854478355294012e-10</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4080.674369677742</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000004136e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8247059006146168</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-338.6500000000001</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.89215e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-58.591</v>
+      </c>
+      <c r="F9" t="n">
+        <v/>
+      </c>
+      <c r="G9" t="n">
+        <v/>
+      </c>
+      <c r="H9" t="n">
+        <v/>
+      </c>
+      <c r="I9" t="n">
+        <v/>
+      </c>
+      <c r="J9" t="n">
+        <v>20.56573264681106</v>
+      </c>
+      <c r="K9" t="n">
+        <v>85.06304538093933</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 11.577x + -39527.863</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>8.888881286838853e-11</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>4019.159256258269</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000000784e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.825002482074498</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-325.04</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.9051e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-59.116</v>
+      </c>
+      <c r="F10" t="n">
+        <v/>
+      </c>
+      <c r="G10" t="n">
+        <v/>
+      </c>
+      <c r="H10" t="n">
+        <v/>
+      </c>
+      <c r="I10" t="n">
+        <v/>
+      </c>
+      <c r="J10" t="n">
+        <v>21.05599875221489</v>
+      </c>
+      <c r="K10" t="n">
+        <v>85.13379570002498</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 11.746x + -39530.004</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.195807746173208e-09</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3958.81546257119</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000004721e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8253164429880856</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-311</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.91838e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-59.576</v>
+      </c>
+      <c r="F11" t="n">
+        <v/>
+      </c>
+      <c r="G11" t="n">
+        <v/>
+      </c>
+      <c r="H11" t="n">
+        <v/>
+      </c>
+      <c r="I11" t="n">
+        <v/>
+      </c>
+      <c r="J11" t="n">
+        <v>21.22271501954666</v>
+      </c>
+      <c r="K11" t="n">
+        <v>85.26426734790432</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 12.071x + -40091.100</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>8.500939757938179e-13</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3902.332604730684</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8256437444659664</v>
       </c>
     </row>
   </sheetData>
@@ -1606,7 +6426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1710,8 +6530,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1741,6 +6559,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-493.6099999999997</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.73994e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-53.809</v>
+      </c>
+      <c r="F2" t="n">
+        <v/>
+      </c>
+      <c r="G2" t="n">
+        <v/>
+      </c>
+      <c r="H2" t="n">
+        <v/>
+      </c>
+      <c r="I2" t="n">
+        <v/>
+      </c>
+      <c r="J2" t="n">
+        <v>16.65024202766109</v>
+      </c>
+      <c r="K2" t="n">
+        <v>84.0920575826744</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 9.664x + -37438.652</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>9.02175536139579e-10</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>4546.412649936276</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000494e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8220192080178026</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-386.9099999999999</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.82652e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-55.663</v>
+      </c>
+      <c r="F3" t="n">
+        <v/>
+      </c>
+      <c r="G3" t="n">
+        <v/>
+      </c>
+      <c r="H3" t="n">
+        <v/>
+      </c>
+      <c r="I3" t="n">
+        <v/>
+      </c>
+      <c r="J3" t="n">
+        <v>22.85443355856995</v>
+      </c>
+      <c r="K3" t="n">
+        <v>84.9164167634538</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 11.241x + -41405.882</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>5.434593854780971e-09</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>4329.940258969168</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.00000000000021e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8224567307894971</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-383.71</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.85529e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-56.196</v>
+      </c>
+      <c r="F4" t="n">
+        <v/>
+      </c>
+      <c r="G4" t="n">
+        <v/>
+      </c>
+      <c r="H4" t="n">
+        <v/>
+      </c>
+      <c r="I4" t="n">
+        <v/>
+      </c>
+      <c r="J4" t="n">
+        <v>18.16672113947876</v>
+      </c>
+      <c r="K4" t="n">
+        <v>84.62196794710012</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 10.622x + -38183.288</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.14876472356141e-10</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>4249.136279704687</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8226063387188727</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-339.3299999999999</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.87585e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-56.593</v>
+      </c>
+      <c r="F5" t="n">
+        <v/>
+      </c>
+      <c r="G5" t="n">
+        <v/>
+      </c>
+      <c r="H5" t="n">
+        <v/>
+      </c>
+      <c r="I5" t="n">
+        <v/>
+      </c>
+      <c r="J5" t="n">
+        <v>26.20309514312794</v>
+      </c>
+      <c r="K5" t="n">
+        <v>85.21983237533961</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 11.958x + -42711.436</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>8.024843145068984e-09</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4193.692545303805</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.00000000000157e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8227340276455047</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-360.48</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.88969e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-56.774</v>
+      </c>
+      <c r="F6" t="n">
+        <v/>
+      </c>
+      <c r="G6" t="n">
+        <v/>
+      </c>
+      <c r="H6" t="n">
+        <v/>
+      </c>
+      <c r="I6" t="n">
+        <v/>
+      </c>
+      <c r="J6" t="n">
+        <v>18.92207292077714</v>
+      </c>
+      <c r="K6" t="n">
+        <v>84.76044963981306</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 10.905x + -38282.818</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>2.880066108315514e-09</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>4145.208135336991</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000000003e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8229057467374162</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-344.9500000000003</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.90505e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-57.086</v>
+      </c>
+      <c r="F7" t="n">
+        <v/>
+      </c>
+      <c r="G7" t="n">
+        <v/>
+      </c>
+      <c r="H7" t="n">
+        <v/>
+      </c>
+      <c r="I7" t="n">
+        <v/>
+      </c>
+      <c r="J7" t="n">
+        <v>19.17563979517855</v>
+      </c>
+      <c r="K7" t="n">
+        <v>84.80621311420852</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 11.001x + -38231.144</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.145084303727157e-09</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4100.652651665622</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000000176e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8231095843191591</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-347.9200000000001</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.91511e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-57.264</v>
+      </c>
+      <c r="F8" t="n">
+        <v/>
+      </c>
+      <c r="G8" t="n">
+        <v/>
+      </c>
+      <c r="H8" t="n">
+        <v/>
+      </c>
+      <c r="I8" t="n">
+        <v/>
+      </c>
+      <c r="J8" t="n">
+        <v>19.28426167645472</v>
+      </c>
+      <c r="K8" t="n">
+        <v>84.85197506290906</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 11.100x + -38216.493</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.515083079458712e-10</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4058.707393125731</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.00000000000002e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8233472699662109</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-333.4499999999998</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.9295e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-57.577</v>
+      </c>
+      <c r="F9" t="n">
+        <v/>
+      </c>
+      <c r="G9" t="n">
+        <v/>
+      </c>
+      <c r="H9" t="n">
+        <v/>
+      </c>
+      <c r="I9" t="n">
+        <v/>
+      </c>
+      <c r="J9" t="n">
+        <v>19.75312333002663</v>
+      </c>
+      <c r="K9" t="n">
+        <v>84.89718462789831</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 11.199x + -38188.370</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.833478426214852e-10</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>4018.348495702831</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8235963307813028</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-314.9200000000001</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.94419e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-57.839</v>
+      </c>
+      <c r="F10" t="n">
+        <v/>
+      </c>
+      <c r="G10" t="n">
+        <v/>
+      </c>
+      <c r="H10" t="n">
+        <v/>
+      </c>
+      <c r="I10" t="n">
+        <v/>
+      </c>
+      <c r="J10" t="n">
+        <v>20.23921765001974</v>
+      </c>
+      <c r="K10" t="n">
+        <v>85.00845129189244</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 11.450x + -38699.499</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>9.68213434659183e-10</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3979.448659800326</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000000085e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8238883918918056</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-302.71</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.95185e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-58.029</v>
+      </c>
+      <c r="F11" t="n">
+        <v/>
+      </c>
+      <c r="G11" t="n">
+        <v/>
+      </c>
+      <c r="H11" t="n">
+        <v/>
+      </c>
+      <c r="I11" t="n">
+        <v/>
+      </c>
+      <c r="J11" t="n">
+        <v>29.28320957413159</v>
+      </c>
+      <c r="K11" t="n">
+        <v>85.47555092902752</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 12.637x + -42607.690</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>4.606741513217921e-09</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3942.416923180658</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000000684e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8241811748189249</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-309.5599999999999</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.96328e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-58.294</v>
+      </c>
+      <c r="F12" t="n">
+        <v/>
+      </c>
+      <c r="G12" t="n">
+        <v/>
+      </c>
+      <c r="H12" t="n">
+        <v/>
+      </c>
+      <c r="I12" t="n">
+        <v/>
+      </c>
+      <c r="J12" t="n">
+        <v>20.69798394253188</v>
+      </c>
+      <c r="K12" t="n">
+        <v>85.09978255247546</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 11.664x + -38767.251</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.178383808251198e-09</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3906.229744126156</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.000000000000049e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8244730081132101</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-303.48</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.97459e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-58.518</v>
+      </c>
+      <c r="F13" t="n">
+        <v/>
+      </c>
+      <c r="G13" t="n">
+        <v/>
+      </c>
+      <c r="H13" t="n">
+        <v/>
+      </c>
+      <c r="I13" t="n">
+        <v/>
+      </c>
+      <c r="J13" t="n">
+        <v>20.44363364977901</v>
+      </c>
+      <c r="K13" t="n">
+        <v>85.12143442605102</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 11.716x + -38598.697</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>5.377195440529159e-10</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3871.158020146187</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.000000000001256e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8247859425800291</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-305.6400000000003</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.98418e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-58.675</v>
+      </c>
+      <c r="F14" t="n">
+        <v/>
+      </c>
+      <c r="G14" t="n">
+        <v/>
+      </c>
+      <c r="H14" t="n">
+        <v/>
+      </c>
+      <c r="I14" t="n">
+        <v/>
+      </c>
+      <c r="J14" t="n">
+        <v>20.91473956733673</v>
+      </c>
+      <c r="K14" t="n">
+        <v>85.15949670657041</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 11.809x + -38582.039</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>3.169718704593535e-10</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3835.989998949466</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.000000000017186e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8250937400237481</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-288.9499999999998</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.99657e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-59.004</v>
+      </c>
+      <c r="F15" t="n">
+        <v/>
+      </c>
+      <c r="G15" t="n">
+        <v/>
+      </c>
+      <c r="H15" t="n">
+        <v/>
+      </c>
+      <c r="I15" t="n">
+        <v/>
+      </c>
+      <c r="J15" t="n">
+        <v>20.69973389341415</v>
+      </c>
+      <c r="K15" t="n">
+        <v>85.1690390181186</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 11.832x + -38317.353</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>5.163221658958326e-11</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3801.152867077442</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.000000000000045e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.8254030500798827</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-279.8800000000001</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2.00639e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-59.255</v>
+      </c>
+      <c r="F16" t="n">
+        <v/>
+      </c>
+      <c r="G16" t="n">
+        <v/>
+      </c>
+      <c r="H16" t="n">
+        <v/>
+      </c>
+      <c r="I16" t="n">
+        <v/>
+      </c>
+      <c r="J16" t="n">
+        <v>21.72126623231179</v>
+      </c>
+      <c r="K16" t="n">
+        <v>85.25589780456357</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 12.050x + -38702.062</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>4.324637531563735e-12</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3765.866408940889</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.000000000000082e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8257383323812864</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-279.0299999999997</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2.01543e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-59.463</v>
+      </c>
+      <c r="F17" t="n">
+        <v/>
+      </c>
+      <c r="G17" t="n">
+        <v/>
+      </c>
+      <c r="H17" t="n">
+        <v/>
+      </c>
+      <c r="I17" t="n">
+        <v/>
+      </c>
+      <c r="J17" t="n">
+        <v>21.40406497986767</v>
+      </c>
+      <c r="K17" t="n">
+        <v>85.23136093573883</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 11.987x + -38150.214</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.985192077426656e-08</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3730.377770053432</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.00000000000952e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8260751871953071</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-275.1999999999998</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.02526e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-59.671</v>
+      </c>
+      <c r="F18" t="n">
+        <v/>
+      </c>
+      <c r="G18" t="n">
+        <v/>
+      </c>
+      <c r="H18" t="n">
+        <v/>
+      </c>
+      <c r="I18" t="n">
+        <v/>
+      </c>
+      <c r="J18" t="n">
+        <v>21.83968277333267</v>
+      </c>
+      <c r="K18" t="n">
+        <v>85.34760129178245</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 12.288x + -38798.014</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>2.0944098674368e-14</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3696.0770156904</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8264155032351327</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-265.9000000000001</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.03566e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-59.987</v>
+      </c>
+      <c r="F19" t="n">
+        <v/>
+      </c>
+      <c r="G19" t="n">
+        <v/>
+      </c>
+      <c r="H19" t="n">
+        <v/>
+      </c>
+      <c r="I19" t="n">
+        <v/>
+      </c>
+      <c r="J19" t="n">
+        <v>21.77438829892117</v>
+      </c>
+      <c r="K19" t="n">
+        <v>85.34220099001631</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 12.274x + -38375.936</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>4.382033804628565e-11</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3659.739763347086</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.00000000000003e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8267777614370228</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-263.2999999999997</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.04622e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-60.198</v>
+      </c>
+      <c r="F20" t="n">
+        <v/>
+      </c>
+      <c r="G20" t="n">
+        <v/>
+      </c>
+      <c r="H20" t="n">
+        <v/>
+      </c>
+      <c r="I20" t="n">
+        <v/>
+      </c>
+      <c r="J20" t="n">
+        <v>22.08652828488558</v>
+      </c>
+      <c r="K20" t="n">
+        <v>85.37319319370786</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 12.357x + -38286.030</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.270549332805959e-09</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3623.718649918355</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.000000000001719e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8271197259094545</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-252.2999999999997</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.05677e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-60.465</v>
+      </c>
+      <c r="F21" t="n">
+        <v/>
+      </c>
+      <c r="G21" t="n">
+        <v/>
+      </c>
+      <c r="H21" t="n">
+        <v/>
+      </c>
+      <c r="I21" t="n">
+        <v/>
+      </c>
+      <c r="J21" t="n">
+        <v>21.43709212669081</v>
+      </c>
+      <c r="K21" t="n">
+        <v>85.36996510611868</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 12.348x + -37899.951</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>9.953075358001483e-09</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3589.402565469917</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.000000000000005e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8274657541930236</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-260.4300000000003</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.06834e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-60.747</v>
+      </c>
+      <c r="F22" t="n">
+        <v/>
+      </c>
+      <c r="G22" t="n">
+        <v/>
+      </c>
+      <c r="H22" t="n">
+        <v/>
+      </c>
+      <c r="I22" t="n">
+        <v/>
+      </c>
+      <c r="J22" t="n">
+        <v>17.62197387619561</v>
+      </c>
+      <c r="K22" t="n">
+        <v>84.9717545413131</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 11.366x + -34370.340</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.31220898286965e-10</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3554.157447565878</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.000000000000035e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8278074676341429</v>
       </c>
     </row>
   </sheetData>
@@ -1754,7 +7664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1858,8 +7768,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1889,6 +7797,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-552.7600000000002</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.8699e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-54.409</v>
+      </c>
+      <c r="F2" t="n">
+        <v/>
+      </c>
+      <c r="G2" t="n">
+        <v/>
+      </c>
+      <c r="H2" t="n">
+        <v/>
+      </c>
+      <c r="I2" t="n">
+        <v/>
+      </c>
+      <c r="J2" t="n">
+        <v>13.6552797202362</v>
+      </c>
+      <c r="K2" t="n">
+        <v>83.3873129477326</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 8.626x + -30076.130</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.548767816972464e-08</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3931.3295098559</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.00000000000951e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8238844464864344</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-352.4099999999999</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.14406e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-60.051</v>
+      </c>
+      <c r="F3" t="n">
+        <v/>
+      </c>
+      <c r="G3" t="n">
+        <v/>
+      </c>
+      <c r="H3" t="n">
+        <v/>
+      </c>
+      <c r="I3" t="n">
+        <v/>
+      </c>
+      <c r="J3" t="n">
+        <v>16.1881635143584</v>
+      </c>
+      <c r="K3" t="n">
+        <v>84.69149544565077</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 10.762x + -30940.692</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.064013584503895e-11</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3330.341443771282</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000000087e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8255413140805614</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-283.5999999999999</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.19537e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-61.536</v>
+      </c>
+      <c r="F4" t="n">
+        <v/>
+      </c>
+      <c r="G4" t="n">
+        <v/>
+      </c>
+      <c r="H4" t="n">
+        <v/>
+      </c>
+      <c r="I4" t="n">
+        <v/>
+      </c>
+      <c r="J4" t="n">
+        <v>22.23690670306605</v>
+      </c>
+      <c r="K4" t="n">
+        <v>85.48198616993866</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 12.655x + -35044.184</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.600304056244478e-11</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3198.773498650586</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000259e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.825821287506694</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-266.4499999999998</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.21631e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-62.294</v>
+      </c>
+      <c r="F5" t="n">
+        <v/>
+      </c>
+      <c r="G5" t="n">
+        <v/>
+      </c>
+      <c r="H5" t="n">
+        <v/>
+      </c>
+      <c r="I5" t="n">
+        <v/>
+      </c>
+      <c r="J5" t="n">
+        <v>18.76464725971489</v>
+      </c>
+      <c r="K5" t="n">
+        <v>85.22762894081315</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 11.978x + -32359.745</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.624150959028984e-12</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3137.91765451105</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000114e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8259357421686137</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-254.9200000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.22776e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-62.742</v>
+      </c>
+      <c r="F6" t="n">
+        <v/>
+      </c>
+      <c r="G6" t="n">
+        <v/>
+      </c>
+      <c r="H6" t="n">
+        <v/>
+      </c>
+      <c r="I6" t="n">
+        <v/>
+      </c>
+      <c r="J6" t="n">
+        <v>19.19121751683202</v>
+      </c>
+      <c r="K6" t="n">
+        <v>85.30778033946123</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 12.183x + -32436.802</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>6.237155215073255e-14</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3090.404222545536</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8261010053753834</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-259.3099999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.23876e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-63.159</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.07973219720024473</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.5530033370411465</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.603931490852451</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.929735276010641</v>
+      </c>
+      <c r="J7" t="n">
+        <v>626.1497252746317</v>
+      </c>
+      <c r="K7" t="n">
+        <v>85.01786830514428</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 11.471x + -29990.228</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.873052751754583e-08</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3045.549785816086</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8263297711641212</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-240.0099999999998</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.25157e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-63.514</v>
+      </c>
+      <c r="F8" t="n">
+        <v/>
+      </c>
+      <c r="G8" t="n">
+        <v/>
+      </c>
+      <c r="H8" t="n">
+        <v/>
+      </c>
+      <c r="I8" t="n">
+        <v/>
+      </c>
+      <c r="J8" t="n">
+        <v>19.49676036367591</v>
+      </c>
+      <c r="K8" t="n">
+        <v>85.40923540709269</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 12.454x + -32245.915</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>4.072263196839266e-11</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3000.177687131686</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.82661497162223</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-231.9200000000001</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.26419e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-63.874</v>
+      </c>
+      <c r="F9" t="n">
+        <v/>
+      </c>
+      <c r="G9" t="n">
+        <v/>
+      </c>
+      <c r="H9" t="n">
+        <v/>
+      </c>
+      <c r="I9" t="n">
+        <v/>
+      </c>
+      <c r="J9" t="n">
+        <v>19.71381537669367</v>
+      </c>
+      <c r="K9" t="n">
+        <v>85.46060189716655</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 12.595x + -32172.309</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.575618300636622e-12</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2955.778520537724</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8269476360445552</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-227.3999999999996</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.27576e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-64.238</v>
+      </c>
+      <c r="F10" t="n">
+        <v/>
+      </c>
+      <c r="G10" t="n">
+        <v/>
+      </c>
+      <c r="H10" t="n">
+        <v/>
+      </c>
+      <c r="I10" t="n">
+        <v/>
+      </c>
+      <c r="J10" t="n">
+        <v>19.39414225518023</v>
+      </c>
+      <c r="K10" t="n">
+        <v>85.45998958481565</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 12.594x + -31717.814</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>4.067180711400814e-10</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2913.40211426387</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000000055e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8272829612088458</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-229.7799999999997</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.28915e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-64.54600000000001</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.2379283489096615</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.7175218340611333</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.707711238720298</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.966200657894796</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>85.17558684606576</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 11.848x + -29321.329</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>9.396591062440979e-10</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2873.572204780687</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000000047e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8276196827158498</v>
       </c>
     </row>
   </sheetData>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 22.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 22.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,12 +528,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -555,6 +555,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-483.7100000000005</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.71082e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-50.662</v>
+      </c>
+      <c r="F2" t="n">
+        <v/>
+      </c>
+      <c r="G2" t="n">
+        <v/>
+      </c>
+      <c r="H2" t="n">
+        <v/>
+      </c>
+      <c r="I2" t="n">
+        <v/>
+      </c>
+      <c r="J2" t="n">
+        <v>21.23081067842276</v>
+      </c>
+      <c r="K2" t="n">
+        <v>84.00972660163535</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>y = 9.530x + -38869.911</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-38869.91105651398</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>788.250215773583</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>483.7100000000005</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>5.776946517833533e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.7372642907052039</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-449.0000000000005</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.73367e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-51.646</v>
+      </c>
+      <c r="F3" t="n">
+        <v/>
+      </c>
+      <c r="G3" t="n">
+        <v/>
+      </c>
+      <c r="H3" t="n">
+        <v/>
+      </c>
+      <c r="I3" t="n">
+        <v/>
+      </c>
+      <c r="J3" t="n">
+        <v>25.71406923883884</v>
+      </c>
+      <c r="K3" t="n">
+        <v>84.38358080225115</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>y = 10.169x + -40922.630</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-40922.63006373644</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.375691008376404e-10</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>449.0000000000005</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.000000000000007e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8240596711769386</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-422.46</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.75642e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-52.397</v>
+      </c>
+      <c r="F4" t="n">
+        <v/>
+      </c>
+      <c r="G4" t="n">
+        <v/>
+      </c>
+      <c r="H4" t="n">
+        <v/>
+      </c>
+      <c r="I4" t="n">
+        <v/>
+      </c>
+      <c r="J4" t="n">
+        <v>28.97652032520341</v>
+      </c>
+      <c r="K4" t="n">
+        <v>84.69632213072371</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>y = 10.772x + -42718.906</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-42718.90590584213</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.036172081155364e-09</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>422.46</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.00000000000816e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.824279506760352</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-429.4099999999999</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.78341e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-53.151</v>
+      </c>
+      <c r="F5" t="n">
+        <v/>
+      </c>
+      <c r="G5" t="n">
+        <v/>
+      </c>
+      <c r="H5" t="n">
+        <v/>
+      </c>
+      <c r="I5" t="n">
+        <v/>
+      </c>
+      <c r="J5" t="n">
+        <v>19.44618721315653</v>
+      </c>
+      <c r="K5" t="n">
+        <v>84.33112037698744</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>y = 10.074x + -38923.463</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-38923.4625149877</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.463323541956249e-10</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>429.4099999999999</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000084e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8247593015898517</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-377.4799999999996</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.81055e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-53.877</v>
+      </c>
+      <c r="F6" t="n">
+        <v/>
+      </c>
+      <c r="G6" t="n">
+        <v/>
+      </c>
+      <c r="H6" t="n">
+        <v/>
+      </c>
+      <c r="I6" t="n">
+        <v/>
+      </c>
+      <c r="J6" t="n">
+        <v>37.43026533996655</v>
+      </c>
+      <c r="K6" t="n">
+        <v>85.13828801524639</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>y = 11.757x + -44884.110</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-44884.11049018749</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.96279307198882e-12</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>377.4799999999996</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8253411027794955</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-390.5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.83885e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-54.565</v>
+      </c>
+      <c r="F7" t="n">
+        <v/>
+      </c>
+      <c r="G7" t="n">
+        <v/>
+      </c>
+      <c r="H7" t="n">
+        <v/>
+      </c>
+      <c r="I7" t="n">
+        <v/>
+      </c>
+      <c r="J7" t="n">
+        <v>21.75365507890085</v>
+      </c>
+      <c r="K7" t="n">
+        <v>84.71587544916852</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>y = 10.812x + -40093.917</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-40093.91730232955</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>6.876750246228913e-09</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>390.5</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000004574e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8259618857344994</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-361.0999999999999</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.86813e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-55.322</v>
+      </c>
+      <c r="F8" t="n">
+        <v/>
+      </c>
+      <c r="G8" t="n">
+        <v/>
+      </c>
+      <c r="H8" t="n">
+        <v/>
+      </c>
+      <c r="I8" t="n">
+        <v/>
+      </c>
+      <c r="J8" t="n">
+        <v>23.79492806229553</v>
+      </c>
+      <c r="K8" t="n">
+        <v>84.90898905485649</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>y = 11.225x + -40789.461</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-40789.46133594657</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>6.302249062980872e-10</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>361.0999999999999</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.000000000000216e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8265813078440759</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-355.0099999999998</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.89274e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-55.928</v>
+      </c>
+      <c r="F9" t="n">
+        <v/>
+      </c>
+      <c r="G9" t="n">
+        <v/>
+      </c>
+      <c r="H9" t="n">
+        <v/>
+      </c>
+      <c r="I9" t="n">
+        <v/>
+      </c>
+      <c r="J9" t="n">
+        <v>24.3529815181112</v>
+      </c>
+      <c r="K9" t="n">
+        <v>84.98913506843884</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>y = 11.405x + -40564.558</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-40564.55818076397</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.111873164219927e-08</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>355.0099999999998</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000001537e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8271987757778315</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-333.2200000000003</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.91901e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-56.604</v>
+      </c>
+      <c r="F10" t="n">
+        <v/>
+      </c>
+      <c r="G10" t="n">
+        <v/>
+      </c>
+      <c r="H10" t="n">
+        <v/>
+      </c>
+      <c r="I10" t="n">
+        <v/>
+      </c>
+      <c r="J10" t="n">
+        <v>25.59849405735725</v>
+      </c>
+      <c r="K10" t="n">
+        <v>85.17432897518572</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>y = 11.845x + -41298.626</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-41298.62569820891</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.08708518102713e-08</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>333.2200000000003</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000018961e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8278455982779082</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-340.9900000000002</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.94336e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-57.197</v>
+      </c>
+      <c r="F11" t="n">
+        <v/>
+      </c>
+      <c r="G11" t="n">
+        <v/>
+      </c>
+      <c r="H11" t="n">
+        <v/>
+      </c>
+      <c r="I11" t="n">
+        <v/>
+      </c>
+      <c r="J11" t="n">
+        <v>19.52106639683354</v>
+      </c>
+      <c r="K11" t="n">
+        <v>84.7806312433331</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>y = 10.947x + -37209.952</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-37209.95171431376</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>3.311748625133803e-09</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>340.9900000000002</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000003197e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8284796375504466</v>
       </c>
     </row>
   </sheetData>
@@ -674,12 +1194,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -689,7 +1209,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -734,19 +1254,19 @@
       <c r="K2" t="n">
         <v>84.31863390628567</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 10.052x + -39534.145</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-39534.14506715898</v>
       </c>
       <c r="Y2" t="n">
         <v>1.244253294594379e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>4625.580325676739</v>
+        <v>409.4700000000003</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000961e-08</v>
@@ -786,19 +1306,19 @@
       <c r="K3" t="n">
         <v>84.70692971997173</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 10.794x + -40617.942</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-40617.94172694472</v>
       </c>
       <c r="Y3" t="n">
         <v>7.377204449657842e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>4433.80859511773</v>
+        <v>360.3799999999997</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000001458e-08</v>
@@ -838,19 +1358,19 @@
       <c r="K4" t="n">
         <v>84.92317105169997</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 11.256x + -41596.090</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-41596.08989601236</v>
       </c>
       <c r="Y4" t="n">
         <v>1.252944243450047e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>4350.238132513493</v>
+        <v>335.9900000000002</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000144e-08</v>
@@ -890,19 +1410,19 @@
       <c r="K5" t="n">
         <v>84.37965575076632</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 10.162x + -36761.966</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-36761.96567934959</v>
       </c>
       <c r="Y5" t="n">
         <v>2.306075202763503e-10</v>
       </c>
       <c r="Z5" t="n">
-        <v>4286.768509053111</v>
+        <v>345.1599999999999</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000012766e-08</v>
@@ -942,19 +1462,19 @@
       <c r="K6" t="n">
         <v>85.04642743210843</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 11.538x + -41540.417</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-41540.41709532502</v>
       </c>
       <c r="Y6" t="n">
         <v>7.584899300526974e-11</v>
       </c>
       <c r="Z6" t="n">
-        <v>4235.722519837079</v>
+        <v>313.6300000000001</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000001277e-08</v>
@@ -994,19 +1514,19 @@
       <c r="K7" t="n">
         <v>85.06202487131932</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 11.574x + -41222.579</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-41222.57852142974</v>
       </c>
       <c r="Y7" t="n">
         <v>5.117943078847159e-10</v>
       </c>
       <c r="Z7" t="n">
-        <v>4188.927113410116</v>
+        <v>297.6399999999999</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000007216e-08</v>
@@ -1046,19 +1566,19 @@
       <c r="K8" t="n">
         <v>85.06432684311901</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 11.580x + -40809.447</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-40809.44726858166</v>
       </c>
       <c r="Y8" t="n">
         <v>8.618493665111624e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>4144.905958139941</v>
+        <v>290.73</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000082e-08</v>
@@ -1098,19 +1618,19 @@
       <c r="K9" t="n">
         <v>84.70764319241597</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 10.795x + -37476.775</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-37476.77544811717</v>
       </c>
       <c r="Y9" t="n">
         <v>3.55756940921727e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>4099.248886566271</v>
+        <v>303.5900000000001</v>
       </c>
       <c r="AA9" t="n">
         <v>1.00000000001205e-08</v>
@@ -1150,19 +1670,19 @@
       <c r="K10" t="n">
         <v>85.19662133565703</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 11.900x + -41104.675</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-41104.67547778001</v>
       </c>
       <c r="Y10" t="n">
         <v>1.916430614249844e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>4053.947623021833</v>
+        <v>273.7900000000004</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000001917e-08</v>
@@ -1202,19 +1722,19 @@
       <c r="K11" t="n">
         <v>85.24536893564016</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 12.023x + -41096.082</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-41096.08193323449</v>
       </c>
       <c r="Y11" t="n">
         <v>6.032241603430068e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>4008.970006005633</v>
+        <v>269.8900000000003</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000006e-08</v>
@@ -1254,19 +1774,19 @@
       <c r="K12" t="n">
         <v>84.74109904396667</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 10.864x + -36516.366</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-36516.36614768529</v>
       </c>
       <c r="Y12" t="n">
         <v>5.039679267589776e-09</v>
       </c>
       <c r="Z12" t="n">
-        <v>3964.680842632226</v>
+        <v>281.27</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000000819e-08</v>
@@ -1306,19 +1826,19 @@
       <c r="K13" t="n">
         <v>85.21576715652263</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 11.948x + -39970.979</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-39970.97906726342</v>
       </c>
       <c r="Y13" t="n">
         <v>2.247265051907677e-10</v>
       </c>
       <c r="Z13" t="n">
-        <v>3921.678424993902</v>
+        <v>256.7999999999997</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000091e-08</v>
@@ -1358,19 +1878,19 @@
       <c r="K14" t="n">
         <v>85.33063676030532</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 12.243x + -40569.323</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-40569.3225769932</v>
       </c>
       <c r="Y14" t="n">
         <v>4.275191088860601e-14</v>
       </c>
       <c r="Z14" t="n">
-        <v>3877.756669921092</v>
+        <v>248.1199999999999</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000015e-08</v>
@@ -1410,19 +1930,19 @@
       <c r="K15" t="n">
         <v>84.81090471609446</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 11.011x + -35870.756</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-35870.75606967674</v>
       </c>
       <c r="Y15" t="n">
         <v>1.899316326970643e-09</v>
       </c>
       <c r="Z15" t="n">
-        <v>3834.879772348723</v>
+        <v>268.23</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000000042e-08</v>
@@ -1462,19 +1982,19 @@
       <c r="K16" t="n">
         <v>84.35721180595374</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 10.121x + -32450.866</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-32450.8659486324</v>
       </c>
       <c r="Y16" t="n">
         <v>6.575769629793456e-10</v>
       </c>
       <c r="Z16" t="n">
-        <v>3793.124220174062</v>
+        <v>283.1800000000003</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000565e-08</v>
@@ -1514,19 +2034,19 @@
       <c r="K17" t="n">
         <v>85.2385804050656</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 12.006x + -38472.166</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-38472.16568915868</v>
       </c>
       <c r="Y17" t="n">
         <v>3.19493814588955e-09</v>
       </c>
       <c r="Z17" t="n">
-        <v>3750.503077605235</v>
+        <v>246.46</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000007e-08</v>
@@ -1566,19 +2086,19 @@
       <c r="K18" t="n">
         <v>84.82500463227315</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 11.042x + -34815.307</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-34815.30717000522</v>
       </c>
       <c r="Y18" t="n">
         <v>3.582871598968226e-10</v>
       </c>
       <c r="Z18" t="n">
-        <v>3707.690031135591</v>
+        <v>260.3200000000002</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000000023e-08</v>
@@ -1618,19 +2138,19 @@
       <c r="K19" t="n">
         <v>84.7160048371845</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 10.813x + -33694.900</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-33694.90035323985</v>
       </c>
       <c r="Y19" t="n">
         <v>7.408941785946461e-11</v>
       </c>
       <c r="Z19" t="n">
-        <v>3666.209999928599</v>
+        <v>261.0700000000002</v>
       </c>
       <c r="AA19" t="n">
         <v>1.00000000000037e-08</v>
@@ -1670,19 +2190,19 @@
       <c r="K20" t="n">
         <v>84.80918195253294</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 11.008x + -33980.125</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-33980.12533270143</v>
       </c>
       <c r="Y20" t="n">
         <v>1.435818496161628e-10</v>
       </c>
       <c r="Z20" t="n">
-        <v>3626.471516064093</v>
+        <v>257.6099999999997</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000036e-08</v>
@@ -1722,19 +2242,19 @@
       <c r="K21" t="n">
         <v>84.71265372220327</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 10.806x + -32959.184</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-32959.18410124019</v>
       </c>
       <c r="Y21" t="n">
         <v>7.518278689948309e-10</v>
       </c>
       <c r="Z21" t="n">
-        <v>3584.932522063923</v>
+        <v>253.02</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000001987e-08</v>
@@ -1774,19 +2294,19 @@
       <c r="K22" t="n">
         <v>84.6746959006757</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 10.728x + -32345.466</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-32345.46584861688</v>
       </c>
       <c r="Y22" t="n">
         <v>5.277796362196904e-09</v>
       </c>
       <c r="Z22" t="n">
-        <v>3543.812075902712</v>
+        <v>253.75</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000289e-08</v>
@@ -1806,7 +2326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1912,12 +2432,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1927,7 +2447,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -1939,6 +2459,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-496.1800000000003</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.72399e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-52.089</v>
+      </c>
+      <c r="F2" t="n">
+        <v/>
+      </c>
+      <c r="G2" t="n">
+        <v/>
+      </c>
+      <c r="H2" t="n">
+        <v/>
+      </c>
+      <c r="I2" t="n">
+        <v/>
+      </c>
+      <c r="J2" t="n">
+        <v>16.3192435020351</v>
+      </c>
+      <c r="K2" t="n">
+        <v>83.72154142991856</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>y = 9.089x + -36235.159</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-36235.15867410284</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>3.370441551673691e-10</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>496.1800000000003</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.000000000000001e-08</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8233695744745619</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-425.27</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.79549e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-53.654</v>
+      </c>
+      <c r="F3" t="n">
+        <v/>
+      </c>
+      <c r="G3" t="n">
+        <v/>
+      </c>
+      <c r="H3" t="n">
+        <v/>
+      </c>
+      <c r="I3" t="n">
+        <v/>
+      </c>
+      <c r="J3" t="n">
+        <v>19.56638938157581</v>
+      </c>
+      <c r="K3" t="n">
+        <v>84.38598410297396</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>y = 10.173x + -38815.233</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-38815.23297486068</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>4.326280667072054e-09</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>425.27</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.00000000000053e-08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8237229251270486</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-395.9499999999998</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.82536e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-54.376</v>
+      </c>
+      <c r="F4" t="n">
+        <v/>
+      </c>
+      <c r="G4" t="n">
+        <v/>
+      </c>
+      <c r="H4" t="n">
+        <v/>
+      </c>
+      <c r="I4" t="n">
+        <v/>
+      </c>
+      <c r="J4" t="n">
+        <v>21.98710571970422</v>
+      </c>
+      <c r="K4" t="n">
+        <v>84.60231401110784</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>y = 10.583x + -39633.702</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-39633.70168602013</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.456479343354473e-08</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>395.9499999999998</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.000000000000297e-08</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8238219038723564</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-386.8200000000002</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.8412e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-54.786</v>
+      </c>
+      <c r="F5" t="n">
+        <v/>
+      </c>
+      <c r="G5" t="n">
+        <v/>
+      </c>
+      <c r="H5" t="n">
+        <v/>
+      </c>
+      <c r="I5" t="n">
+        <v/>
+      </c>
+      <c r="J5" t="n">
+        <v>22.41186192344545</v>
+      </c>
+      <c r="K5" t="n">
+        <v>84.74167270718836</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>y = 10.866x + -40164.323</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-40164.32289764511</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>2.021853569404719e-08</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>386.8200000000002</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.000000000000305e-08</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.823899961307078</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-361.3499999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.86066e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-55.223</v>
+      </c>
+      <c r="F6" t="n">
+        <v/>
+      </c>
+      <c r="G6" t="n">
+        <v/>
+      </c>
+      <c r="H6" t="n">
+        <v/>
+      </c>
+      <c r="I6" t="n">
+        <v/>
+      </c>
+      <c r="J6" t="n">
+        <v>23.50993891044167</v>
+      </c>
+      <c r="K6" t="n">
+        <v>84.91731698274958</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>y = 11.243x + -41086.843</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-41086.84302222927</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>7.963394350270732e-09</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>361.3499999999999</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.000000000000182e-08</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8240713645438792</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-353.3299999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.87424e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-55.659</v>
+      </c>
+      <c r="F7" t="n">
+        <v/>
+      </c>
+      <c r="G7" t="n">
+        <v/>
+      </c>
+      <c r="H7" t="n">
+        <v/>
+      </c>
+      <c r="I7" t="n">
+        <v/>
+      </c>
+      <c r="J7" t="n">
+        <v>24.84336257640265</v>
+      </c>
+      <c r="K7" t="n">
+        <v>84.95317909915963</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>y = 11.323x + -40906.778</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-40906.77792795659</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.086095934796582e-09</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>353.3299999999999</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.000000000000184e-08</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8243026155147587</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-348.3800000000001</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.88632e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-56.009</v>
+      </c>
+      <c r="F8" t="n">
+        <v/>
+      </c>
+      <c r="G8" t="n">
+        <v/>
+      </c>
+      <c r="H8" t="n">
+        <v/>
+      </c>
+      <c r="I8" t="n">
+        <v/>
+      </c>
+      <c r="J8" t="n">
+        <v>25.29286219318779</v>
+      </c>
+      <c r="K8" t="n">
+        <v>85.03215631551546</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>y = 11.504x + -41112.094</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-41112.09358396035</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>5.001618958464682e-09</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>348.3800000000001</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.00000000000034e-08</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8246081757614356</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-338.5599999999999</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.90074e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-56.323</v>
+      </c>
+      <c r="F9" t="n">
+        <v/>
+      </c>
+      <c r="G9" t="n">
+        <v/>
+      </c>
+      <c r="H9" t="n">
+        <v/>
+      </c>
+      <c r="I9" t="n">
+        <v/>
+      </c>
+      <c r="J9" t="n">
+        <v>25.80279666689886</v>
+      </c>
+      <c r="K9" t="n">
+        <v>85.05382371749656</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>y = 11.555x + -40843.306</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-40843.30632908228</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>4.828934291583226e-09</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>338.5599999999999</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.000000000000324e-08</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8249324201468028</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-336.5999999999999</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.91118e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-56.663</v>
+      </c>
+      <c r="F10" t="n">
+        <v/>
+      </c>
+      <c r="G10" t="n">
+        <v/>
+      </c>
+      <c r="H10" t="n">
+        <v/>
+      </c>
+      <c r="I10" t="n">
+        <v/>
+      </c>
+      <c r="J10" t="n">
+        <v>26.74685142827596</v>
+      </c>
+      <c r="K10" t="n">
+        <v>85.12931880014725</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>y = 11.735x + -41044.520</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-41044.51981480025</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>3.642114611136962e-09</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>336.5999999999999</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.000000000000343e-08</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.8252927739600296</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-320.25</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.92627e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-57.043</v>
+      </c>
+      <c r="F11" t="n">
+        <v/>
+      </c>
+      <c r="G11" t="n">
+        <v/>
+      </c>
+      <c r="H11" t="n">
+        <v/>
+      </c>
+      <c r="I11" t="n">
+        <v/>
+      </c>
+      <c r="J11" t="n">
+        <v>27.03177272917698</v>
+      </c>
+      <c r="K11" t="n">
+        <v>85.19305089951024</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>y = 11.891x + -41148.007</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-41148.00692236799</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>6.102817101340699e-10</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>320.25</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.000000000003967e-08</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.8256566511396339</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-341.8000000000002</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.93583e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-57.361</v>
+      </c>
+      <c r="F12" t="n">
+        <v/>
+      </c>
+      <c r="G12" t="n">
+        <v/>
+      </c>
+      <c r="H12" t="n">
+        <v/>
+      </c>
+      <c r="I12" t="n">
+        <v/>
+      </c>
+      <c r="J12" t="n">
+        <v>19.51781537820423</v>
+      </c>
+      <c r="K12" t="n">
+        <v>84.77480757353189</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>y = 10.935x + -37217.957</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-37217.95747578702</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>2.839090205752015e-08</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>341.8000000000002</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.000000000000054e-08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.8260697927830143</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-322.6900000000001</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.94953e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-57.729</v>
+      </c>
+      <c r="F13" t="n">
+        <v/>
+      </c>
+      <c r="G13" t="n">
+        <v/>
+      </c>
+      <c r="H13" t="n">
+        <v/>
+      </c>
+      <c r="I13" t="n">
+        <v/>
+      </c>
+      <c r="J13" t="n">
+        <v>19.96205683460482</v>
+      </c>
+      <c r="K13" t="n">
+        <v>84.91415073579513</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>y = 11.236x + -37867.554</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-37867.55414078048</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>9.05080574630993e-09</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>322.6900000000001</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.000000000000142e-08</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.8264726393485065</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-320.6099999999997</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.96063e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-58.034</v>
+      </c>
+      <c r="F14" t="n">
+        <v/>
+      </c>
+      <c r="G14" t="n">
+        <v/>
+      </c>
+      <c r="H14" t="n">
+        <v/>
+      </c>
+      <c r="I14" t="n">
+        <v/>
+      </c>
+      <c r="J14" t="n">
+        <v>20.27987189891192</v>
+      </c>
+      <c r="K14" t="n">
+        <v>84.90803050963144</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>y = 11.223x + -37413.048</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-37413.04763397378</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>7.782032172183475e-10</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>320.6099999999997</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.000000000020272e-08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.8268555981197554</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-309.96</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.9725e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-58.369</v>
+      </c>
+      <c r="F15" t="n">
+        <v/>
+      </c>
+      <c r="G15" t="n">
+        <v/>
+      </c>
+      <c r="H15" t="n">
+        <v/>
+      </c>
+      <c r="I15" t="n">
+        <v/>
+      </c>
+      <c r="J15" t="n">
+        <v>20.40660015110164</v>
+      </c>
+      <c r="K15" t="n">
+        <v>84.97187181591673</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>y = 11.366x + -37504.011</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-37504.01101230338</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>8.556457137991386e-10</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>309.96</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.000000000000318e-08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.827276243333097</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-311.2799999999997</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.9827e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-58.617</v>
+      </c>
+      <c r="F16" t="n">
+        <v/>
+      </c>
+      <c r="G16" t="n">
+        <v/>
+      </c>
+      <c r="H16" t="n">
+        <v/>
+      </c>
+      <c r="I16" t="n">
+        <v/>
+      </c>
+      <c r="J16" t="n">
+        <v>20.56625733558626</v>
+      </c>
+      <c r="K16" t="n">
+        <v>85.02533131411187</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>y = 11.489x + -37528.922</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-37528.9224004475</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.323400534726482e-09</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>311.2799999999997</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.000000000000302e-08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.8276832922759507</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-296.6699999999996</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.99642e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-58.992</v>
+      </c>
+      <c r="F17" t="n">
+        <v/>
+      </c>
+      <c r="G17" t="n">
+        <v/>
+      </c>
+      <c r="H17" t="n">
+        <v/>
+      </c>
+      <c r="I17" t="n">
+        <v/>
+      </c>
+      <c r="J17" t="n">
+        <v>20.92645479702185</v>
+      </c>
+      <c r="K17" t="n">
+        <v>85.04224778047599</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>y = 11.528x + -37242.389</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-37242.38901594248</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2.272349103142619e-08</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>296.6699999999996</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.000000000006625e-08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8280989444214035</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-295.4400000000001</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.00614e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-59.251</v>
+      </c>
+      <c r="F18" t="n">
+        <v/>
+      </c>
+      <c r="G18" t="n">
+        <v/>
+      </c>
+      <c r="H18" t="n">
+        <v/>
+      </c>
+      <c r="I18" t="n">
+        <v/>
+      </c>
+      <c r="J18" t="n">
+        <v>20.93295799701737</v>
+      </c>
+      <c r="K18" t="n">
+        <v>85.12278138397797</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>y = 11.719x + -37505.718</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-37505.71823373426</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.961663329049757e-10</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>295.4400000000001</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.000000000000267e-08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8284828717544276</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-281.9299999999998</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2.01951e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-59.573</v>
+      </c>
+      <c r="F19" t="n">
+        <v/>
+      </c>
+      <c r="G19" t="n">
+        <v/>
+      </c>
+      <c r="H19" t="n">
+        <v/>
+      </c>
+      <c r="I19" t="n">
+        <v/>
+      </c>
+      <c r="J19" t="n">
+        <v>20.96851813911583</v>
+      </c>
+      <c r="K19" t="n">
+        <v>85.09290417806083</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>y = 11.648x + -36863.706</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-36863.70579542115</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>7.567410631462515e-09</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>281.9299999999998</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.000000000014656e-08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8289049433645949</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-276.9900000000002</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2.02908e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-59.879</v>
+      </c>
+      <c r="F20" t="n">
+        <v/>
+      </c>
+      <c r="G20" t="n">
+        <v/>
+      </c>
+      <c r="H20" t="n">
+        <v/>
+      </c>
+      <c r="I20" t="n">
+        <v/>
+      </c>
+      <c r="J20" t="n">
+        <v>21.17139303834685</v>
+      </c>
+      <c r="K20" t="n">
+        <v>85.15003984049703</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>y = 11.785x + -36932.042</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-36932.04206809559</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>6.264038407816971e-09</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>276.9900000000002</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.000000000000332e-08</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8293174286155287</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-251</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.03928e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-60.214</v>
+      </c>
+      <c r="F21" t="n">
+        <v/>
+      </c>
+      <c r="G21" t="n">
+        <v/>
+      </c>
+      <c r="H21" t="n">
+        <v/>
+      </c>
+      <c r="I21" t="n">
+        <v/>
+      </c>
+      <c r="J21" t="n">
+        <v>30.49858366863883</v>
+      </c>
+      <c r="K21" t="n">
+        <v>85.67335799269094</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>y = 13.217x + -41245.701</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-41245.70124435767</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.276296621604266e-09</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>251</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.000000000000082e-08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8297332157516336</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-260.2199999999998</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2.0524e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-60.493</v>
+      </c>
+      <c r="F22" t="n">
+        <v/>
+      </c>
+      <c r="G22" t="n">
+        <v/>
+      </c>
+      <c r="H22" t="n">
+        <v/>
+      </c>
+      <c r="I22" t="n">
+        <v/>
+      </c>
+      <c r="J22" t="n">
+        <v>20.60680118591322</v>
+      </c>
+      <c r="K22" t="n">
+        <v>85.18416620534684</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>y = 11.869x + -36398.707</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-36398.70661123101</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>6.594935833323153e-10</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>260.2199999999998</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.000000000000062e-08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8301443599002153</v>
       </c>
     </row>
   </sheetData>
@@ -2058,12 +3670,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2073,7 +3685,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -2118,19 +3730,19 @@
       <c r="K2" t="n">
         <v>82.98382619435225</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 8.125x + -38585.075</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-38585.07460894478</v>
       </c>
       <c r="Y2" t="n">
         <v>1073.340318774666</v>
       </c>
       <c r="Z2" t="n">
-        <v>2380.480950607625</v>
+        <v>605.8199999999997</v>
       </c>
       <c r="AA2" t="n">
         <v>3.617301330012724e-07</v>
@@ -2170,19 +3782,19 @@
       <c r="K3" t="n">
         <v>84.3872862644204</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 10.176x + -41718.397</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-41718.39668810336</v>
       </c>
       <c r="Y3" t="n">
         <v>1.050785003349686e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>4805.057663809637</v>
+        <v>435.6900000000001</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000005e-08</v>
@@ -2222,19 +3834,19 @@
       <c r="K4" t="n">
         <v>84.25376652323321</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 9.938x + -38984.178</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-38984.17810447094</v>
       </c>
       <c r="Y4" t="n">
         <v>1.613962061907532e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>4633.811805503475</v>
+        <v>414.4700000000003</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000004e-08</v>
@@ -2274,19 +3886,19 @@
       <c r="K5" t="n">
         <v>84.52179248102041</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 10.427x + -40188.995</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-40188.99471371515</v>
       </c>
       <c r="Y5" t="n">
         <v>2.080062898592666e-10</v>
       </c>
       <c r="Z5" t="n">
-        <v>4548.456229770773</v>
+        <v>375.0100000000002</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000052e-08</v>
@@ -2326,19 +3938,19 @@
       <c r="K6" t="n">
         <v>84.70747604893575</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 10.795x + -41046.508</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-41046.50829060654</v>
       </c>
       <c r="Y6" t="n">
         <v>1.060273260654305e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>4481.83669330781</v>
+        <v>360.1699999999996</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000009808e-08</v>
@@ -2378,19 +3990,19 @@
       <c r="K7" t="n">
         <v>84.78113512812322</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 10.948x + -41075.083</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-41075.08273355191</v>
       </c>
       <c r="Y7" t="n">
         <v>9.994339978598567e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>4420.373114729879</v>
+        <v>344.8600000000001</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000015099e-08</v>
@@ -2430,19 +4042,19 @@
       <c r="K8" t="n">
         <v>84.90649324016671</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 11.219x + -41552.923</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-41552.92251922782</v>
       </c>
       <c r="Y8" t="n">
         <v>1.917301806367308e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>4359.515578070504</v>
+        <v>331.1700000000001</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000368e-08</v>
@@ -2482,19 +4094,19 @@
       <c r="K9" t="n">
         <v>84.99801088160652</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 11.425x + -41807.915</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-41807.91473405976</v>
       </c>
       <c r="Y9" t="n">
         <v>7.272425296825485e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>4302.387579045705</v>
+        <v>319.9399999999996</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000001809e-08</v>
@@ -2534,19 +4146,19 @@
       <c r="K10" t="n">
         <v>85.00741874675249</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 11.447x + -41365.480</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-41365.48015405237</v>
       </c>
       <c r="Y10" t="n">
         <v>3.786705163748536e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>4248.92922349523</v>
+        <v>307.6500000000001</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000004836e-08</v>
@@ -2586,19 +4198,19 @@
       <c r="K11" t="n">
         <v>85.13589535915867</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 11.751x + -42023.618</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-42023.61822488459</v>
       </c>
       <c r="Y11" t="n">
         <v>1.501267779284147e-08</v>
       </c>
       <c r="Z11" t="n">
-        <v>4198.953644447599</v>
+        <v>296.0500000000002</v>
       </c>
       <c r="AA11" t="n">
         <v>1.00000000000075e-08</v>
@@ -2724,12 +4336,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2739,7 +4351,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -2784,19 +4396,19 @@
       <c r="K2" t="n">
         <v>83.61969474219417</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 8.943x + -35423.976</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-35423.97564794312</v>
       </c>
       <c r="Y2" t="n">
         <v>1.521657633262843e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>4653.890839873927</v>
+        <v>497.1500000000001</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000054e-08</v>
@@ -2836,19 +4448,19 @@
       <c r="K3" t="n">
         <v>84.51476939731096</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 10.414x + -39193.999</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-39193.99875693533</v>
       </c>
       <c r="Y3" t="n">
         <v>2.910658385666193e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>4428.909836046425</v>
+        <v>396.6900000000005</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000407e-08</v>
@@ -2888,19 +4500,19 @@
       <c r="K4" t="n">
         <v>84.77022221196508</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 10.925x + -40420.985</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-40420.98541322634</v>
       </c>
       <c r="Y4" t="n">
         <v>6.229554545332458e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>4352.02768845258</v>
+        <v>361.98</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000844e-08</v>
@@ -2940,19 +4552,19 @@
       <c r="K5" t="n">
         <v>84.85761396175705</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 11.112x + -40590.778</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-40590.77826771026</v>
       </c>
       <c r="Y5" t="n">
         <v>3.760496163544514e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>4296.716262856918</v>
+        <v>346.9000000000001</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000816e-08</v>
@@ -2992,19 +4604,19 @@
       <c r="K6" t="n">
         <v>84.93781898397262</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 11.289x + -40766.216</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-40766.21594067842</v>
       </c>
       <c r="Y6" t="n">
         <v>5.185417571141088e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>4244.709705821757</v>
+        <v>338.8599999999997</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000715e-08</v>
@@ -3044,19 +4656,19 @@
       <c r="K7" t="n">
         <v>85.0819747048894</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 11.622x + -41526.573</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-41526.57298806445</v>
       </c>
       <c r="Y7" t="n">
         <v>1.617339558873035e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>4192.791121687596</v>
+        <v>325.96</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000001757e-08</v>
@@ -3096,19 +4708,19 @@
       <c r="K8" t="n">
         <v>85.17393988620762</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 11.844x + -41860.974</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-41860.97354407657</v>
       </c>
       <c r="Y8" t="n">
         <v>1.847126196992954e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>4142.230575826401</v>
+        <v>314.98</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000057e-08</v>
@@ -3148,19 +4760,19 @@
       <c r="K9" t="n">
         <v>85.16012248004422</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 11.810x + -41250.466</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-41250.46562680621</v>
       </c>
       <c r="Y9" t="n">
         <v>1.991278277557005e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>4093.828928492236</v>
+        <v>313.9400000000001</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000001947e-08</v>
@@ -3200,19 +4812,19 @@
       <c r="K10" t="n">
         <v>85.21521602354497</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 11.947x + -41277.836</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-41277.83624842841</v>
       </c>
       <c r="Y10" t="n">
         <v>7.891125767703922e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>4047.154068088556</v>
+        <v>302.6700000000001</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000006667e-08</v>
@@ -3252,19 +4864,19 @@
       <c r="K11" t="n">
         <v>84.7370648577123</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 10.856x + -36879.855</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-36879.85482537232</v>
       </c>
       <c r="Y11" t="n">
         <v>3.299733213975684e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>4001.816873409182</v>
+        <v>315.7999999999997</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000005228e-08</v>
@@ -3304,19 +4916,19 @@
       <c r="K12" t="n">
         <v>84.81127316187894</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 11.012x + -37032.877</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-37032.87724548585</v>
       </c>
       <c r="Y12" t="n">
         <v>1.265069957050443e-11</v>
       </c>
       <c r="Z12" t="n">
-        <v>3958.889677470831</v>
+        <v>309.4000000000001</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000000027e-08</v>
@@ -3356,19 +4968,19 @@
       <c r="K13" t="n">
         <v>85.39710007192203</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 12.421x + -41640.336</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-41640.33620342238</v>
       </c>
       <c r="Y13" t="n">
         <v>1.168556271462451e-08</v>
       </c>
       <c r="Z13" t="n">
-        <v>3917.910732737846</v>
+        <v>277.54</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000023e-08</v>
@@ -3408,19 +5020,19 @@
       <c r="K14" t="n">
         <v>84.92263007399227</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 11.255x + -37119.708</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-37119.70767182198</v>
       </c>
       <c r="Y14" t="n">
         <v>4.648870650044301e-10</v>
       </c>
       <c r="Z14" t="n">
-        <v>3877.639945750469</v>
+        <v>294.5899999999997</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000102e-08</v>
@@ -3460,19 +5072,19 @@
       <c r="K15" t="n">
         <v>84.93737002792997</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 11.288x + -36871.411</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-36871.4112509617</v>
       </c>
       <c r="Y15" t="n">
         <v>3.043708393811753e-10</v>
       </c>
       <c r="Z15" t="n">
-        <v>3837.930304753713</v>
+        <v>288.9499999999998</v>
       </c>
       <c r="AA15" t="n">
         <v>1.00000000000016e-08</v>
@@ -3512,19 +5124,19 @@
       <c r="K16" t="n">
         <v>85.46533146925215</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 12.609x + -41045.803</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-41045.80255470653</v>
       </c>
       <c r="Y16" t="n">
         <v>3.395595330295504e-11</v>
       </c>
       <c r="Z16" t="n">
-        <v>3799.431494836769</v>
+        <v>256.2600000000002</v>
       </c>
       <c r="AA16" t="n">
         <v>1e-08</v>
@@ -3564,19 +5176,19 @@
       <c r="K17" t="n">
         <v>85.09085296151095</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 11.643x + -37345.720</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-37345.71976115601</v>
       </c>
       <c r="Y17" t="n">
         <v>8.747000056007439e-11</v>
       </c>
       <c r="Z17" t="n">
-        <v>3761.326044031936</v>
+        <v>273.6300000000001</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000002902e-08</v>
@@ -3616,19 +5228,19 @@
       <c r="K18" t="n">
         <v>85.08234391024732</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 11.622x + -36912.860</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-36912.85957093524</v>
       </c>
       <c r="Y18" t="n">
         <v>2.857883550239786e-10</v>
       </c>
       <c r="Z18" t="n">
-        <v>3723.576550417546</v>
+        <v>270.6599999999999</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000001416e-08</v>
@@ -3668,19 +5280,19 @@
       <c r="K19" t="n">
         <v>85.11374002852462</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 11.697x + -36789.860</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-36789.86004587459</v>
       </c>
       <c r="Y19" t="n">
         <v>5.615926122380126e-09</v>
       </c>
       <c r="Z19" t="n">
-        <v>3685.61143786212</v>
+        <v>261.96</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000000003e-08</v>
@@ -3720,19 +5332,19 @@
       <c r="K20" t="n">
         <v>85.10782026205494</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 11.683x + -36383.086</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-36383.08632855428</v>
       </c>
       <c r="Y20" t="n">
         <v>7.181368074988119e-09</v>
       </c>
       <c r="Z20" t="n">
-        <v>3648.260515367372</v>
+        <v>259.4000000000001</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000405e-08</v>
@@ -3772,19 +5384,19 @@
       <c r="K21" t="n">
         <v>85.15954364590017</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 11.809x + -36425.825</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-36425.82521801424</v>
       </c>
       <c r="Y21" t="n">
         <v>1.532190754060749e-09</v>
       </c>
       <c r="Z21" t="n">
-        <v>3610.871663855977</v>
+        <v>252</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000001747e-08</v>
@@ -3824,19 +5436,19 @@
       <c r="K22" t="n">
         <v>85.13022644778653</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 11.737x + -35833.967</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-35833.96723458635</v>
       </c>
       <c r="Y22" t="n">
         <v>3.959365931943967e-10</v>
       </c>
       <c r="Z22" t="n">
-        <v>3574.213531026992</v>
+        <v>251.1300000000001</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000061e-08</v>
@@ -3962,12 +5574,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -3977,7 +5589,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -4022,19 +5634,19 @@
       <c r="K2" t="n">
         <v>82.26140399246577</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 7.359x + -34424.683</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-34424.68344287606</v>
       </c>
       <c r="Y2" t="n">
         <v>1055.080731106669</v>
       </c>
       <c r="Z2" t="n">
-        <v>2293.908302385268</v>
+        <v>646.7700000000004</v>
       </c>
       <c r="AA2" t="n">
         <v>2.835846168589033e-07</v>
@@ -4074,19 +5686,19 @@
       <c r="K3" t="n">
         <v>84.34246022243882</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 10.094x + -40963.239</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-40963.23885384059</v>
       </c>
       <c r="Y3" t="n">
         <v>1.623045504896294e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>4753.384423106874</v>
+        <v>437.29</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000001e-08</v>
@@ -4126,19 +5738,19 @@
       <c r="K4" t="n">
         <v>84.30001966450594</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 10.019x + -38971.582</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-38971.58159006686</v>
       </c>
       <c r="Y4" t="n">
         <v>8.249716657774193e-13</v>
       </c>
       <c r="Z4" t="n">
-        <v>4590.643252646193</v>
+        <v>402.73</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000002e-08</v>
@@ -4178,19 +5790,19 @@
       <c r="K5" t="n">
         <v>84.52616719992889</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 10.435x + -39914.770</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-39914.77040381361</v>
       </c>
       <c r="Y5" t="n">
         <v>1.602638798140937e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>4510.666258300266</v>
+        <v>380.4199999999996</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000017e-08</v>
@@ -4230,19 +5842,19 @@
       <c r="K6" t="n">
         <v>84.67154290748921</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 10.722x + -40424.185</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-40424.1852491955</v>
       </c>
       <c r="Y6" t="n">
         <v>1.169127569493476e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>4443.624127221153</v>
+        <v>346.2800000000002</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000002368e-08</v>
@@ -4282,19 +5894,19 @@
       <c r="K7" t="n">
         <v>84.80952539062433</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 11.008x + -40989.636</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-40989.63622504757</v>
       </c>
       <c r="Y7" t="n">
         <v>3.488492394900494e-10</v>
       </c>
       <c r="Z7" t="n">
-        <v>4381.919398490669</v>
+        <v>335.6100000000001</v>
       </c>
       <c r="AA7" t="n">
         <v>1.00000000000195e-08</v>
@@ -4334,19 +5946,19 @@
       <c r="K8" t="n">
         <v>84.88251420967354</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 11.166x + -41023.953</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-41023.95344322815</v>
       </c>
       <c r="Y8" t="n">
         <v>5.089663676532676e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>4320.782336644716</v>
+        <v>331.1100000000001</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000002041e-08</v>
@@ -4386,19 +5998,19 @@
       <c r="K9" t="n">
         <v>84.96493977149893</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 11.350x + -41162.870</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-41162.87044068253</v>
       </c>
       <c r="Y9" t="n">
         <v>2.34267778668352e-10</v>
       </c>
       <c r="Z9" t="n">
-        <v>4261.567840336447</v>
+        <v>316.52</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000184e-08</v>
@@ -4438,19 +6050,19 @@
       <c r="K10" t="n">
         <v>85.03391924578762</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 11.509x + -41216.367</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-41216.36672372974</v>
       </c>
       <c r="Y10" t="n">
         <v>3.533449238697481e-10</v>
       </c>
       <c r="Z10" t="n">
-        <v>4205.152332984519</v>
+        <v>308.8400000000001</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000001e-08</v>
@@ -4490,19 +6102,19 @@
       <c r="K11" t="n">
         <v>84.54892914421082</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 10.479x + -36846.719</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-36846.71880798282</v>
       </c>
       <c r="Y11" t="n">
         <v>1.123019456708511e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>4152.477972393427</v>
+        <v>318.1900000000001</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000001e-08</v>
@@ -4628,12 +6240,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -4643,7 +6255,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -4688,19 +6300,19 @@
       <c r="K2" t="n">
         <v>84.37194995486097</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 10.148x + -40301.795</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-40301.79480221806</v>
       </c>
       <c r="Y2" t="n">
         <v>1.235926572917609e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>4630.804069233268</v>
+        <v>442.3800000000001</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000034e-08</v>
@@ -4740,19 +6352,19 @@
       <c r="K3" t="n">
         <v>84.56822515595378</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 10.517x + -39451.086</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-39451.08615926488</v>
       </c>
       <c r="Y3" t="n">
         <v>3.108028271526496e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>4417.453442020096</v>
+        <v>374.9000000000001</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000004962e-08</v>
@@ -4792,19 +6404,19 @@
       <c r="K4" t="n">
         <v>84.82002628009154</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 11.031x + -40680.185</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-40680.18506933431</v>
       </c>
       <c r="Y4" t="n">
         <v>3.29061613257218e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>4341.507534985692</v>
+        <v>344.0300000000002</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000843e-08</v>
@@ -4844,19 +6456,19 @@
       <c r="K5" t="n">
         <v>84.41382556502128</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 10.224x + -37035.445</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-37035.44504081913</v>
       </c>
       <c r="Y5" t="n">
         <v>9.156242664486849e-10</v>
       </c>
       <c r="Z5" t="n">
-        <v>4287.261472372335</v>
+        <v>352.1500000000001</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000538e-08</v>
@@ -4896,19 +6508,19 @@
       <c r="K6" t="n">
         <v>85.04345898647802</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 11.531x + -41565.985</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-41565.98529472275</v>
       </c>
       <c r="Y6" t="n">
         <v>1.702110812891749e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>4236.770548968717</v>
+        <v>317.3000000000002</v>
       </c>
       <c r="AA6" t="n">
         <v>1.00000000000441e-08</v>
@@ -4948,19 +6560,19 @@
       <c r="K7" t="n">
         <v>85.06295837070962</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 11.577x + -41291.753</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-41291.75285344612</v>
       </c>
       <c r="Y7" t="n">
         <v>1.017413315847881e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>4191.244207467593</v>
+        <v>302.0599999999999</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000018746e-08</v>
@@ -5000,19 +6612,19 @@
       <c r="K8" t="n">
         <v>85.16472102842944</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 11.821x + -41786.273</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-41786.27346587367</v>
       </c>
       <c r="Y8" t="n">
         <v>1.135560371762622e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>4150.409573333377</v>
+        <v>298.8500000000004</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000954e-08</v>
@@ -5052,19 +6664,19 @@
       <c r="K9" t="n">
         <v>84.63053671236834</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 10.639x + -37016.404</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-37016.40395681278</v>
       </c>
       <c r="Y9" t="n">
         <v>9.005111509448654e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>4109.546372580284</v>
+        <v>313.2399999999998</v>
       </c>
       <c r="AA9" t="n">
         <v>1.00000000000022e-08</v>
@@ -5104,19 +6716,19 @@
       <c r="K10" t="n">
         <v>85.25099179818707</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 12.037x + -41782.158</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-41782.15808609482</v>
       </c>
       <c r="Y10" t="n">
         <v>8.968435402752091e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>4069.647770720112</v>
+        <v>288.8299999999999</v>
       </c>
       <c r="AA10" t="n">
         <v>1.00000000000632e-08</v>
@@ -5156,19 +6768,19 @@
       <c r="K11" t="n">
         <v>85.24754351245532</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 12.028x + -41345.471</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-41345.47078662629</v>
       </c>
       <c r="Y11" t="n">
         <v>1.649035460946066e-08</v>
       </c>
       <c r="Z11" t="n">
-        <v>4030.907290418277</v>
+        <v>277.3600000000001</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000046e-08</v>
@@ -5208,19 +6820,19 @@
       <c r="K12" t="n">
         <v>84.81800580983017</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 11.027x + -37364.129</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-37364.12935134943</v>
       </c>
       <c r="Y12" t="n">
         <v>1.284098864596018e-08</v>
       </c>
       <c r="Z12" t="n">
-        <v>3993.970859178094</v>
+        <v>287.6700000000001</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000001263e-08</v>
@@ -5260,19 +6872,19 @@
       <c r="K13" t="n">
         <v>84.83859398258224</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 11.071x + -37195.101</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-37195.10094076003</v>
       </c>
       <c r="Y13" t="n">
         <v>8.622869047033051e-09</v>
       </c>
       <c r="Z13" t="n">
-        <v>3957.811488573836</v>
+        <v>282.02</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000254e-08</v>
@@ -5312,19 +6924,19 @@
       <c r="K14" t="n">
         <v>85.39142285893249</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 12.406x + -41572.932</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-41572.93156759319</v>
       </c>
       <c r="Y14" t="n">
         <v>5.380529307457898e-09</v>
       </c>
       <c r="Z14" t="n">
-        <v>3921.772438603268</v>
+        <v>254.0799999999999</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000001409e-08</v>
@@ -5364,19 +6976,19 @@
       <c r="K15" t="n">
         <v>84.88020865647478</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 11.161x + -36859.368</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-36859.36792161804</v>
       </c>
       <c r="Y15" t="n">
         <v>2.31898092160703e-08</v>
       </c>
       <c r="Z15" t="n">
-        <v>3886.490196109462</v>
+        <v>266.1799999999998</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000000254e-08</v>
@@ -5416,19 +7028,19 @@
       <c r="K16" t="n">
         <v>85.36840923792033</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 12.344x + -40623.664</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-40623.66442183763</v>
       </c>
       <c r="Y16" t="n">
         <v>3.887219174510559e-10</v>
       </c>
       <c r="Z16" t="n">
-        <v>3850.310176161137</v>
+        <v>246.77</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000003e-08</v>
@@ -5468,19 +7080,19 @@
       <c r="K17" t="n">
         <v>85.38427135282539</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 12.386x + -40396.953</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-40396.95267118809</v>
       </c>
       <c r="Y17" t="n">
         <v>3.847306411100364e-13</v>
       </c>
       <c r="Z17" t="n">
-        <v>3813.412746061818</v>
+        <v>244.5900000000001</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000934e-08</v>
@@ -5520,19 +7132,19 @@
       <c r="K18" t="n">
         <v>84.92813358557217</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 11.267x + -36189.511</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-36189.51110608188</v>
       </c>
       <c r="Y18" t="n">
         <v>2.319893135992098e-10</v>
       </c>
       <c r="Z18" t="n">
-        <v>3775.852345068222</v>
+        <v>260.8000000000002</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000002044e-08</v>
@@ -5572,19 +7184,19 @@
       <c r="K19" t="n">
         <v>84.89451430268149</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 11.193x + -35593.802</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-35593.80162284902</v>
       </c>
       <c r="Y19" t="n">
         <v>6.150625741378004e-10</v>
       </c>
       <c r="Z19" t="n">
-        <v>3736.967588206503</v>
+        <v>259.54</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000000714e-08</v>
@@ -5624,19 +7236,19 @@
       <c r="K20" t="n">
         <v>84.91390576830854</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 11.236x + -35380.260</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-35380.25998478269</v>
       </c>
       <c r="Y20" t="n">
         <v>2.772094132424919e-11</v>
       </c>
       <c r="Z20" t="n">
-        <v>3699.112071811785</v>
+        <v>258.8200000000002</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000024e-08</v>
@@ -5676,19 +7288,19 @@
       <c r="K21" t="n">
         <v>84.83976307364459</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 11.073x + -34508.166</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-34508.16578125785</v>
       </c>
       <c r="Y21" t="n">
         <v>3.085022071799043e-10</v>
       </c>
       <c r="Z21" t="n">
-        <v>3661.643515416152</v>
+        <v>257.8800000000001</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000001086e-08</v>
@@ -5728,19 +7340,19 @@
       <c r="K22" t="n">
         <v>84.391455818899</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 10.183x + -31263.076</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-31263.07622818363</v>
       </c>
       <c r="Y22" t="n">
         <v>5.122970399824468e-10</v>
       </c>
       <c r="Z22" t="n">
-        <v>3624.657915364857</v>
+        <v>269.9000000000001</v>
       </c>
       <c r="AA22" t="n">
         <v>1.00000000000025e-08</v>
@@ -5866,12 +7478,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -5881,7 +7493,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -5926,19 +7538,19 @@
       <c r="K2" t="n">
         <v>81.81875342185096</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 6.956x + -31236.518</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-31236.51774651871</v>
       </c>
       <c r="Y2" t="n">
         <v>934.1838519358612</v>
       </c>
       <c r="Z2" t="n">
-        <v>2385.730023543495</v>
+        <v>705.1000000000004</v>
       </c>
       <c r="AA2" t="n">
         <v>5.80745350768789e-08</v>
@@ -5978,19 +7590,19 @@
       <c r="K3" t="n">
         <v>83.93441480572473</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 9.411x + -36215.349</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-36215.34938611357</v>
       </c>
       <c r="Y3" t="n">
         <v>6.272320891073169e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>4524.855126340347</v>
+        <v>486.6899999999996</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000235e-08</v>
@@ -6030,19 +7642,19 @@
       <c r="K4" t="n">
         <v>84.67557237840853</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 10.730x + -39782.669</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-39782.66938161801</v>
       </c>
       <c r="Y4" t="n">
         <v>6.204547895892845e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>4358.934873678555</v>
+        <v>411.7999999999997</v>
       </c>
       <c r="AA4" t="n">
         <v>1.00000000000358e-08</v>
@@ -6082,19 +7694,19 @@
       <c r="K5" t="n">
         <v>84.50587999348703</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 10.397x + -37610.762</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-37610.76231594136</v>
       </c>
       <c r="Y5" t="n">
         <v>8.426656367275097e-10</v>
       </c>
       <c r="Z5" t="n">
-        <v>4276.393863301896</v>
+        <v>399.8800000000001</v>
       </c>
       <c r="AA5" t="n">
         <v>1.00000000000093e-08</v>
@@ -6134,19 +7746,19 @@
       <c r="K6" t="n">
         <v>85.16510080591267</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 11.822x + -42398.091</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-42398.09056029002</v>
       </c>
       <c r="Y6" t="n">
         <v>5.687449380712621e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>4207.704869634666</v>
+        <v>362.1199999999999</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000369e-08</v>
@@ -6186,19 +7798,19 @@
       <c r="K7" t="n">
         <v>84.81679480537839</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 11.024x + -38723.295</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-38723.29491528345</v>
       </c>
       <c r="Y7" t="n">
         <v>9.464932124904462e-10</v>
       </c>
       <c r="Z7" t="n">
-        <v>4143.848226298488</v>
+        <v>368.5</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000707e-08</v>
@@ -6238,19 +7850,19 @@
       <c r="K8" t="n">
         <v>85.47121552740533</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 12.625x + -44019.348</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-44019.34813406553</v>
       </c>
       <c r="Y8" t="n">
         <v>5.854478355294012e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>4080.674369677742</v>
+        <v>327.96</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000004136e-08</v>
@@ -6290,19 +7902,19 @@
       <c r="K9" t="n">
         <v>85.06304538093933</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 11.577x + -39527.863</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-39527.86271113251</v>
       </c>
       <c r="Y9" t="n">
         <v>8.888881286838853e-11</v>
       </c>
       <c r="Z9" t="n">
-        <v>4019.159256258269</v>
+        <v>338.6500000000001</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000784e-08</v>
@@ -6342,19 +7954,19 @@
       <c r="K10" t="n">
         <v>85.13379570002498</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 11.746x + -39530.004</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-39530.00364594071</v>
       </c>
       <c r="Y10" t="n">
         <v>1.195807746173208e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>3958.81546257119</v>
+        <v>325.04</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000004721e-08</v>
@@ -6394,19 +8006,19 @@
       <c r="K11" t="n">
         <v>85.26426734790432</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 12.071x + -40091.100</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-40091.09987426962</v>
       </c>
       <c r="Y11" t="n">
         <v>8.500939757938179e-13</v>
       </c>
       <c r="Z11" t="n">
-        <v>3902.332604730684</v>
+        <v>311</v>
       </c>
       <c r="AA11" t="n">
         <v>1e-08</v>
@@ -6532,12 +8144,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -6547,7 +8159,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -6592,19 +8204,19 @@
       <c r="K2" t="n">
         <v>84.0920575826744</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 9.664x + -37438.652</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-37438.65193121058</v>
       </c>
       <c r="Y2" t="n">
         <v>9.02175536139579e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>4546.412649936276</v>
+        <v>493.6099999999997</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000494e-08</v>
@@ -6644,19 +8256,19 @@
       <c r="K3" t="n">
         <v>84.9164167634538</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 11.241x + -41405.882</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-41405.88197391653</v>
       </c>
       <c r="Y3" t="n">
         <v>5.434593854780971e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>4329.940258969168</v>
+        <v>386.9099999999999</v>
       </c>
       <c r="AA3" t="n">
         <v>1.00000000000021e-08</v>
@@ -6696,19 +8308,19 @@
       <c r="K4" t="n">
         <v>84.62196794710012</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 10.622x + -38183.288</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-38183.28783422406</v>
       </c>
       <c r="Y4" t="n">
         <v>2.14876472356141e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>4249.136279704687</v>
+        <v>383.71</v>
       </c>
       <c r="AA4" t="n">
         <v>1e-08</v>
@@ -6748,19 +8360,19 @@
       <c r="K5" t="n">
         <v>85.21983237533961</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 11.958x + -42711.436</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-42711.43636522233</v>
       </c>
       <c r="Y5" t="n">
         <v>8.024843145068984e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>4193.692545303805</v>
+        <v>339.3299999999999</v>
       </c>
       <c r="AA5" t="n">
         <v>1.00000000000157e-08</v>
@@ -6800,19 +8412,19 @@
       <c r="K6" t="n">
         <v>84.76044963981306</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 10.905x + -38282.818</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-38282.81836715888</v>
       </c>
       <c r="Y6" t="n">
         <v>2.880066108315514e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>4145.208135336991</v>
+        <v>360.48</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000003e-08</v>
@@ -6852,19 +8464,19 @@
       <c r="K7" t="n">
         <v>84.80621311420852</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 11.001x + -38231.144</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-38231.144362366</v>
       </c>
       <c r="Y7" t="n">
         <v>1.145084303727157e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>4100.652651665622</v>
+        <v>344.9500000000003</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000176e-08</v>
@@ -6904,19 +8516,19 @@
       <c r="K8" t="n">
         <v>84.85197506290906</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 11.100x + -38216.493</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-38216.49275971144</v>
       </c>
       <c r="Y8" t="n">
         <v>1.515083079458712e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>4058.707393125731</v>
+        <v>347.9200000000001</v>
       </c>
       <c r="AA8" t="n">
         <v>1.00000000000002e-08</v>
@@ -6956,19 +8568,19 @@
       <c r="K9" t="n">
         <v>84.89718462789831</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 11.199x + -38188.370</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-38188.37004848402</v>
       </c>
       <c r="Y9" t="n">
         <v>2.833478426214852e-10</v>
       </c>
       <c r="Z9" t="n">
-        <v>4018.348495702831</v>
+        <v>333.4499999999998</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000001e-08</v>
@@ -7008,19 +8620,19 @@
       <c r="K10" t="n">
         <v>85.00845129189244</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 11.450x + -38699.499</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-38699.49919989831</v>
       </c>
       <c r="Y10" t="n">
         <v>9.68213434659183e-10</v>
       </c>
       <c r="Z10" t="n">
-        <v>3979.448659800326</v>
+        <v>314.9200000000001</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000085e-08</v>
@@ -7060,19 +8672,19 @@
       <c r="K11" t="n">
         <v>85.47555092902752</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 12.637x + -42607.690</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-42607.68993200607</v>
       </c>
       <c r="Y11" t="n">
         <v>4.606741513217921e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>3942.416923180658</v>
+        <v>302.71</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000684e-08</v>
@@ -7112,19 +8724,19 @@
       <c r="K12" t="n">
         <v>85.09978255247546</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 11.664x + -38767.251</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-38767.25062149622</v>
       </c>
       <c r="Y12" t="n">
         <v>1.178383808251198e-09</v>
       </c>
       <c r="Z12" t="n">
-        <v>3906.229744126156</v>
+        <v>309.5599999999999</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000000049e-08</v>
@@ -7164,19 +8776,19 @@
       <c r="K13" t="n">
         <v>85.12143442605102</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 11.716x + -38598.697</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-38598.69676550315</v>
       </c>
       <c r="Y13" t="n">
         <v>5.377195440529159e-10</v>
       </c>
       <c r="Z13" t="n">
-        <v>3871.158020146187</v>
+        <v>303.48</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000001256e-08</v>
@@ -7216,19 +8828,19 @@
       <c r="K14" t="n">
         <v>85.15949670657041</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 11.809x + -38582.039</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-38582.03856828791</v>
       </c>
       <c r="Y14" t="n">
         <v>3.169718704593535e-10</v>
       </c>
       <c r="Z14" t="n">
-        <v>3835.989998949466</v>
+        <v>305.6400000000003</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000017186e-08</v>
@@ -7268,19 +8880,19 @@
       <c r="K15" t="n">
         <v>85.1690390181186</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 11.832x + -38317.353</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-38317.35342556189</v>
       </c>
       <c r="Y15" t="n">
         <v>5.163221658958326e-11</v>
       </c>
       <c r="Z15" t="n">
-        <v>3801.152867077442</v>
+        <v>288.9499999999998</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000000045e-08</v>
@@ -7320,19 +8932,19 @@
       <c r="K16" t="n">
         <v>85.25589780456357</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 12.050x + -38702.062</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-38702.06183167682</v>
       </c>
       <c r="Y16" t="n">
         <v>4.324637531563735e-12</v>
       </c>
       <c r="Z16" t="n">
-        <v>3765.866408940889</v>
+        <v>279.8800000000001</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000082e-08</v>
@@ -7372,19 +8984,19 @@
       <c r="K17" t="n">
         <v>85.23136093573883</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 11.987x + -38150.214</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-38150.21430726999</v>
       </c>
       <c r="Y17" t="n">
         <v>1.985192077426656e-08</v>
       </c>
       <c r="Z17" t="n">
-        <v>3730.377770053432</v>
+        <v>279.0299999999997</v>
       </c>
       <c r="AA17" t="n">
         <v>1.00000000000952e-08</v>
@@ -7424,19 +9036,19 @@
       <c r="K18" t="n">
         <v>85.34760129178245</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 12.288x + -38798.014</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-38798.01367035966</v>
       </c>
       <c r="Y18" t="n">
         <v>2.0944098674368e-14</v>
       </c>
       <c r="Z18" t="n">
-        <v>3696.0770156904</v>
+        <v>275.1999999999998</v>
       </c>
       <c r="AA18" t="n">
         <v>1e-08</v>
@@ -7476,19 +9088,19 @@
       <c r="K19" t="n">
         <v>85.34220099001631</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 12.274x + -38375.936</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-38375.93558057064</v>
       </c>
       <c r="Y19" t="n">
         <v>4.382033804628565e-11</v>
       </c>
       <c r="Z19" t="n">
-        <v>3659.739763347086</v>
+        <v>265.9000000000001</v>
       </c>
       <c r="AA19" t="n">
         <v>1.00000000000003e-08</v>
@@ -7528,19 +9140,19 @@
       <c r="K20" t="n">
         <v>85.37319319370786</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 12.357x + -38286.030</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-38286.0299618542</v>
       </c>
       <c r="Y20" t="n">
         <v>1.270549332805959e-09</v>
       </c>
       <c r="Z20" t="n">
-        <v>3623.718649918355</v>
+        <v>263.2999999999997</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000001719e-08</v>
@@ -7580,19 +9192,19 @@
       <c r="K21" t="n">
         <v>85.36996510611868</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 12.348x + -37899.951</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-37899.95117546595</v>
       </c>
       <c r="Y21" t="n">
         <v>9.953075358001483e-09</v>
       </c>
       <c r="Z21" t="n">
-        <v>3589.402565469917</v>
+        <v>252.2999999999997</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000000005e-08</v>
@@ -7632,19 +9244,19 @@
       <c r="K22" t="n">
         <v>84.9717545413131</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 11.366x + -34370.340</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-34370.34040002357</v>
       </c>
       <c r="Y22" t="n">
         <v>2.31220898286965e-10</v>
       </c>
       <c r="Z22" t="n">
-        <v>3554.157447565878</v>
+        <v>263.6400000000003</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000035e-08</v>
@@ -7770,12 +9382,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -7785,7 +9397,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -7830,19 +9442,19 @@
       <c r="K2" t="n">
         <v>83.3873129477326</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 8.626x + -30076.130</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-30076.12992159559</v>
       </c>
       <c r="Y2" t="n">
         <v>2.548767816972464e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>3931.3295098559</v>
+        <v>552.7600000000002</v>
       </c>
       <c r="AA2" t="n">
         <v>1.00000000000951e-08</v>
@@ -7882,19 +9494,19 @@
       <c r="K3" t="n">
         <v>84.69149544565077</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 10.762x + -30940.692</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-30940.69225926958</v>
       </c>
       <c r="Y3" t="n">
         <v>2.064013584503895e-11</v>
       </c>
       <c r="Z3" t="n">
-        <v>3330.341443771282</v>
+        <v>352.4099999999999</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000087e-08</v>
@@ -7934,19 +9546,19 @@
       <c r="K4" t="n">
         <v>85.48198616993866</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 12.655x + -35044.184</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-35044.1838767528</v>
       </c>
       <c r="Y4" t="n">
         <v>2.600304056244478e-11</v>
       </c>
       <c r="Z4" t="n">
-        <v>3198.773498650586</v>
+        <v>283.5999999999999</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000259e-08</v>
@@ -7986,19 +9598,19 @@
       <c r="K5" t="n">
         <v>85.22762894081315</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 11.978x + -32359.745</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-32359.74514723961</v>
       </c>
       <c r="Y5" t="n">
         <v>1.624150959028984e-12</v>
       </c>
       <c r="Z5" t="n">
-        <v>3137.91765451105</v>
+        <v>266.4499999999998</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000114e-08</v>
@@ -8038,19 +9650,19 @@
       <c r="K6" t="n">
         <v>85.30778033946123</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 12.183x + -32436.802</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-32436.80238746237</v>
       </c>
       <c r="Y6" t="n">
         <v>6.237155215073255e-14</v>
       </c>
       <c r="Z6" t="n">
-        <v>3090.404222545536</v>
+        <v>254.9200000000001</v>
       </c>
       <c r="AA6" t="n">
         <v>1e-08</v>
@@ -8090,19 +9702,19 @@
       <c r="K7" t="n">
         <v>85.01786830514428</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 11.471x + -29990.228</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-29990.2279741978</v>
       </c>
       <c r="Y7" t="n">
         <v>1.873052751754583e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>3045.549785816086</v>
+        <v>259.3099999999999</v>
       </c>
       <c r="AA7" t="n">
         <v>1e-08</v>
@@ -8142,19 +9754,19 @@
       <c r="K8" t="n">
         <v>85.40923540709269</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 12.454x + -32245.915</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-32245.91517107652</v>
       </c>
       <c r="Y8" t="n">
         <v>4.072263196839266e-11</v>
       </c>
       <c r="Z8" t="n">
-        <v>3000.177687131686</v>
+        <v>240.0099999999998</v>
       </c>
       <c r="AA8" t="n">
         <v>1e-08</v>
@@ -8194,19 +9806,19 @@
       <c r="K9" t="n">
         <v>85.46060189716655</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 12.595x + -32172.309</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-32172.30905325947</v>
       </c>
       <c r="Y9" t="n">
         <v>1.575618300636622e-12</v>
       </c>
       <c r="Z9" t="n">
-        <v>2955.778520537724</v>
+        <v>231.9200000000001</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -8246,19 +9858,19 @@
       <c r="K10" t="n">
         <v>85.45998958481565</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 12.594x + -31717.814</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-31717.81379658414</v>
       </c>
       <c r="Y10" t="n">
         <v>4.067180711400814e-10</v>
       </c>
       <c r="Z10" t="n">
-        <v>2913.40211426387</v>
+        <v>233.2599999999998</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000055e-08</v>
@@ -8298,19 +9910,19 @@
       <c r="K11" t="n">
         <v>85.17558684606576</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 11.848x + -29321.329</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-29321.32910393714</v>
       </c>
       <c r="Y11" t="n">
         <v>9.396591062440979e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>2873.572204780687</v>
+        <v>239.3999999999996</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000047e-08</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 22.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 22.xlsx
@@ -528,12 +528,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -588,10 +588,8 @@
       <c r="K2" t="n">
         <v>84.00972660163535</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 9.530x + -38869.911</t>
-        </is>
+      <c r="W2" t="n">
+        <v>9.529926668694126</v>
       </c>
       <c r="X2" t="n">
         <v>-38869.91105651398</v>
@@ -600,7 +598,7 @@
         <v>788.250215773583</v>
       </c>
       <c r="Z2" t="n">
-        <v>483.7100000000005</v>
+        <v>2340.447322745747</v>
       </c>
       <c r="AA2" t="n">
         <v>5.776946517833533e-08</v>
@@ -640,10 +638,8 @@
       <c r="K3" t="n">
         <v>84.38358080225115</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 10.169x + -40922.630</t>
-        </is>
+      <c r="W3" t="n">
+        <v>10.16878251503987</v>
       </c>
       <c r="X3" t="n">
         <v>-40922.63006373644</v>
@@ -652,7 +648,7 @@
         <v>1.375691008376404e-10</v>
       </c>
       <c r="Z3" t="n">
-        <v>449.0000000000005</v>
+        <v>4730.196575854054</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000007e-08</v>
@@ -692,10 +688,8 @@
       <c r="K4" t="n">
         <v>84.69632213072371</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 10.772x + -42718.906</t>
-        </is>
+      <c r="W4" t="n">
+        <v>10.7721546218689</v>
       </c>
       <c r="X4" t="n">
         <v>-42718.90590584213</v>
@@ -704,7 +698,7 @@
         <v>1.036172081155364e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>422.46</v>
+        <v>4652.823575540586</v>
       </c>
       <c r="AA4" t="n">
         <v>1.00000000000816e-08</v>
@@ -744,10 +738,8 @@
       <c r="K5" t="n">
         <v>84.33112037698744</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 10.074x + -38923.463</t>
-        </is>
+      <c r="W5" t="n">
+        <v>10.07407113442692</v>
       </c>
       <c r="X5" t="n">
         <v>-38923.4625149877</v>
@@ -756,7 +748,7 @@
         <v>1.463323541956249e-10</v>
       </c>
       <c r="Z5" t="n">
-        <v>429.4099999999999</v>
+        <v>4555.875472880276</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000084e-08</v>
@@ -796,10 +788,8 @@
       <c r="K6" t="n">
         <v>85.13828801524639</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 11.757x + -44884.110</t>
-        </is>
+      <c r="W6" t="n">
+        <v>11.75680574084049</v>
       </c>
       <c r="X6" t="n">
         <v>-44884.11049018749</v>
@@ -808,7 +798,7 @@
         <v>1.96279307198882e-12</v>
       </c>
       <c r="Z6" t="n">
-        <v>377.4799999999996</v>
+        <v>4457.927960395239</v>
       </c>
       <c r="AA6" t="n">
         <v>1e-08</v>
@@ -848,10 +838,8 @@
       <c r="K7" t="n">
         <v>84.71587544916852</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 10.812x + -40093.917</t>
-        </is>
+      <c r="W7" t="n">
+        <v>10.81224398248577</v>
       </c>
       <c r="X7" t="n">
         <v>-40093.91730232955</v>
@@ -860,7 +848,7 @@
         <v>6.876750246228913e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>390.5</v>
+        <v>4354.72800904437</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000004574e-08</v>
@@ -900,10 +888,8 @@
       <c r="K8" t="n">
         <v>84.90898905485649</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 11.225x + -40789.461</t>
-        </is>
+      <c r="W8" t="n">
+        <v>11.22466905058597</v>
       </c>
       <c r="X8" t="n">
         <v>-40789.46133594657</v>
@@ -912,7 +898,7 @@
         <v>6.302249062980872e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>361.0999999999999</v>
+        <v>4259.853162524257</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000216e-08</v>
@@ -952,10 +938,8 @@
       <c r="K9" t="n">
         <v>84.98913506843884</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 11.405x + -40564.558</t>
-        </is>
+      <c r="W9" t="n">
+        <v>11.40514239894206</v>
       </c>
       <c r="X9" t="n">
         <v>-40564.55818076397</v>
@@ -964,7 +948,7 @@
         <v>1.111873164219927e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>355.0099999999998</v>
+        <v>4162.922824612825</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000001537e-08</v>
@@ -1004,10 +988,8 @@
       <c r="K10" t="n">
         <v>85.17432897518572</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 11.845x + -41298.626</t>
-        </is>
+      <c r="W10" t="n">
+        <v>11.84503382959757</v>
       </c>
       <c r="X10" t="n">
         <v>-41298.62569820891</v>
@@ -1016,7 +998,7 @@
         <v>1.08708518102713e-08</v>
       </c>
       <c r="Z10" t="n">
-        <v>333.2200000000003</v>
+        <v>4073.216394573936</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000018961e-08</v>
@@ -1056,10 +1038,8 @@
       <c r="K11" t="n">
         <v>84.7806312433331</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 10.947x + -37209.952</t>
-        </is>
+      <c r="W11" t="n">
+        <v>10.94714859245517</v>
       </c>
       <c r="X11" t="n">
         <v>-37209.95171431376</v>
@@ -1068,7 +1048,7 @@
         <v>3.311748625133803e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>340.9900000000002</v>
+        <v>3987.893471212805</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000003197e-08</v>
@@ -1194,12 +1174,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1254,10 +1234,8 @@
       <c r="K2" t="n">
         <v>84.31863390628567</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 10.052x + -39534.145</t>
-        </is>
+      <c r="W2" t="n">
+        <v>10.05178508705094</v>
       </c>
       <c r="X2" t="n">
         <v>-39534.14506715898</v>
@@ -1266,7 +1244,7 @@
         <v>1.244253294594379e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>409.4700000000003</v>
+        <v>4625.580325676739</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000961e-08</v>
@@ -1306,10 +1284,8 @@
       <c r="K3" t="n">
         <v>84.70692971997173</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 10.794x + -40617.942</t>
-        </is>
+      <c r="W3" t="n">
+        <v>10.79386627188064</v>
       </c>
       <c r="X3" t="n">
         <v>-40617.94172694472</v>
@@ -1318,7 +1294,7 @@
         <v>7.377204449657842e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>360.3799999999997</v>
+        <v>4433.80859511773</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000001458e-08</v>
@@ -1358,10 +1334,8 @@
       <c r="K4" t="n">
         <v>84.92317105169997</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 11.256x + -41596.090</t>
-        </is>
+      <c r="W4" t="n">
+        <v>11.25619030677185</v>
       </c>
       <c r="X4" t="n">
         <v>-41596.08989601236</v>
@@ -1370,7 +1344,7 @@
         <v>1.252944243450047e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>335.9900000000002</v>
+        <v>4350.238132513493</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000144e-08</v>
@@ -1410,10 +1384,8 @@
       <c r="K5" t="n">
         <v>84.37965575076632</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 10.162x + -36761.966</t>
-        </is>
+      <c r="W5" t="n">
+        <v>10.16163528093561</v>
       </c>
       <c r="X5" t="n">
         <v>-36761.96567934959</v>
@@ -1422,7 +1394,7 @@
         <v>2.306075202763503e-10</v>
       </c>
       <c r="Z5" t="n">
-        <v>345.1599999999999</v>
+        <v>4286.768509053111</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000012766e-08</v>
@@ -1462,10 +1434,8 @@
       <c r="K6" t="n">
         <v>85.04642743210843</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 11.538x + -41540.417</t>
-        </is>
+      <c r="W6" t="n">
+        <v>11.53772392275306</v>
       </c>
       <c r="X6" t="n">
         <v>-41540.41709532502</v>
@@ -1474,7 +1444,7 @@
         <v>7.584899300526974e-11</v>
       </c>
       <c r="Z6" t="n">
-        <v>313.6300000000001</v>
+        <v>4235.722519837079</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000001277e-08</v>
@@ -1514,10 +1484,8 @@
       <c r="K7" t="n">
         <v>85.06202487131932</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 11.574x + -41222.579</t>
-        </is>
+      <c r="W7" t="n">
+        <v>11.57434974943677</v>
       </c>
       <c r="X7" t="n">
         <v>-41222.57852142974</v>
@@ -1526,7 +1494,7 @@
         <v>5.117943078847159e-10</v>
       </c>
       <c r="Z7" t="n">
-        <v>297.6399999999999</v>
+        <v>4188.927113410116</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000007216e-08</v>
@@ -1566,10 +1534,8 @@
       <c r="K8" t="n">
         <v>85.06432684311901</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 11.580x + -40809.447</t>
-        </is>
+      <c r="W8" t="n">
+        <v>11.57977478226463</v>
       </c>
       <c r="X8" t="n">
         <v>-40809.44726858166</v>
@@ -1578,7 +1544,7 @@
         <v>8.618493665111624e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>290.73</v>
+        <v>4144.905958139941</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000082e-08</v>
@@ -1618,10 +1584,8 @@
       <c r="K9" t="n">
         <v>84.70764319241597</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 10.795x + -37476.775</t>
-        </is>
+      <c r="W9" t="n">
+        <v>10.79532972467283</v>
       </c>
       <c r="X9" t="n">
         <v>-37476.77544811717</v>
@@ -1630,7 +1594,7 @@
         <v>3.55756940921727e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>303.5900000000001</v>
+        <v>4099.248886566271</v>
       </c>
       <c r="AA9" t="n">
         <v>1.00000000001205e-08</v>
@@ -1670,10 +1634,8 @@
       <c r="K10" t="n">
         <v>85.19662133565703</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 11.900x + -41104.675</t>
-        </is>
+      <c r="W10" t="n">
+        <v>11.90026656620677</v>
       </c>
       <c r="X10" t="n">
         <v>-41104.67547778001</v>
@@ -1682,7 +1644,7 @@
         <v>1.916430614249844e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>273.7900000000004</v>
+        <v>4053.947623021833</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000001917e-08</v>
@@ -1722,10 +1684,8 @@
       <c r="K11" t="n">
         <v>85.24536893564016</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 12.023x + -41096.082</t>
-        </is>
+      <c r="W11" t="n">
+        <v>12.02284655495185</v>
       </c>
       <c r="X11" t="n">
         <v>-41096.08193323449</v>
@@ -1734,7 +1694,7 @@
         <v>6.032241603430068e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>269.8900000000003</v>
+        <v>4008.970006005633</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000006e-08</v>
@@ -1774,10 +1734,8 @@
       <c r="K12" t="n">
         <v>84.74109904396667</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 10.864x + -36516.366</t>
-        </is>
+      <c r="W12" t="n">
+        <v>10.86439794910021</v>
       </c>
       <c r="X12" t="n">
         <v>-36516.36614768529</v>
@@ -1786,7 +1744,7 @@
         <v>5.039679267589776e-09</v>
       </c>
       <c r="Z12" t="n">
-        <v>281.27</v>
+        <v>3964.680842632226</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000000819e-08</v>
@@ -1826,10 +1784,8 @@
       <c r="K13" t="n">
         <v>85.21576715652263</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 11.948x + -39970.979</t>
-        </is>
+      <c r="W13" t="n">
+        <v>11.94811317017568</v>
       </c>
       <c r="X13" t="n">
         <v>-39970.97906726342</v>
@@ -1838,7 +1794,7 @@
         <v>2.247265051907677e-10</v>
       </c>
       <c r="Z13" t="n">
-        <v>256.7999999999997</v>
+        <v>3921.678424993902</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000091e-08</v>
@@ -1878,10 +1834,8 @@
       <c r="K14" t="n">
         <v>85.33063676030532</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 12.243x + -40569.323</t>
-        </is>
+      <c r="W14" t="n">
+        <v>12.24339935461345</v>
       </c>
       <c r="X14" t="n">
         <v>-40569.3225769932</v>
@@ -1890,7 +1844,7 @@
         <v>4.275191088860601e-14</v>
       </c>
       <c r="Z14" t="n">
-        <v>248.1199999999999</v>
+        <v>3877.756669921092</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000015e-08</v>
@@ -1930,10 +1884,8 @@
       <c r="K15" t="n">
         <v>84.81090471609446</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 11.011x + -35870.756</t>
-        </is>
+      <c r="W15" t="n">
+        <v>11.01136853543128</v>
       </c>
       <c r="X15" t="n">
         <v>-35870.75606967674</v>
@@ -1942,7 +1894,7 @@
         <v>1.899316326970643e-09</v>
       </c>
       <c r="Z15" t="n">
-        <v>268.23</v>
+        <v>3834.879772348723</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000000042e-08</v>
@@ -1982,10 +1934,8 @@
       <c r="K16" t="n">
         <v>84.35721180595374</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 10.121x + -32450.866</t>
-        </is>
+      <c r="W16" t="n">
+        <v>10.1209568542319</v>
       </c>
       <c r="X16" t="n">
         <v>-32450.8659486324</v>
@@ -1994,7 +1944,7 @@
         <v>6.575769629793456e-10</v>
       </c>
       <c r="Z16" t="n">
-        <v>283.1800000000003</v>
+        <v>3793.124220174062</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000565e-08</v>
@@ -2034,10 +1984,8 @@
       <c r="K17" t="n">
         <v>85.2385804050656</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 12.006x + -38472.166</t>
-        </is>
+      <c r="W17" t="n">
+        <v>12.00562613711686</v>
       </c>
       <c r="X17" t="n">
         <v>-38472.16568915868</v>
@@ -2046,7 +1994,7 @@
         <v>3.19493814588955e-09</v>
       </c>
       <c r="Z17" t="n">
-        <v>246.46</v>
+        <v>3750.503077605235</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000007e-08</v>
@@ -2086,10 +2034,8 @@
       <c r="K18" t="n">
         <v>84.82500463227315</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 11.042x + -34815.307</t>
-        </is>
+      <c r="W18" t="n">
+        <v>11.0415348364297</v>
       </c>
       <c r="X18" t="n">
         <v>-34815.30717000522</v>
@@ -2098,7 +2044,7 @@
         <v>3.582871598968226e-10</v>
       </c>
       <c r="Z18" t="n">
-        <v>260.3200000000002</v>
+        <v>3707.690031135591</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000000023e-08</v>
@@ -2138,10 +2084,8 @@
       <c r="K19" t="n">
         <v>84.7160048371845</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 10.813x + -33694.900</t>
-        </is>
+      <c r="W19" t="n">
+        <v>10.81251024672851</v>
       </c>
       <c r="X19" t="n">
         <v>-33694.90035323985</v>
@@ -2150,7 +2094,7 @@
         <v>7.408941785946461e-11</v>
       </c>
       <c r="Z19" t="n">
-        <v>261.0700000000002</v>
+        <v>3666.209999928599</v>
       </c>
       <c r="AA19" t="n">
         <v>1.00000000000037e-08</v>
@@ -2190,10 +2134,8 @@
       <c r="K20" t="n">
         <v>84.80918195253294</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 11.008x + -33980.125</t>
-        </is>
+      <c r="W20" t="n">
+        <v>11.00769394458616</v>
       </c>
       <c r="X20" t="n">
         <v>-33980.12533270143</v>
@@ -2202,7 +2144,7 @@
         <v>1.435818496161628e-10</v>
       </c>
       <c r="Z20" t="n">
-        <v>257.6099999999997</v>
+        <v>3626.471516064093</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000036e-08</v>
@@ -2242,10 +2184,8 @@
       <c r="K21" t="n">
         <v>84.71265372220327</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 10.806x + -32959.184</t>
-        </is>
+      <c r="W21" t="n">
+        <v>10.80561826422022</v>
       </c>
       <c r="X21" t="n">
         <v>-32959.18410124019</v>
@@ -2254,7 +2194,7 @@
         <v>7.518278689948309e-10</v>
       </c>
       <c r="Z21" t="n">
-        <v>253.02</v>
+        <v>3584.932522063923</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000001987e-08</v>
@@ -2294,10 +2234,8 @@
       <c r="K22" t="n">
         <v>84.6746959006757</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 10.728x + -32345.466</t>
-        </is>
+      <c r="W22" t="n">
+        <v>10.72815714776935</v>
       </c>
       <c r="X22" t="n">
         <v>-32345.46584861688</v>
@@ -2306,7 +2244,7 @@
         <v>5.277796362196904e-09</v>
       </c>
       <c r="Z22" t="n">
-        <v>253.75</v>
+        <v>3543.812075902712</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000289e-08</v>
@@ -2432,12 +2370,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2492,10 +2430,8 @@
       <c r="K2" t="n">
         <v>83.72154142991856</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 9.089x + -36235.159</t>
-        </is>
+      <c r="W2" t="n">
+        <v>9.089215831055673</v>
       </c>
       <c r="X2" t="n">
         <v>-36235.15867410284</v>
@@ -2504,7 +2440,7 @@
         <v>3.370441551673691e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>496.1800000000003</v>
+        <v>4693.538148331047</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000001e-08</v>
@@ -2544,10 +2480,8 @@
       <c r="K3" t="n">
         <v>84.38598410297396</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 10.173x + -38815.233</t>
-        </is>
+      <c r="W3" t="n">
+        <v>10.17316366861972</v>
       </c>
       <c r="X3" t="n">
         <v>-38815.23297486068</v>
@@ -2556,7 +2490,7 @@
         <v>4.326280667072054e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>425.27</v>
+        <v>4491.923364118757</v>
       </c>
       <c r="AA3" t="n">
         <v>1.00000000000053e-08</v>
@@ -2596,10 +2530,8 @@
       <c r="K4" t="n">
         <v>84.60231401110784</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 10.583x + -39633.702</t>
-        </is>
+      <c r="W4" t="n">
+        <v>10.58345717344595</v>
       </c>
       <c r="X4" t="n">
         <v>-39633.70168602013</v>
@@ -2608,7 +2540,7 @@
         <v>2.456479343354473e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>395.9499999999998</v>
+        <v>4407.761219687009</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000297e-08</v>
@@ -2648,10 +2580,8 @@
       <c r="K5" t="n">
         <v>84.74167270718836</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 10.866x + -40164.323</t>
-        </is>
+      <c r="W5" t="n">
+        <v>10.86558989574807</v>
       </c>
       <c r="X5" t="n">
         <v>-40164.32289764511</v>
@@ -2660,7 +2590,7 @@
         <v>2.021853569404719e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>386.8200000000002</v>
+        <v>4347.078069917857</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000305e-08</v>
@@ -2700,10 +2630,8 @@
       <c r="K6" t="n">
         <v>84.91731698274958</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 11.243x + -41086.843</t>
-        </is>
+      <c r="W6" t="n">
+        <v>11.24315764557522</v>
       </c>
       <c r="X6" t="n">
         <v>-41086.84302222927</v>
@@ -2712,7 +2640,7 @@
         <v>7.963394350270732e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>361.3499999999999</v>
+        <v>4292.763830766055</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000182e-08</v>
@@ -2752,10 +2680,8 @@
       <c r="K7" t="n">
         <v>84.95317909915963</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 11.323x + -40906.778</t>
-        </is>
+      <c r="W7" t="n">
+        <v>11.32346939693878</v>
       </c>
       <c r="X7" t="n">
         <v>-40906.77792795659</v>
@@ -2764,7 +2690,7 @@
         <v>2.086095934796582e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>353.3299999999999</v>
+        <v>4241.652248228808</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000184e-08</v>
@@ -2804,10 +2730,8 @@
       <c r="K8" t="n">
         <v>85.03215631551546</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 11.504x + -41112.094</t>
-        </is>
+      <c r="W8" t="n">
+        <v>11.50441354234504</v>
       </c>
       <c r="X8" t="n">
         <v>-41112.09358396035</v>
@@ -2816,7 +2740,7 @@
         <v>5.001618958464682e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>348.3800000000001</v>
+        <v>4192.374254727407</v>
       </c>
       <c r="AA8" t="n">
         <v>1.00000000000034e-08</v>
@@ -2856,10 +2780,8 @@
       <c r="K9" t="n">
         <v>85.05382371749656</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 11.555x + -40843.306</t>
-        </is>
+      <c r="W9" t="n">
+        <v>11.55506311629947</v>
       </c>
       <c r="X9" t="n">
         <v>-40843.30632908228</v>
@@ -2868,7 +2790,7 @@
         <v>4.828934291583226e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>338.5599999999999</v>
+        <v>4144.157110079499</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000324e-08</v>
@@ -2908,10 +2830,8 @@
       <c r="K10" t="n">
         <v>85.12931880014725</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 11.735x + -41044.520</t>
-        </is>
+      <c r="W10" t="n">
+        <v>11.73505156560163</v>
       </c>
       <c r="X10" t="n">
         <v>-41044.51981480025</v>
@@ -2920,7 +2840,7 @@
         <v>3.642114611136962e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>336.5999999999999</v>
+        <v>4096.364819230179</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000343e-08</v>
@@ -2960,10 +2880,8 @@
       <c r="K11" t="n">
         <v>85.19305089951024</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 11.891x + -41148.007</t>
-        </is>
+      <c r="W11" t="n">
+        <v>11.89138589081178</v>
       </c>
       <c r="X11" t="n">
         <v>-41148.00692236799</v>
@@ -2972,7 +2890,7 @@
         <v>6.102817101340699e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>320.25</v>
+        <v>4050.705572598322</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000003967e-08</v>
@@ -3012,10 +2930,8 @@
       <c r="K12" t="n">
         <v>84.77480757353189</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 10.935x + -37217.957</t>
-        </is>
+      <c r="W12" t="n">
+        <v>10.93487979251238</v>
       </c>
       <c r="X12" t="n">
         <v>-37217.95747578702</v>
@@ -3024,7 +2940,7 @@
         <v>2.839090205752015e-08</v>
       </c>
       <c r="Z12" t="n">
-        <v>341.8000000000002</v>
+        <v>4005.107665360809</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000000054e-08</v>
@@ -3064,10 +2980,8 @@
       <c r="K13" t="n">
         <v>84.91415073579513</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 11.236x + -37867.554</t>
-        </is>
+      <c r="W13" t="n">
+        <v>11.23612123574488</v>
       </c>
       <c r="X13" t="n">
         <v>-37867.55414078048</v>
@@ -3076,7 +2990,7 @@
         <v>9.05080574630993e-09</v>
       </c>
       <c r="Z13" t="n">
-        <v>322.6900000000001</v>
+        <v>3959.623991028577</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000142e-08</v>
@@ -3116,10 +3030,8 @@
       <c r="K14" t="n">
         <v>84.90803050963144</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 11.223x + -37413.048</t>
-        </is>
+      <c r="W14" t="n">
+        <v>11.22254488250005</v>
       </c>
       <c r="X14" t="n">
         <v>-37413.04763397378</v>
@@ -3128,7 +3040,7 @@
         <v>7.782032172183475e-10</v>
       </c>
       <c r="Z14" t="n">
-        <v>320.6099999999997</v>
+        <v>3915.607949259376</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000020272e-08</v>
@@ -3168,10 +3080,8 @@
       <c r="K15" t="n">
         <v>84.97187181591673</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 11.366x + -37504.011</t>
-        </is>
+      <c r="W15" t="n">
+        <v>11.3657839875253</v>
       </c>
       <c r="X15" t="n">
         <v>-37504.01101230338</v>
@@ -3180,7 +3090,7 @@
         <v>8.556457137991386e-10</v>
       </c>
       <c r="Z15" t="n">
-        <v>309.96</v>
+        <v>3871.722882687917</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000000318e-08</v>
@@ -3220,10 +3130,8 @@
       <c r="K16" t="n">
         <v>85.02533131411187</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 11.489x + -37528.922</t>
-        </is>
+      <c r="W16" t="n">
+        <v>11.4885506135527</v>
       </c>
       <c r="X16" t="n">
         <v>-37528.9224004475</v>
@@ -3232,7 +3140,7 @@
         <v>2.323400534726482e-09</v>
       </c>
       <c r="Z16" t="n">
-        <v>311.2799999999997</v>
+        <v>3828.637181266008</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000302e-08</v>
@@ -3272,10 +3180,8 @@
       <c r="K17" t="n">
         <v>85.04224778047599</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 11.528x + -37242.389</t>
-        </is>
+      <c r="W17" t="n">
+        <v>11.52794834076292</v>
       </c>
       <c r="X17" t="n">
         <v>-37242.38901594248</v>
@@ -3284,7 +3190,7 @@
         <v>2.272349103142619e-08</v>
       </c>
       <c r="Z17" t="n">
-        <v>296.6699999999996</v>
+        <v>3786.329487144363</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000006625e-08</v>
@@ -3324,10 +3230,8 @@
       <c r="K18" t="n">
         <v>85.12278138397797</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 11.719x + -37505.718</t>
-        </is>
+      <c r="W18" t="n">
+        <v>11.71924583219236</v>
       </c>
       <c r="X18" t="n">
         <v>-37505.71823373426</v>
@@ -3336,7 +3240,7 @@
         <v>1.961663329049757e-10</v>
       </c>
       <c r="Z18" t="n">
-        <v>295.4400000000001</v>
+        <v>3746.125570984323</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000000267e-08</v>
@@ -3376,10 +3280,8 @@
       <c r="K19" t="n">
         <v>85.09290417806083</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 11.648x + -36863.706</t>
-        </is>
+      <c r="W19" t="n">
+        <v>11.64754544486694</v>
       </c>
       <c r="X19" t="n">
         <v>-36863.70579542115</v>
@@ -3388,7 +3290,7 @@
         <v>7.567410631462515e-09</v>
       </c>
       <c r="Z19" t="n">
-        <v>281.9299999999998</v>
+        <v>3705.096468878992</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000014656e-08</v>
@@ -3428,10 +3330,8 @@
       <c r="K20" t="n">
         <v>85.15003984049703</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 11.785x + -36932.042</t>
-        </is>
+      <c r="W20" t="n">
+        <v>11.7854304179996</v>
       </c>
       <c r="X20" t="n">
         <v>-36932.04206809559</v>
@@ -3440,7 +3340,7 @@
         <v>6.264038407816971e-09</v>
       </c>
       <c r="Z20" t="n">
-        <v>276.9900000000002</v>
+        <v>3665.14807273726</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000332e-08</v>
@@ -3480,10 +3380,8 @@
       <c r="K21" t="n">
         <v>85.67335799269094</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 13.217x + -41245.701</t>
-        </is>
+      <c r="W21" t="n">
+        <v>13.21737052182922</v>
       </c>
       <c r="X21" t="n">
         <v>-41245.70124435767</v>
@@ -3492,7 +3390,7 @@
         <v>1.276296621604266e-09</v>
       </c>
       <c r="Z21" t="n">
-        <v>251</v>
+        <v>3625.031257930533</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000000082e-08</v>
@@ -3532,10 +3430,8 @@
       <c r="K22" t="n">
         <v>85.18416620534684</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 11.869x + -36398.707</t>
-        </is>
+      <c r="W22" t="n">
+        <v>11.86934418587773</v>
       </c>
       <c r="X22" t="n">
         <v>-36398.70661123101</v>
@@ -3544,7 +3440,7 @@
         <v>6.594935833323153e-10</v>
       </c>
       <c r="Z22" t="n">
-        <v>260.2199999999998</v>
+        <v>3584.938918758713</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000062e-08</v>
@@ -3670,12 +3566,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -3730,10 +3626,8 @@
       <c r="K2" t="n">
         <v>82.98382619435225</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 8.125x + -38585.075</t>
-        </is>
+      <c r="W2" t="n">
+        <v>8.12538358958281</v>
       </c>
       <c r="X2" t="n">
         <v>-38585.07460894478</v>
@@ -3742,7 +3636,7 @@
         <v>1073.340318774666</v>
       </c>
       <c r="Z2" t="n">
-        <v>605.8199999999997</v>
+        <v>2380.480950607625</v>
       </c>
       <c r="AA2" t="n">
         <v>3.617301330012724e-07</v>
@@ -3782,10 +3676,8 @@
       <c r="K3" t="n">
         <v>84.3872862644204</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 10.176x + -41718.397</t>
-        </is>
+      <c r="W3" t="n">
+        <v>10.17553903660041</v>
       </c>
       <c r="X3" t="n">
         <v>-41718.39668810336</v>
@@ -3794,7 +3686,7 @@
         <v>1.050785003349686e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>435.6900000000001</v>
+        <v>4805.057663809637</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000005e-08</v>
@@ -3834,10 +3726,8 @@
       <c r="K4" t="n">
         <v>84.25376652323321</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 9.938x + -38984.178</t>
-        </is>
+      <c r="W4" t="n">
+        <v>9.937562212808553</v>
       </c>
       <c r="X4" t="n">
         <v>-38984.17810447094</v>
@@ -3846,7 +3736,7 @@
         <v>1.613962061907532e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>414.4700000000003</v>
+        <v>4633.811805503475</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000004e-08</v>
@@ -3886,10 +3776,8 @@
       <c r="K5" t="n">
         <v>84.52179248102041</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 10.427x + -40188.995</t>
-        </is>
+      <c r="W5" t="n">
+        <v>10.42696489757683</v>
       </c>
       <c r="X5" t="n">
         <v>-40188.99471371515</v>
@@ -3898,7 +3786,7 @@
         <v>2.080062898592666e-10</v>
       </c>
       <c r="Z5" t="n">
-        <v>375.0100000000002</v>
+        <v>4548.456229770773</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000052e-08</v>
@@ -3938,10 +3826,8 @@
       <c r="K6" t="n">
         <v>84.70747604893575</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 10.795x + -41046.508</t>
-        </is>
+      <c r="W6" t="n">
+        <v>10.79498684980381</v>
       </c>
       <c r="X6" t="n">
         <v>-41046.50829060654</v>
@@ -3950,7 +3836,7 @@
         <v>1.060273260654305e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>360.1699999999996</v>
+        <v>4481.83669330781</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000009808e-08</v>
@@ -3990,10 +3876,8 @@
       <c r="K7" t="n">
         <v>84.78113512812322</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 10.948x + -41075.083</t>
-        </is>
+      <c r="W7" t="n">
+        <v>10.94821141649907</v>
       </c>
       <c r="X7" t="n">
         <v>-41075.08273355191</v>
@@ -4002,7 +3886,7 @@
         <v>9.994339978598567e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>344.8600000000001</v>
+        <v>4420.373114729879</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000015099e-08</v>
@@ -4042,10 +3926,8 @@
       <c r="K8" t="n">
         <v>84.90649324016671</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 11.219x + -41552.923</t>
-        </is>
+      <c r="W8" t="n">
+        <v>11.21913990711417</v>
       </c>
       <c r="X8" t="n">
         <v>-41552.92251922782</v>
@@ -4054,7 +3936,7 @@
         <v>1.917301806367308e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>331.1700000000001</v>
+        <v>4359.515578070504</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000368e-08</v>
@@ -4094,10 +3976,8 @@
       <c r="K9" t="n">
         <v>84.99801088160652</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 11.425x + -41807.915</t>
-        </is>
+      <c r="W9" t="n">
+        <v>11.42548380217679</v>
       </c>
       <c r="X9" t="n">
         <v>-41807.91473405976</v>
@@ -4106,7 +3986,7 @@
         <v>7.272425296825485e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>319.9399999999996</v>
+        <v>4302.387579045705</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000001809e-08</v>
@@ -4146,10 +4026,8 @@
       <c r="K10" t="n">
         <v>85.00741874675249</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 11.447x + -41365.480</t>
-        </is>
+      <c r="W10" t="n">
+        <v>11.44712330908488</v>
       </c>
       <c r="X10" t="n">
         <v>-41365.48015405237</v>
@@ -4158,7 +4036,7 @@
         <v>3.786705163748536e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>307.6500000000001</v>
+        <v>4248.92922349523</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000004836e-08</v>
@@ -4198,10 +4076,8 @@
       <c r="K11" t="n">
         <v>85.13589535915867</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 11.751x + -42023.618</t>
-        </is>
+      <c r="W11" t="n">
+        <v>11.75099470107848</v>
       </c>
       <c r="X11" t="n">
         <v>-42023.61822488459</v>
@@ -4210,7 +4086,7 @@
         <v>1.501267779284147e-08</v>
       </c>
       <c r="Z11" t="n">
-        <v>296.0500000000002</v>
+        <v>4198.953644447599</v>
       </c>
       <c r="AA11" t="n">
         <v>1.00000000000075e-08</v>
@@ -4336,12 +4212,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -4396,10 +4272,8 @@
       <c r="K2" t="n">
         <v>83.61969474219417</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 8.943x + -35423.976</t>
-        </is>
+      <c r="W2" t="n">
+        <v>8.942950208030554</v>
       </c>
       <c r="X2" t="n">
         <v>-35423.97564794312</v>
@@ -4408,7 +4282,7 @@
         <v>1.521657633262843e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>497.1500000000001</v>
+        <v>4653.890839873927</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000054e-08</v>
@@ -4448,10 +4322,8 @@
       <c r="K3" t="n">
         <v>84.51476939731096</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 10.414x + -39193.999</t>
-        </is>
+      <c r="W3" t="n">
+        <v>10.41353283768751</v>
       </c>
       <c r="X3" t="n">
         <v>-39193.99875693533</v>
@@ -4460,7 +4332,7 @@
         <v>2.910658385666193e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>396.6900000000005</v>
+        <v>4428.909836046425</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000407e-08</v>
@@ -4500,10 +4372,8 @@
       <c r="K4" t="n">
         <v>84.77022221196508</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 10.925x + -40420.985</t>
-        </is>
+      <c r="W4" t="n">
+        <v>10.92523892590962</v>
       </c>
       <c r="X4" t="n">
         <v>-40420.98541322634</v>
@@ -4512,7 +4382,7 @@
         <v>6.229554545332458e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>361.98</v>
+        <v>4352.02768845258</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000844e-08</v>
@@ -4552,10 +4422,8 @@
       <c r="K5" t="n">
         <v>84.85761396175705</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 11.112x + -40590.778</t>
-        </is>
+      <c r="W5" t="n">
+        <v>11.11193338455345</v>
       </c>
       <c r="X5" t="n">
         <v>-40590.77826771026</v>
@@ -4564,7 +4432,7 @@
         <v>3.760496163544514e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>346.9000000000001</v>
+        <v>4296.716262856918</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000816e-08</v>
@@ -4604,10 +4472,8 @@
       <c r="K6" t="n">
         <v>84.93781898397262</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 11.289x + -40766.216</t>
-        </is>
+      <c r="W6" t="n">
+        <v>11.2889320921749</v>
       </c>
       <c r="X6" t="n">
         <v>-40766.21594067842</v>
@@ -4616,7 +4482,7 @@
         <v>5.185417571141088e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>338.8599999999997</v>
+        <v>4244.709705821757</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000715e-08</v>
@@ -4656,10 +4522,8 @@
       <c r="K7" t="n">
         <v>85.0819747048894</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 11.622x + -41526.573</t>
-        </is>
+      <c r="W7" t="n">
+        <v>11.62153360636297</v>
       </c>
       <c r="X7" t="n">
         <v>-41526.57298806445</v>
@@ -4668,7 +4532,7 @@
         <v>1.617339558873035e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>325.96</v>
+        <v>4192.791121687596</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000001757e-08</v>
@@ -4708,10 +4572,8 @@
       <c r="K8" t="n">
         <v>85.17393988620762</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 11.844x + -41860.974</t>
-        </is>
+      <c r="W8" t="n">
+        <v>11.84407432212893</v>
       </c>
       <c r="X8" t="n">
         <v>-41860.97354407657</v>
@@ -4720,7 +4582,7 @@
         <v>1.847126196992954e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>314.98</v>
+        <v>4142.230575826401</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000057e-08</v>
@@ -4760,10 +4622,8 @@
       <c r="K9" t="n">
         <v>85.16012248004422</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 11.810x + -41250.466</t>
-        </is>
+      <c r="W9" t="n">
+        <v>11.81009988108586</v>
       </c>
       <c r="X9" t="n">
         <v>-41250.46562680621</v>
@@ -4772,7 +4632,7 @@
         <v>1.991278277557005e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>313.9400000000001</v>
+        <v>4093.828928492236</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000001947e-08</v>
@@ -4812,10 +4672,8 @@
       <c r="K10" t="n">
         <v>85.21521602354497</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 11.947x + -41277.836</t>
-        </is>
+      <c r="W10" t="n">
+        <v>11.94673051434306</v>
       </c>
       <c r="X10" t="n">
         <v>-41277.83624842841</v>
@@ -4824,7 +4682,7 @@
         <v>7.891125767703922e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>302.6700000000001</v>
+        <v>4047.154068088556</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000006667e-08</v>
@@ -4864,10 +4722,8 @@
       <c r="K11" t="n">
         <v>84.7370648577123</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 10.856x + -36879.855</t>
-        </is>
+      <c r="W11" t="n">
+        <v>10.85602311100728</v>
       </c>
       <c r="X11" t="n">
         <v>-36879.85482537232</v>
@@ -4876,7 +4732,7 @@
         <v>3.299733213975684e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>315.7999999999997</v>
+        <v>4001.816873409182</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000005228e-08</v>
@@ -4916,10 +4772,8 @@
       <c r="K12" t="n">
         <v>84.81127316187894</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 11.012x + -37032.877</t>
-        </is>
+      <c r="W12" t="n">
+        <v>11.01215473250446</v>
       </c>
       <c r="X12" t="n">
         <v>-37032.87724548585</v>
@@ -4928,7 +4782,7 @@
         <v>1.265069957050443e-11</v>
       </c>
       <c r="Z12" t="n">
-        <v>309.4000000000001</v>
+        <v>3958.889677470831</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000000027e-08</v>
@@ -4968,10 +4822,8 @@
       <c r="K13" t="n">
         <v>85.39710007192203</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 12.421x + -41640.336</t>
-        </is>
+      <c r="W13" t="n">
+        <v>12.42096682264062</v>
       </c>
       <c r="X13" t="n">
         <v>-41640.33620342238</v>
@@ -4980,7 +4832,7 @@
         <v>1.168556271462451e-08</v>
       </c>
       <c r="Z13" t="n">
-        <v>277.54</v>
+        <v>3917.910732737846</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000023e-08</v>
@@ -5020,10 +4872,8 @@
       <c r="K14" t="n">
         <v>84.92263007399227</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 11.255x + -37119.708</t>
-        </is>
+      <c r="W14" t="n">
+        <v>11.25498469447073</v>
       </c>
       <c r="X14" t="n">
         <v>-37119.70767182198</v>
@@ -5032,7 +4882,7 @@
         <v>4.648870650044301e-10</v>
       </c>
       <c r="Z14" t="n">
-        <v>294.5899999999997</v>
+        <v>3877.639945750469</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000102e-08</v>
@@ -5072,10 +4922,8 @@
       <c r="K15" t="n">
         <v>84.93737002792997</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 11.288x + -36871.411</t>
-        </is>
+      <c r="W15" t="n">
+        <v>11.28792575612751</v>
       </c>
       <c r="X15" t="n">
         <v>-36871.4112509617</v>
@@ -5084,7 +4932,7 @@
         <v>3.043708393811753e-10</v>
       </c>
       <c r="Z15" t="n">
-        <v>288.9499999999998</v>
+        <v>3837.930304753713</v>
       </c>
       <c r="AA15" t="n">
         <v>1.00000000000016e-08</v>
@@ -5124,10 +4972,8 @@
       <c r="K16" t="n">
         <v>85.46533146925215</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 12.609x + -41045.803</t>
-        </is>
+      <c r="W16" t="n">
+        <v>12.60866084940955</v>
       </c>
       <c r="X16" t="n">
         <v>-41045.80255470653</v>
@@ -5136,7 +4982,7 @@
         <v>3.395595330295504e-11</v>
       </c>
       <c r="Z16" t="n">
-        <v>256.2600000000002</v>
+        <v>3799.431494836769</v>
       </c>
       <c r="AA16" t="n">
         <v>1e-08</v>
@@ -5176,10 +5022,8 @@
       <c r="K17" t="n">
         <v>85.09085296151095</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 11.643x + -37345.720</t>
-        </is>
+      <c r="W17" t="n">
+        <v>11.64265479999428</v>
       </c>
       <c r="X17" t="n">
         <v>-37345.71976115601</v>
@@ -5188,7 +5032,7 @@
         <v>8.747000056007439e-11</v>
       </c>
       <c r="Z17" t="n">
-        <v>273.6300000000001</v>
+        <v>3761.326044031936</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000002902e-08</v>
@@ -5228,10 +5072,8 @@
       <c r="K18" t="n">
         <v>85.08234391024732</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 11.622x + -36912.860</t>
-        </is>
+      <c r="W18" t="n">
+        <v>11.622410422415</v>
       </c>
       <c r="X18" t="n">
         <v>-36912.85957093524</v>
@@ -5240,7 +5082,7 @@
         <v>2.857883550239786e-10</v>
       </c>
       <c r="Z18" t="n">
-        <v>270.6599999999999</v>
+        <v>3723.576550417546</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000001416e-08</v>
@@ -5280,10 +5122,8 @@
       <c r="K19" t="n">
         <v>85.11374002852462</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 11.697x + -36789.860</t>
-        </is>
+      <c r="W19" t="n">
+        <v>11.69745576595683</v>
       </c>
       <c r="X19" t="n">
         <v>-36789.86004587459</v>
@@ -5292,7 +5132,7 @@
         <v>5.615926122380126e-09</v>
       </c>
       <c r="Z19" t="n">
-        <v>261.96</v>
+        <v>3685.61143786212</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000000003e-08</v>
@@ -5332,10 +5172,8 @@
       <c r="K20" t="n">
         <v>85.10782026205494</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 11.683x + -36383.086</t>
-        </is>
+      <c r="W20" t="n">
+        <v>11.68323239211993</v>
       </c>
       <c r="X20" t="n">
         <v>-36383.08632855428</v>
@@ -5344,7 +5182,7 @@
         <v>7.181368074988119e-09</v>
       </c>
       <c r="Z20" t="n">
-        <v>259.4000000000001</v>
+        <v>3648.260515367372</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000405e-08</v>
@@ -5384,10 +5222,8 @@
       <c r="K21" t="n">
         <v>85.15954364590017</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 11.809x + -36425.825</t>
-        </is>
+      <c r="W21" t="n">
+        <v>11.80868085809995</v>
       </c>
       <c r="X21" t="n">
         <v>-36425.82521801424</v>
@@ -5396,7 +5232,7 @@
         <v>1.532190754060749e-09</v>
       </c>
       <c r="Z21" t="n">
-        <v>252</v>
+        <v>3610.871663855977</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000001747e-08</v>
@@ -5436,10 +5272,8 @@
       <c r="K22" t="n">
         <v>85.13022644778653</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 11.737x + -35833.967</t>
-        </is>
+      <c r="W22" t="n">
+        <v>11.73724936301718</v>
       </c>
       <c r="X22" t="n">
         <v>-35833.96723458635</v>
@@ -5448,7 +5282,7 @@
         <v>3.959365931943967e-10</v>
       </c>
       <c r="Z22" t="n">
-        <v>251.1300000000001</v>
+        <v>3574.213531026992</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000061e-08</v>
@@ -5574,12 +5408,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -5634,10 +5468,8 @@
       <c r="K2" t="n">
         <v>82.26140399246577</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 7.359x + -34424.683</t>
-        </is>
+      <c r="W2" t="n">
+        <v>7.35882234351787</v>
       </c>
       <c r="X2" t="n">
         <v>-34424.68344287606</v>
@@ -5646,7 +5478,7 @@
         <v>1055.080731106669</v>
       </c>
       <c r="Z2" t="n">
-        <v>646.7700000000004</v>
+        <v>2293.908302385268</v>
       </c>
       <c r="AA2" t="n">
         <v>2.835846168589033e-07</v>
@@ -5686,10 +5518,8 @@
       <c r="K3" t="n">
         <v>84.34246022243882</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 10.094x + -40963.239</t>
-        </is>
+      <c r="W3" t="n">
+        <v>10.09439562558507</v>
       </c>
       <c r="X3" t="n">
         <v>-40963.23885384059</v>
@@ -5698,7 +5528,7 @@
         <v>1.623045504896294e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>437.29</v>
+        <v>4753.384423106874</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000001e-08</v>
@@ -5738,10 +5568,8 @@
       <c r="K4" t="n">
         <v>84.30001966450594</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 10.019x + -38971.582</t>
-        </is>
+      <c r="W4" t="n">
+        <v>10.01874277927667</v>
       </c>
       <c r="X4" t="n">
         <v>-38971.58159006686</v>
@@ -5750,7 +5578,7 @@
         <v>8.249716657774193e-13</v>
       </c>
       <c r="Z4" t="n">
-        <v>402.73</v>
+        <v>4590.643252646193</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000002e-08</v>
@@ -5790,10 +5618,8 @@
       <c r="K5" t="n">
         <v>84.52616719992889</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 10.435x + -39914.770</t>
-        </is>
+      <c r="W5" t="n">
+        <v>10.43534917298133</v>
       </c>
       <c r="X5" t="n">
         <v>-39914.77040381361</v>
@@ -5802,7 +5628,7 @@
         <v>1.602638798140937e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>380.4199999999996</v>
+        <v>4510.666258300266</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000017e-08</v>
@@ -5842,10 +5668,8 @@
       <c r="K6" t="n">
         <v>84.67154290748921</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 10.722x + -40424.185</t>
-        </is>
+      <c r="W6" t="n">
+        <v>10.72177228678657</v>
       </c>
       <c r="X6" t="n">
         <v>-40424.1852491955</v>
@@ -5854,7 +5678,7 @@
         <v>1.169127569493476e-10</v>
       </c>
       <c r="Z6" t="n">
-        <v>346.2800000000002</v>
+        <v>4443.624127221153</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000002368e-08</v>
@@ -5894,10 +5718,8 @@
       <c r="K7" t="n">
         <v>84.80952539062433</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 11.008x + -40989.636</t>
-        </is>
+      <c r="W7" t="n">
+        <v>11.00842629117617</v>
       </c>
       <c r="X7" t="n">
         <v>-40989.63622504757</v>
@@ -5906,7 +5728,7 @@
         <v>3.488492394900494e-10</v>
       </c>
       <c r="Z7" t="n">
-        <v>335.6100000000001</v>
+        <v>4381.919398490669</v>
       </c>
       <c r="AA7" t="n">
         <v>1.00000000000195e-08</v>
@@ -5946,10 +5768,8 @@
       <c r="K8" t="n">
         <v>84.88251420967354</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 11.166x + -41023.953</t>
-        </is>
+      <c r="W8" t="n">
+        <v>11.16629167330433</v>
       </c>
       <c r="X8" t="n">
         <v>-41023.95344322815</v>
@@ -5958,7 +5778,7 @@
         <v>5.089663676532676e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>331.1100000000001</v>
+        <v>4320.782336644716</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000002041e-08</v>
@@ -5998,10 +5818,8 @@
       <c r="K9" t="n">
         <v>84.96493977149893</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 11.350x + -41162.870</t>
-        </is>
+      <c r="W9" t="n">
+        <v>11.35005540197875</v>
       </c>
       <c r="X9" t="n">
         <v>-41162.87044068253</v>
@@ -6010,7 +5828,7 @@
         <v>2.34267778668352e-10</v>
       </c>
       <c r="Z9" t="n">
-        <v>316.52</v>
+        <v>4261.567840336447</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000184e-08</v>
@@ -6050,10 +5868,8 @@
       <c r="K10" t="n">
         <v>85.03391924578762</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 11.509x + -41216.367</t>
-        </is>
+      <c r="W10" t="n">
+        <v>11.50851808021725</v>
       </c>
       <c r="X10" t="n">
         <v>-41216.36672372974</v>
@@ -6062,7 +5878,7 @@
         <v>3.533449238697481e-10</v>
       </c>
       <c r="Z10" t="n">
-        <v>308.8400000000001</v>
+        <v>4205.152332984519</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000001e-08</v>
@@ -6102,10 +5918,8 @@
       <c r="K11" t="n">
         <v>84.54892914421082</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 10.479x + -36846.719</t>
-        </is>
+      <c r="W11" t="n">
+        <v>10.47918960611136</v>
       </c>
       <c r="X11" t="n">
         <v>-36846.71880798282</v>
@@ -6114,7 +5928,7 @@
         <v>1.123019456708511e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>318.1900000000001</v>
+        <v>4152.477972393427</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000001e-08</v>
@@ -6240,12 +6054,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -6300,10 +6114,8 @@
       <c r="K2" t="n">
         <v>84.37194995486097</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 10.148x + -40301.795</t>
-        </is>
+      <c r="W2" t="n">
+        <v>10.14763249012263</v>
       </c>
       <c r="X2" t="n">
         <v>-40301.79480221806</v>
@@ -6312,7 +6124,7 @@
         <v>1.235926572917609e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>442.3800000000001</v>
+        <v>4630.804069233268</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000034e-08</v>
@@ -6352,10 +6164,8 @@
       <c r="K3" t="n">
         <v>84.56822515595378</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 10.517x + -39451.086</t>
-        </is>
+      <c r="W3" t="n">
+        <v>10.51664140539485</v>
       </c>
       <c r="X3" t="n">
         <v>-39451.08615926488</v>
@@ -6364,7 +6174,7 @@
         <v>3.108028271526496e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>374.9000000000001</v>
+        <v>4417.453442020096</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000004962e-08</v>
@@ -6404,10 +6214,8 @@
       <c r="K4" t="n">
         <v>84.82002628009154</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 11.031x + -40680.185</t>
-        </is>
+      <c r="W4" t="n">
+        <v>11.03086511325033</v>
       </c>
       <c r="X4" t="n">
         <v>-40680.18506933431</v>
@@ -6416,7 +6224,7 @@
         <v>3.29061613257218e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>344.0300000000002</v>
+        <v>4341.507534985692</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000843e-08</v>
@@ -6456,10 +6264,8 @@
       <c r="K5" t="n">
         <v>84.41382556502128</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 10.224x + -37035.445</t>
-        </is>
+      <c r="W5" t="n">
+        <v>10.22419183090734</v>
       </c>
       <c r="X5" t="n">
         <v>-37035.44504081913</v>
@@ -6468,7 +6274,7 @@
         <v>9.156242664486849e-10</v>
       </c>
       <c r="Z5" t="n">
-        <v>352.1500000000001</v>
+        <v>4287.261472372335</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000538e-08</v>
@@ -6508,10 +6314,8 @@
       <c r="K6" t="n">
         <v>85.04345898647802</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 11.531x + -41565.985</t>
-        </is>
+      <c r="W6" t="n">
+        <v>11.53077947867919</v>
       </c>
       <c r="X6" t="n">
         <v>-41565.98529472275</v>
@@ -6520,7 +6324,7 @@
         <v>1.702110812891749e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>317.3000000000002</v>
+        <v>4236.770548968717</v>
       </c>
       <c r="AA6" t="n">
         <v>1.00000000000441e-08</v>
@@ -6560,10 +6364,8 @@
       <c r="K7" t="n">
         <v>85.06295837070962</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 11.577x + -41291.753</t>
-        </is>
+      <c r="W7" t="n">
+        <v>11.57654910938406</v>
       </c>
       <c r="X7" t="n">
         <v>-41291.75285344612</v>
@@ -6572,7 +6374,7 @@
         <v>1.017413315847881e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>302.0599999999999</v>
+        <v>4191.244207467593</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000018746e-08</v>
@@ -6612,10 +6414,8 @@
       <c r="K8" t="n">
         <v>85.16472102842944</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 11.821x + -41786.273</t>
-        </is>
+      <c r="W8" t="n">
+        <v>11.82138535280553</v>
       </c>
       <c r="X8" t="n">
         <v>-41786.27346587367</v>
@@ -6624,7 +6424,7 @@
         <v>1.135560371762622e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>298.8500000000004</v>
+        <v>4150.409573333377</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000954e-08</v>
@@ -6664,10 +6464,8 @@
       <c r="K9" t="n">
         <v>84.63053671236834</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 10.639x + -37016.404</t>
-        </is>
+      <c r="W9" t="n">
+        <v>10.63941504269721</v>
       </c>
       <c r="X9" t="n">
         <v>-37016.40395681278</v>
@@ -6676,7 +6474,7 @@
         <v>9.005111509448654e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>313.2399999999998</v>
+        <v>4109.546372580284</v>
       </c>
       <c r="AA9" t="n">
         <v>1.00000000000022e-08</v>
@@ -6716,10 +6514,8 @@
       <c r="K10" t="n">
         <v>85.25099179818707</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 12.037x + -41782.158</t>
-        </is>
+      <c r="W10" t="n">
+        <v>12.03714722233262</v>
       </c>
       <c r="X10" t="n">
         <v>-41782.15808609482</v>
@@ -6728,7 +6524,7 @@
         <v>8.968435402752091e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>288.8299999999999</v>
+        <v>4069.647770720112</v>
       </c>
       <c r="AA10" t="n">
         <v>1.00000000000632e-08</v>
@@ -6768,10 +6564,8 @@
       <c r="K11" t="n">
         <v>85.24754351245532</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 12.028x + -41345.471</t>
-        </is>
+      <c r="W11" t="n">
+        <v>12.02837316834888</v>
       </c>
       <c r="X11" t="n">
         <v>-41345.47078662629</v>
@@ -6780,7 +6574,7 @@
         <v>1.649035460946066e-08</v>
       </c>
       <c r="Z11" t="n">
-        <v>277.3600000000001</v>
+        <v>4030.907290418277</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000046e-08</v>
@@ -6820,10 +6614,8 @@
       <c r="K12" t="n">
         <v>84.81800580983017</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 11.027x + -37364.129</t>
-        </is>
+      <c r="W12" t="n">
+        <v>11.02654062579769</v>
       </c>
       <c r="X12" t="n">
         <v>-37364.12935134943</v>
@@ -6832,7 +6624,7 @@
         <v>1.284098864596018e-08</v>
       </c>
       <c r="Z12" t="n">
-        <v>287.6700000000001</v>
+        <v>3993.970859178094</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000001263e-08</v>
@@ -6872,10 +6664,8 @@
       <c r="K13" t="n">
         <v>84.83859398258224</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 11.071x + -37195.101</t>
-        </is>
+      <c r="W13" t="n">
+        <v>11.07076434560354</v>
       </c>
       <c r="X13" t="n">
         <v>-37195.10094076003</v>
@@ -6884,7 +6674,7 @@
         <v>8.622869047033051e-09</v>
       </c>
       <c r="Z13" t="n">
-        <v>282.02</v>
+        <v>3957.811488573836</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000254e-08</v>
@@ -6924,10 +6714,8 @@
       <c r="K14" t="n">
         <v>85.39142285893249</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 12.406x + -41572.932</t>
-        </is>
+      <c r="W14" t="n">
+        <v>12.40559961116149</v>
       </c>
       <c r="X14" t="n">
         <v>-41572.93156759319</v>
@@ -6936,7 +6724,7 @@
         <v>5.380529307457898e-09</v>
       </c>
       <c r="Z14" t="n">
-        <v>254.0799999999999</v>
+        <v>3921.772438603268</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000001409e-08</v>
@@ -6976,10 +6764,8 @@
       <c r="K15" t="n">
         <v>84.88020865647478</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 11.161x + -36859.368</t>
-        </is>
+      <c r="W15" t="n">
+        <v>11.16123640086761</v>
       </c>
       <c r="X15" t="n">
         <v>-36859.36792161804</v>
@@ -6988,7 +6774,7 @@
         <v>2.31898092160703e-08</v>
       </c>
       <c r="Z15" t="n">
-        <v>266.1799999999998</v>
+        <v>3886.490196109462</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000000254e-08</v>
@@ -7028,10 +6814,8 @@
       <c r="K16" t="n">
         <v>85.36840923792033</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 12.344x + -40623.664</t>
-        </is>
+      <c r="W16" t="n">
+        <v>12.3436908627228</v>
       </c>
       <c r="X16" t="n">
         <v>-40623.66442183763</v>
@@ -7040,7 +6824,7 @@
         <v>3.887219174510559e-10</v>
       </c>
       <c r="Z16" t="n">
-        <v>246.77</v>
+        <v>3850.310176161137</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000003e-08</v>
@@ -7080,10 +6864,8 @@
       <c r="K17" t="n">
         <v>85.38427135282539</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 12.386x + -40396.953</t>
-        </is>
+      <c r="W17" t="n">
+        <v>12.38629543527072</v>
       </c>
       <c r="X17" t="n">
         <v>-40396.95267118809</v>
@@ -7092,7 +6874,7 @@
         <v>3.847306411100364e-13</v>
       </c>
       <c r="Z17" t="n">
-        <v>244.5900000000001</v>
+        <v>3813.412746061818</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000934e-08</v>
@@ -7132,10 +6914,8 @@
       <c r="K18" t="n">
         <v>84.92813358557217</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 11.267x + -36189.511</t>
-        </is>
+      <c r="W18" t="n">
+        <v>11.26726168155364</v>
       </c>
       <c r="X18" t="n">
         <v>-36189.51110608188</v>
@@ -7144,7 +6924,7 @@
         <v>2.319893135992098e-10</v>
       </c>
       <c r="Z18" t="n">
-        <v>260.8000000000002</v>
+        <v>3775.852345068222</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000002044e-08</v>
@@ -7184,10 +6964,8 @@
       <c r="K19" t="n">
         <v>84.89451430268149</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 11.193x + -35593.802</t>
-        </is>
+      <c r="W19" t="n">
+        <v>11.19267721396151</v>
       </c>
       <c r="X19" t="n">
         <v>-35593.80162284902</v>
@@ -7196,7 +6974,7 @@
         <v>6.150625741378004e-10</v>
       </c>
       <c r="Z19" t="n">
-        <v>259.54</v>
+        <v>3736.967588206503</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000000714e-08</v>
@@ -7236,10 +7014,8 @@
       <c r="K20" t="n">
         <v>84.91390576830854</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 11.236x + -35380.260</t>
-        </is>
+      <c r="W20" t="n">
+        <v>11.23557720408171</v>
       </c>
       <c r="X20" t="n">
         <v>-35380.25998478269</v>
@@ -7248,7 +7024,7 @@
         <v>2.772094132424919e-11</v>
       </c>
       <c r="Z20" t="n">
-        <v>258.8200000000002</v>
+        <v>3699.112071811785</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000024e-08</v>
@@ -7288,10 +7064,8 @@
       <c r="K21" t="n">
         <v>84.83976307364459</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 11.073x + -34508.166</t>
-        </is>
+      <c r="W21" t="n">
+        <v>11.07328613103322</v>
       </c>
       <c r="X21" t="n">
         <v>-34508.16578125785</v>
@@ -7300,7 +7074,7 @@
         <v>3.085022071799043e-10</v>
       </c>
       <c r="Z21" t="n">
-        <v>257.8800000000001</v>
+        <v>3661.643515416152</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000001086e-08</v>
@@ -7340,10 +7114,8 @@
       <c r="K22" t="n">
         <v>84.391455818899</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 10.183x + -31263.076</t>
-        </is>
+      <c r="W22" t="n">
+        <v>10.18315242270782</v>
       </c>
       <c r="X22" t="n">
         <v>-31263.07622818363</v>
@@ -7352,7 +7124,7 @@
         <v>5.122970399824468e-10</v>
       </c>
       <c r="Z22" t="n">
-        <v>269.9000000000001</v>
+        <v>3624.657915364857</v>
       </c>
       <c r="AA22" t="n">
         <v>1.00000000000025e-08</v>
@@ -7478,12 +7250,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -7538,10 +7310,8 @@
       <c r="K2" t="n">
         <v>81.81875342185096</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 6.956x + -31236.518</t>
-        </is>
+      <c r="W2" t="n">
+        <v>6.955645380548447</v>
       </c>
       <c r="X2" t="n">
         <v>-31236.51774651871</v>
@@ -7550,7 +7320,7 @@
         <v>934.1838519358612</v>
       </c>
       <c r="Z2" t="n">
-        <v>705.1000000000004</v>
+        <v>2385.730023543495</v>
       </c>
       <c r="AA2" t="n">
         <v>5.80745350768789e-08</v>
@@ -7590,10 +7360,8 @@
       <c r="K3" t="n">
         <v>83.93441480572473</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 9.411x + -36215.349</t>
-        </is>
+      <c r="W3" t="n">
+        <v>9.410728618248074</v>
       </c>
       <c r="X3" t="n">
         <v>-36215.34938611357</v>
@@ -7602,7 +7370,7 @@
         <v>6.272320891073169e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>486.6899999999996</v>
+        <v>4524.855126340347</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000235e-08</v>
@@ -7642,10 +7410,8 @@
       <c r="K4" t="n">
         <v>84.67557237840853</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 10.730x + -39782.669</t>
-        </is>
+      <c r="W4" t="n">
+        <v>10.72993336835555</v>
       </c>
       <c r="X4" t="n">
         <v>-39782.66938161801</v>
@@ -7654,7 +7420,7 @@
         <v>6.204547895892845e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>411.7999999999997</v>
+        <v>4358.934873678555</v>
       </c>
       <c r="AA4" t="n">
         <v>1.00000000000358e-08</v>
@@ -7694,10 +7460,8 @@
       <c r="K5" t="n">
         <v>84.50587999348703</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 10.397x + -37610.762</t>
-        </is>
+      <c r="W5" t="n">
+        <v>10.39658042173464</v>
       </c>
       <c r="X5" t="n">
         <v>-37610.76231594136</v>
@@ -7706,7 +7470,7 @@
         <v>8.426656367275097e-10</v>
       </c>
       <c r="Z5" t="n">
-        <v>399.8800000000001</v>
+        <v>4276.393863301896</v>
       </c>
       <c r="AA5" t="n">
         <v>1.00000000000093e-08</v>
@@ -7746,10 +7510,8 @@
       <c r="K6" t="n">
         <v>85.16510080591267</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 11.822x + -42398.091</t>
-        </is>
+      <c r="W6" t="n">
+        <v>11.82231833650094</v>
       </c>
       <c r="X6" t="n">
         <v>-42398.09056029002</v>
@@ -7758,7 +7520,7 @@
         <v>5.687449380712621e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>362.1199999999999</v>
+        <v>4207.704869634666</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000369e-08</v>
@@ -7798,10 +7560,8 @@
       <c r="K7" t="n">
         <v>84.81679480537839</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 11.024x + -38723.295</t>
-        </is>
+      <c r="W7" t="n">
+        <v>11.0239502795976</v>
       </c>
       <c r="X7" t="n">
         <v>-38723.29491528345</v>
@@ -7810,7 +7570,7 @@
         <v>9.464932124904462e-10</v>
       </c>
       <c r="Z7" t="n">
-        <v>368.5</v>
+        <v>4143.848226298488</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000707e-08</v>
@@ -7850,10 +7610,8 @@
       <c r="K8" t="n">
         <v>85.47121552740533</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 12.625x + -44019.348</t>
-        </is>
+      <c r="W8" t="n">
+        <v>12.62511131505569</v>
       </c>
       <c r="X8" t="n">
         <v>-44019.34813406553</v>
@@ -7862,7 +7620,7 @@
         <v>5.854478355294012e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>327.96</v>
+        <v>4080.674369677742</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000004136e-08</v>
@@ -7902,10 +7660,8 @@
       <c r="K9" t="n">
         <v>85.06304538093933</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 11.577x + -39527.863</t>
-        </is>
+      <c r="W9" t="n">
+        <v>11.57675415105346</v>
       </c>
       <c r="X9" t="n">
         <v>-39527.86271113251</v>
@@ -7914,7 +7670,7 @@
         <v>8.888881286838853e-11</v>
       </c>
       <c r="Z9" t="n">
-        <v>338.6500000000001</v>
+        <v>4019.159256258269</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000784e-08</v>
@@ -7954,10 +7710,8 @@
       <c r="K10" t="n">
         <v>85.13379570002498</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 11.746x + -39530.004</t>
-        </is>
+      <c r="W10" t="n">
+        <v>11.74589995883921</v>
       </c>
       <c r="X10" t="n">
         <v>-39530.00364594071</v>
@@ -7966,7 +7720,7 @@
         <v>1.195807746173208e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>325.04</v>
+        <v>3958.81546257119</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000004721e-08</v>
@@ -8006,10 +7760,8 @@
       <c r="K11" t="n">
         <v>85.26426734790432</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 12.071x + -40091.100</t>
-        </is>
+      <c r="W11" t="n">
+        <v>12.07104545363868</v>
       </c>
       <c r="X11" t="n">
         <v>-40091.09987426962</v>
@@ -8018,7 +7770,7 @@
         <v>8.500939757938179e-13</v>
       </c>
       <c r="Z11" t="n">
-        <v>311</v>
+        <v>3902.332604730684</v>
       </c>
       <c r="AA11" t="n">
         <v>1e-08</v>
@@ -8144,12 +7896,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -8204,10 +7956,8 @@
       <c r="K2" t="n">
         <v>84.0920575826744</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 9.664x + -37438.652</t>
-        </is>
+      <c r="W2" t="n">
+        <v>9.663698360290462</v>
       </c>
       <c r="X2" t="n">
         <v>-37438.65193121058</v>
@@ -8216,7 +7966,7 @@
         <v>9.02175536139579e-10</v>
       </c>
       <c r="Z2" t="n">
-        <v>493.6099999999997</v>
+        <v>4546.412649936276</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000494e-08</v>
@@ -8256,10 +8006,8 @@
       <c r="K3" t="n">
         <v>84.9164167634538</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 11.241x + -41405.882</t>
-        </is>
+      <c r="W3" t="n">
+        <v>11.24115618197382</v>
       </c>
       <c r="X3" t="n">
         <v>-41405.88197391653</v>
@@ -8268,7 +8016,7 @@
         <v>5.434593854780971e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>386.9099999999999</v>
+        <v>4329.940258969168</v>
       </c>
       <c r="AA3" t="n">
         <v>1.00000000000021e-08</v>
@@ -8308,10 +8056,8 @@
       <c r="K4" t="n">
         <v>84.62196794710012</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 10.622x + -38183.288</t>
-        </is>
+      <c r="W4" t="n">
+        <v>10.62236362828402</v>
       </c>
       <c r="X4" t="n">
         <v>-38183.28783422406</v>
@@ -8320,7 +8066,7 @@
         <v>2.14876472356141e-10</v>
       </c>
       <c r="Z4" t="n">
-        <v>383.71</v>
+        <v>4249.136279704687</v>
       </c>
       <c r="AA4" t="n">
         <v>1e-08</v>
@@ -8360,10 +8106,8 @@
       <c r="K5" t="n">
         <v>85.21983237533961</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 11.958x + -42711.436</t>
-        </is>
+      <c r="W5" t="n">
+        <v>11.958321621289</v>
       </c>
       <c r="X5" t="n">
         <v>-42711.43636522233</v>
@@ -8372,7 +8116,7 @@
         <v>8.024843145068984e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>339.3299999999999</v>
+        <v>4193.692545303805</v>
       </c>
       <c r="AA5" t="n">
         <v>1.00000000000157e-08</v>
@@ -8412,10 +8156,8 @@
       <c r="K6" t="n">
         <v>84.76044963981306</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 10.905x + -38282.818</t>
-        </is>
+      <c r="W6" t="n">
+        <v>10.90474793523806</v>
       </c>
       <c r="X6" t="n">
         <v>-38282.81836715888</v>
@@ -8424,7 +8166,7 @@
         <v>2.880066108315514e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>360.48</v>
+        <v>4145.208135336991</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000003e-08</v>
@@ -8464,10 +8206,8 @@
       <c r="K7" t="n">
         <v>84.80621311420852</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 11.001x + -38231.144</t>
-        </is>
+      <c r="W7" t="n">
+        <v>11.00136722693087</v>
       </c>
       <c r="X7" t="n">
         <v>-38231.144362366</v>
@@ -8476,7 +8216,7 @@
         <v>1.145084303727157e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>344.9500000000003</v>
+        <v>4100.652651665622</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000176e-08</v>
@@ -8516,10 +8256,8 @@
       <c r="K8" t="n">
         <v>84.85197506290906</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 11.100x + -38216.493</t>
-        </is>
+      <c r="W8" t="n">
+        <v>11.09969626108848</v>
       </c>
       <c r="X8" t="n">
         <v>-38216.49275971144</v>
@@ -8528,7 +8266,7 @@
         <v>1.515083079458712e-10</v>
       </c>
       <c r="Z8" t="n">
-        <v>347.9200000000001</v>
+        <v>4058.707393125731</v>
       </c>
       <c r="AA8" t="n">
         <v>1.00000000000002e-08</v>
@@ -8568,10 +8306,8 @@
       <c r="K9" t="n">
         <v>84.89718462789831</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 11.199x + -38188.370</t>
-        </is>
+      <c r="W9" t="n">
+        <v>11.1985655017525</v>
       </c>
       <c r="X9" t="n">
         <v>-38188.37004848402</v>
@@ -8580,7 +8316,7 @@
         <v>2.833478426214852e-10</v>
       </c>
       <c r="Z9" t="n">
-        <v>333.4499999999998</v>
+        <v>4018.348495702831</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000001e-08</v>
@@ -8620,10 +8356,8 @@
       <c r="K10" t="n">
         <v>85.00845129189244</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 11.450x + -38699.499</t>
-        </is>
+      <c r="W10" t="n">
+        <v>11.44950327344338</v>
       </c>
       <c r="X10" t="n">
         <v>-38699.49919989831</v>
@@ -8632,7 +8366,7 @@
         <v>9.68213434659183e-10</v>
       </c>
       <c r="Z10" t="n">
-        <v>314.9200000000001</v>
+        <v>3979.448659800326</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000085e-08</v>
@@ -8672,10 +8406,8 @@
       <c r="K11" t="n">
         <v>85.47555092902752</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 12.637x + -42607.690</t>
-        </is>
+      <c r="W11" t="n">
+        <v>12.63725941556235</v>
       </c>
       <c r="X11" t="n">
         <v>-42607.68993200607</v>
@@ -8684,7 +8416,7 @@
         <v>4.606741513217921e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>302.71</v>
+        <v>3942.416923180658</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000684e-08</v>
@@ -8724,10 +8456,8 @@
       <c r="K12" t="n">
         <v>85.09978255247546</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 11.664x + -38767.251</t>
-        </is>
+      <c r="W12" t="n">
+        <v>11.66397512784265</v>
       </c>
       <c r="X12" t="n">
         <v>-38767.25062149622</v>
@@ -8736,7 +8466,7 @@
         <v>1.178383808251198e-09</v>
       </c>
       <c r="Z12" t="n">
-        <v>309.5599999999999</v>
+        <v>3906.229744126156</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000000049e-08</v>
@@ -8776,10 +8506,8 @@
       <c r="K13" t="n">
         <v>85.12143442605102</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 11.716x + -38598.697</t>
-        </is>
+      <c r="W13" t="n">
+        <v>11.71599449655293</v>
       </c>
       <c r="X13" t="n">
         <v>-38598.69676550315</v>
@@ -8788,7 +8516,7 @@
         <v>5.377195440529159e-10</v>
       </c>
       <c r="Z13" t="n">
-        <v>303.48</v>
+        <v>3871.158020146187</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000001256e-08</v>
@@ -8828,10 +8556,8 @@
       <c r="K14" t="n">
         <v>85.15949670657041</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 11.809x + -38582.039</t>
-        </is>
+      <c r="W14" t="n">
+        <v>11.8085658002754</v>
       </c>
       <c r="X14" t="n">
         <v>-38582.03856828791</v>
@@ -8840,7 +8566,7 @@
         <v>3.169718704593535e-10</v>
       </c>
       <c r="Z14" t="n">
-        <v>305.6400000000003</v>
+        <v>3835.989998949466</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000017186e-08</v>
@@ -8880,10 +8606,8 @@
       <c r="K15" t="n">
         <v>85.1690390181186</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 11.832x + -38317.353</t>
-        </is>
+      <c r="W15" t="n">
+        <v>11.83200180715637</v>
       </c>
       <c r="X15" t="n">
         <v>-38317.35342556189</v>
@@ -8892,7 +8616,7 @@
         <v>5.163221658958326e-11</v>
       </c>
       <c r="Z15" t="n">
-        <v>288.9499999999998</v>
+        <v>3801.152867077442</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000000045e-08</v>
@@ -8932,10 +8656,8 @@
       <c r="K16" t="n">
         <v>85.25589780456357</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 12.050x + -38702.062</t>
-        </is>
+      <c r="W16" t="n">
+        <v>12.04965233268006</v>
       </c>
       <c r="X16" t="n">
         <v>-38702.06183167682</v>
@@ -8944,7 +8666,7 @@
         <v>4.324637531563735e-12</v>
       </c>
       <c r="Z16" t="n">
-        <v>279.8800000000001</v>
+        <v>3765.866408940889</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000082e-08</v>
@@ -8984,10 +8706,8 @@
       <c r="K17" t="n">
         <v>85.23136093573883</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 11.987x + -38150.214</t>
-        </is>
+      <c r="W17" t="n">
+        <v>11.98736623285835</v>
       </c>
       <c r="X17" t="n">
         <v>-38150.21430726999</v>
@@ -8996,7 +8716,7 @@
         <v>1.985192077426656e-08</v>
       </c>
       <c r="Z17" t="n">
-        <v>279.0299999999997</v>
+        <v>3730.377770053432</v>
       </c>
       <c r="AA17" t="n">
         <v>1.00000000000952e-08</v>
@@ -9036,10 +8756,8 @@
       <c r="K18" t="n">
         <v>85.34760129178245</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 12.288x + -38798.014</t>
-        </is>
+      <c r="W18" t="n">
+        <v>12.28824167717495</v>
       </c>
       <c r="X18" t="n">
         <v>-38798.01367035966</v>
@@ -9048,7 +8766,7 @@
         <v>2.0944098674368e-14</v>
       </c>
       <c r="Z18" t="n">
-        <v>275.1999999999998</v>
+        <v>3696.0770156904</v>
       </c>
       <c r="AA18" t="n">
         <v>1e-08</v>
@@ -9088,10 +8806,8 @@
       <c r="K19" t="n">
         <v>85.34220099001631</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 12.274x + -38375.936</t>
-        </is>
+      <c r="W19" t="n">
+        <v>12.27393170467297</v>
       </c>
       <c r="X19" t="n">
         <v>-38375.93558057064</v>
@@ -9100,7 +8816,7 @@
         <v>4.382033804628565e-11</v>
       </c>
       <c r="Z19" t="n">
-        <v>265.9000000000001</v>
+        <v>3659.739763347086</v>
       </c>
       <c r="AA19" t="n">
         <v>1.00000000000003e-08</v>
@@ -9140,10 +8856,8 @@
       <c r="K20" t="n">
         <v>85.37319319370786</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 12.357x + -38286.030</t>
-        </is>
+      <c r="W20" t="n">
+        <v>12.35650954682889</v>
       </c>
       <c r="X20" t="n">
         <v>-38286.0299618542</v>
@@ -9152,7 +8866,7 @@
         <v>1.270549332805959e-09</v>
       </c>
       <c r="Z20" t="n">
-        <v>263.2999999999997</v>
+        <v>3623.718649918355</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000001719e-08</v>
@@ -9192,10 +8906,8 @@
       <c r="K21" t="n">
         <v>85.36996510611868</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 12.348x + -37899.951</t>
-        </is>
+      <c r="W21" t="n">
+        <v>12.34785693550832</v>
       </c>
       <c r="X21" t="n">
         <v>-37899.95117546595</v>
@@ -9204,7 +8916,7 @@
         <v>9.953075358001483e-09</v>
       </c>
       <c r="Z21" t="n">
-        <v>252.2999999999997</v>
+        <v>3589.402565469917</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000000005e-08</v>
@@ -9244,10 +8956,8 @@
       <c r="K22" t="n">
         <v>84.9717545413131</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 11.366x + -34370.340</t>
-        </is>
+      <c r="W22" t="n">
+        <v>11.3655175355196</v>
       </c>
       <c r="X22" t="n">
         <v>-34370.34040002357</v>
@@ -9256,7 +8966,7 @@
         <v>2.31220898286965e-10</v>
       </c>
       <c r="Z22" t="n">
-        <v>263.6400000000003</v>
+        <v>3554.157447565878</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000035e-08</v>
@@ -9382,12 +9092,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -9442,10 +9152,8 @@
       <c r="K2" t="n">
         <v>83.3873129477326</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 8.626x + -30076.130</t>
-        </is>
+      <c r="W2" t="n">
+        <v>8.626017809074218</v>
       </c>
       <c r="X2" t="n">
         <v>-30076.12992159559</v>
@@ -9454,7 +9162,7 @@
         <v>2.548767816972464e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>552.7600000000002</v>
+        <v>3931.3295098559</v>
       </c>
       <c r="AA2" t="n">
         <v>1.00000000000951e-08</v>
@@ -9494,10 +9202,8 @@
       <c r="K3" t="n">
         <v>84.69149544565077</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 10.762x + -30940.692</t>
-        </is>
+      <c r="W3" t="n">
+        <v>10.76230398801983</v>
       </c>
       <c r="X3" t="n">
         <v>-30940.69225926958</v>
@@ -9506,7 +9212,7 @@
         <v>2.064013584503895e-11</v>
       </c>
       <c r="Z3" t="n">
-        <v>352.4099999999999</v>
+        <v>3330.341443771282</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000087e-08</v>
@@ -9546,10 +9252,8 @@
       <c r="K4" t="n">
         <v>85.48198616993866</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 12.655x + -35044.184</t>
-        </is>
+      <c r="W4" t="n">
+        <v>12.65533431116263</v>
       </c>
       <c r="X4" t="n">
         <v>-35044.1838767528</v>
@@ -9558,7 +9262,7 @@
         <v>2.600304056244478e-11</v>
       </c>
       <c r="Z4" t="n">
-        <v>283.5999999999999</v>
+        <v>3198.773498650586</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000259e-08</v>
@@ -9598,10 +9302,8 @@
       <c r="K5" t="n">
         <v>85.22762894081315</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 11.978x + -32359.745</t>
-        </is>
+      <c r="W5" t="n">
+        <v>11.97794866364626</v>
       </c>
       <c r="X5" t="n">
         <v>-32359.74514723961</v>
@@ -9610,7 +9312,7 @@
         <v>1.624150959028984e-12</v>
       </c>
       <c r="Z5" t="n">
-        <v>266.4499999999998</v>
+        <v>3137.91765451105</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000114e-08</v>
@@ -9650,10 +9352,8 @@
       <c r="K6" t="n">
         <v>85.30778033946123</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 12.183x + -32436.802</t>
-        </is>
+      <c r="W6" t="n">
+        <v>12.18349460640757</v>
       </c>
       <c r="X6" t="n">
         <v>-32436.80238746237</v>
@@ -9662,7 +9362,7 @@
         <v>6.237155215073255e-14</v>
       </c>
       <c r="Z6" t="n">
-        <v>254.9200000000001</v>
+        <v>3090.404222545536</v>
       </c>
       <c r="AA6" t="n">
         <v>1e-08</v>
@@ -9702,10 +9402,8 @@
       <c r="K7" t="n">
         <v>85.01786830514428</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 11.471x + -29990.228</t>
-        </is>
+      <c r="W7" t="n">
+        <v>11.47125442352901</v>
       </c>
       <c r="X7" t="n">
         <v>-29990.2279741978</v>
@@ -9714,7 +9412,7 @@
         <v>1.873052751754583e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>259.3099999999999</v>
+        <v>3045.549785816086</v>
       </c>
       <c r="AA7" t="n">
         <v>1e-08</v>
@@ -9754,10 +9452,8 @@
       <c r="K8" t="n">
         <v>85.40923540709269</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 12.454x + -32245.915</t>
-        </is>
+      <c r="W8" t="n">
+        <v>12.4539422077933</v>
       </c>
       <c r="X8" t="n">
         <v>-32245.91517107652</v>
@@ -9766,7 +9462,7 @@
         <v>4.072263196839266e-11</v>
       </c>
       <c r="Z8" t="n">
-        <v>240.0099999999998</v>
+        <v>3000.177687131686</v>
       </c>
       <c r="AA8" t="n">
         <v>1e-08</v>
@@ -9806,10 +9502,8 @@
       <c r="K9" t="n">
         <v>85.46060189716655</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 12.595x + -32172.309</t>
-        </is>
+      <c r="W9" t="n">
+        <v>12.59546891167583</v>
       </c>
       <c r="X9" t="n">
         <v>-32172.30905325947</v>
@@ -9818,7 +9512,7 @@
         <v>1.575618300636622e-12</v>
       </c>
       <c r="Z9" t="n">
-        <v>231.9200000000001</v>
+        <v>2955.778520537724</v>
       </c>
       <c r="AA9" t="n">
         <v>1e-08</v>
@@ -9858,10 +9552,8 @@
       <c r="K10" t="n">
         <v>85.45998958481565</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 12.594x + -31717.814</t>
-        </is>
+      <c r="W10" t="n">
+        <v>12.59376302753793</v>
       </c>
       <c r="X10" t="n">
         <v>-31717.81379658414</v>
@@ -9870,7 +9562,7 @@
         <v>4.067180711400814e-10</v>
       </c>
       <c r="Z10" t="n">
-        <v>233.2599999999998</v>
+        <v>2913.40211426387</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000055e-08</v>
@@ -9910,10 +9602,8 @@
       <c r="K11" t="n">
         <v>85.17558684606576</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 11.848x + -29321.329</t>
-        </is>
+      <c r="W11" t="n">
+        <v>11.84813684104621</v>
       </c>
       <c r="X11" t="n">
         <v>-29321.32910393714</v>
@@ -9922,7 +9612,7 @@
         <v>9.396591062440979e-10</v>
       </c>
       <c r="Z11" t="n">
-        <v>239.3999999999996</v>
+        <v>2873.572204780687</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000047e-08</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 22.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 22.xlsx
@@ -428,7 +428,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -559,7 +559,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-483.7100000000005</v>
@@ -609,7 +609,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-449.0000000000005</v>
@@ -659,7 +659,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-422.46</v>
@@ -709,7 +709,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-429.4099999999999</v>
@@ -759,7 +759,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-377.4799999999996</v>
@@ -809,7 +809,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-390.5</v>
@@ -859,7 +859,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-361.0999999999999</v>
@@ -909,7 +909,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-355.0099999999998</v>
@@ -959,7 +959,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-333.2200000000003</v>
@@ -1009,7 +1009,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-340.9900000000002</v>
@@ -1074,7 +1074,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -2270,7 +2270,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -3466,7 +3466,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -3597,7 +3597,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-605.8199999999997</v>
@@ -3647,7 +3647,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-435.6900000000001</v>
@@ -3697,7 +3697,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-414.4700000000003</v>
@@ -3747,7 +3747,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-375.0100000000002</v>
@@ -3797,7 +3797,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-360.1699999999996</v>
@@ -3847,7 +3847,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-344.8600000000001</v>
@@ -3897,7 +3897,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-331.1700000000001</v>
@@ -3947,7 +3947,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-319.9399999999996</v>
@@ -3997,7 +3997,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-307.6500000000001</v>
@@ -4047,7 +4047,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-296.0500000000002</v>
@@ -4112,7 +4112,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -5308,7 +5308,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -5439,7 +5439,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-646.7700000000004</v>
@@ -5489,7 +5489,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-437.29</v>
@@ -5539,7 +5539,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-402.73</v>
@@ -5589,7 +5589,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-380.4199999999996</v>
@@ -5639,7 +5639,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-346.2800000000002</v>
@@ -5689,7 +5689,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-335.6100000000001</v>
@@ -5739,7 +5739,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-331.1100000000001</v>
@@ -5789,7 +5789,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-316.52</v>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-308.8400000000001</v>
@@ -5889,7 +5889,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-318.1900000000001</v>
@@ -5954,7 +5954,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -7150,7 +7150,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -7281,7 +7281,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-705.1000000000004</v>
@@ -7331,7 +7331,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-486.6899999999996</v>
@@ -7381,7 +7381,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-411.7999999999997</v>
@@ -7431,7 +7431,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-399.8800000000001</v>
@@ -7481,7 +7481,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-362.1199999999999</v>
@@ -7531,7 +7531,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-368.5</v>
@@ -7581,7 +7581,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-327.96</v>
@@ -7631,7 +7631,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-338.6500000000001</v>
@@ -7681,7 +7681,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-325.04</v>
@@ -7731,7 +7731,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-311</v>
@@ -7796,7 +7796,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -8992,7 +8992,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -9123,7 +9123,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-552.7600000000002</v>
@@ -9173,7 +9173,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-352.4099999999999</v>
@@ -9223,7 +9223,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-283.5999999999999</v>
@@ -9273,7 +9273,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-266.4499999999998</v>
@@ -9323,7 +9323,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-254.9200000000001</v>
@@ -9373,7 +9373,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-259.3099999999999</v>
@@ -9423,7 +9423,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-240.0099999999998</v>
@@ -9473,7 +9473,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-231.9200000000001</v>
@@ -9523,7 +9523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-227.3999999999996</v>
@@ -9573,7 +9573,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-229.7799999999997</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 22.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 22.xlsx
@@ -562,7 +562,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-483.7100000000005</v>
+        <v>3852.46</v>
       </c>
       <c r="D2" t="n">
         <v>1.71082e-07</v>
@@ -612,7 +612,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-449.0000000000005</v>
+        <v>3790.98</v>
       </c>
       <c r="D3" t="n">
         <v>1.73367e-07</v>
@@ -662,7 +662,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-422.46</v>
+        <v>3729.496</v>
       </c>
       <c r="D4" t="n">
         <v>1.75642e-07</v>
@@ -712,7 +712,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-429.4099999999999</v>
+        <v>3624.505</v>
       </c>
       <c r="D5" t="n">
         <v>1.78341e-07</v>
@@ -762,7 +762,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-377.4799999999996</v>
+        <v>3578.594</v>
       </c>
       <c r="D6" t="n">
         <v>1.81055e-07</v>
@@ -812,7 +812,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-390.5</v>
+        <v>3467.432</v>
       </c>
       <c r="D7" t="n">
         <v>1.83885e-07</v>
@@ -862,7 +862,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-361.0999999999999</v>
+        <v>3395.408</v>
       </c>
       <c r="D8" t="n">
         <v>1.86813e-07</v>
@@ -912,7 +912,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-355.0099999999998</v>
+        <v>3319.295</v>
       </c>
       <c r="D9" t="n">
         <v>1.89274e-07</v>
@@ -962,7 +962,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-333.2200000000003</v>
+        <v>3249.987</v>
       </c>
       <c r="D10" t="n">
         <v>1.91901e-07</v>
@@ -1012,7 +1012,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-340.9900000000002</v>
+        <v>3159.553</v>
       </c>
       <c r="D11" t="n">
         <v>1.94336e-07</v>
@@ -1208,7 +1208,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-409.4700000000003</v>
+        <v>3678.332</v>
       </c>
       <c r="D2" t="n">
         <v>1.7639e-07</v>
@@ -1258,7 +1258,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-360.3799999999997</v>
+        <v>3506.666</v>
       </c>
       <c r="D3" t="n">
         <v>1.8282e-07</v>
@@ -1308,7 +1308,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-335.9900000000002</v>
+        <v>3437.748</v>
       </c>
       <c r="D4" t="n">
         <v>1.85578e-07</v>
@@ -1358,7 +1358,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-345.1599999999999</v>
+        <v>3359.498</v>
       </c>
       <c r="D5" t="n">
         <v>1.87738e-07</v>
@@ -1408,7 +1408,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-313.6300000000001</v>
+        <v>3339.811</v>
       </c>
       <c r="D6" t="n">
         <v>1.89258e-07</v>
@@ -1458,7 +1458,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-297.6399999999999</v>
+        <v>3304.196</v>
       </c>
       <c r="D7" t="n">
         <v>1.90869e-07</v>
@@ -1508,7 +1508,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-290.73</v>
+        <v>3267.329</v>
       </c>
       <c r="D8" t="n">
         <v>1.92183e-07</v>
@@ -1558,7 +1558,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-303.5900000000001</v>
+        <v>3212.279</v>
       </c>
       <c r="D9" t="n">
         <v>1.93504e-07</v>
@@ -1608,7 +1608,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-273.7900000000004</v>
+        <v>3196.691</v>
       </c>
       <c r="D10" t="n">
         <v>1.94873e-07</v>
@@ -1658,7 +1658,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-269.8900000000003</v>
+        <v>3160.866</v>
       </c>
       <c r="D11" t="n">
         <v>1.96086e-07</v>
@@ -1708,7 +1708,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-281.27</v>
+        <v>3102.288</v>
       </c>
       <c r="D12" t="n">
         <v>1.97487e-07</v>
@@ -1758,7 +1758,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-253.4699999999998</v>
+        <v>3091.035</v>
       </c>
       <c r="D13" t="n">
         <v>1.98728e-07</v>
@@ -1808,7 +1808,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-240.7399999999998</v>
+        <v>3061.303</v>
       </c>
       <c r="D14" t="n">
         <v>2.00064e-07</v>
@@ -1858,7 +1858,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-257.02</v>
+        <v>3006.722</v>
       </c>
       <c r="D15" t="n">
         <v>2.01331e-07</v>
@@ -1908,7 +1908,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-264.25</v>
+        <v>2955.034</v>
       </c>
       <c r="D16" t="n">
         <v>2.02546e-07</v>
@@ -1958,7 +1958,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-224.6799999999998</v>
+        <v>2955.911</v>
       </c>
       <c r="D17" t="n">
         <v>2.03775e-07</v>
@@ -2008,7 +2008,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-235.96</v>
+        <v>2905.613</v>
       </c>
       <c r="D18" t="n">
         <v>2.05031e-07</v>
@@ -2058,7 +2058,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-225.79</v>
+        <v>2872.563</v>
       </c>
       <c r="D19" t="n">
         <v>2.06361e-07</v>
@@ -2108,7 +2108,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-226.0299999999997</v>
+        <v>2839.418</v>
       </c>
       <c r="D20" t="n">
         <v>2.07254e-07</v>
@@ -2158,7 +2158,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-210.98</v>
+        <v>2813.507</v>
       </c>
       <c r="D21" t="n">
         <v>2.08796e-07</v>
@@ -2208,7 +2208,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-209.3600000000001</v>
+        <v>2779.263</v>
       </c>
       <c r="D22" t="n">
         <v>2.09799e-07</v>
@@ -2404,7 +2404,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-496.1800000000003</v>
+        <v>3744.922</v>
       </c>
       <c r="D2" t="n">
         <v>1.72399e-07</v>
@@ -2454,7 +2454,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-425.27</v>
+        <v>3569.268</v>
       </c>
       <c r="D3" t="n">
         <v>1.79549e-07</v>
@@ -2504,7 +2504,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-395.9499999999998</v>
+        <v>3493.123</v>
       </c>
       <c r="D4" t="n">
         <v>1.82536e-07</v>
@@ -2554,7 +2554,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-386.8200000000002</v>
+        <v>3445.376</v>
       </c>
       <c r="D5" t="n">
         <v>1.8412e-07</v>
@@ -2604,7 +2604,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-361.3499999999999</v>
+        <v>3406.698</v>
       </c>
       <c r="D6" t="n">
         <v>1.86066e-07</v>
@@ -2654,7 +2654,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-353.3299999999999</v>
+        <v>3361.387</v>
       </c>
       <c r="D7" t="n">
         <v>1.87424e-07</v>
@@ -2704,7 +2704,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-348.3800000000001</v>
+        <v>3319.906</v>
       </c>
       <c r="D8" t="n">
         <v>1.88632e-07</v>
@@ -2754,7 +2754,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-338.5599999999999</v>
+        <v>3283.179</v>
       </c>
       <c r="D9" t="n">
         <v>1.90074e-07</v>
@@ -2804,7 +2804,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-336.5999999999999</v>
+        <v>3245.033</v>
       </c>
       <c r="D10" t="n">
         <v>1.91118e-07</v>
@@ -2854,7 +2854,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-320.25</v>
+        <v>3209.143</v>
       </c>
       <c r="D11" t="n">
         <v>1.92627e-07</v>
@@ -2904,7 +2904,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-341.8000000000002</v>
+        <v>3150.149</v>
       </c>
       <c r="D12" t="n">
         <v>1.93583e-07</v>
@@ -2954,7 +2954,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-322.6900000000001</v>
+        <v>3121.904</v>
       </c>
       <c r="D13" t="n">
         <v>1.94953e-07</v>
@@ -3004,7 +3004,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-320.6099999999997</v>
+        <v>3085.339</v>
       </c>
       <c r="D14" t="n">
         <v>1.96063e-07</v>
@@ -3054,7 +3054,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-309.96</v>
+        <v>3056.301</v>
       </c>
       <c r="D15" t="n">
         <v>1.9725e-07</v>
@@ -3104,7 +3104,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-311.2799999999997</v>
+        <v>3021.043</v>
       </c>
       <c r="D16" t="n">
         <v>1.9827e-07</v>
@@ -3154,7 +3154,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-296.6699999999996</v>
+        <v>2988.04</v>
       </c>
       <c r="D17" t="n">
         <v>1.99642e-07</v>
@@ -3204,7 +3204,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-295.4400000000001</v>
+        <v>2955.594</v>
       </c>
       <c r="D18" t="n">
         <v>2.00614e-07</v>
@@ -3254,7 +3254,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-281.9299999999998</v>
+        <v>2923.937</v>
       </c>
       <c r="D19" t="n">
         <v>2.01951e-07</v>
@@ -3304,7 +3304,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-276.9900000000002</v>
+        <v>2889.878</v>
       </c>
       <c r="D20" t="n">
         <v>2.02908e-07</v>
@@ -3354,7 +3354,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-251</v>
+        <v>2880.713</v>
       </c>
       <c r="D21" t="n">
         <v>2.03928e-07</v>
@@ -3404,7 +3404,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-260.2199999999998</v>
+        <v>2830.395</v>
       </c>
       <c r="D22" t="n">
         <v>2.0524e-07</v>
@@ -3600,7 +3600,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-605.8199999999997</v>
+        <v>4525.086</v>
       </c>
       <c r="D2" t="n">
         <v>1.48052e-07</v>
@@ -3650,7 +3650,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-435.6900000000001</v>
+        <v>3853.317</v>
       </c>
       <c r="D3" t="n">
         <v>1.72127e-07</v>
@@ -3700,7 +3700,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-414.4700000000003</v>
+        <v>3670.807</v>
       </c>
       <c r="D4" t="n">
         <v>1.78213e-07</v>
@@ -3750,7 +3750,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-375.0100000000002</v>
+        <v>3602.979</v>
       </c>
       <c r="D5" t="n">
         <v>1.81295e-07</v>
@@ -3800,7 +3800,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-360.1699999999996</v>
+        <v>3549.37</v>
       </c>
       <c r="D6" t="n">
         <v>1.83132e-07</v>
@@ -3850,7 +3850,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-344.8600000000001</v>
+        <v>3496.687</v>
       </c>
       <c r="D7" t="n">
         <v>1.8503e-07</v>
@@ -3900,7 +3900,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-331.1700000000001</v>
+        <v>3449.656</v>
       </c>
       <c r="D8" t="n">
         <v>1.86653e-07</v>
@@ -3950,7 +3950,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-319.9399999999996</v>
+        <v>3403.369</v>
       </c>
       <c r="D9" t="n">
         <v>1.88258e-07</v>
@@ -4000,7 +4000,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-307.6500000000001</v>
+        <v>3357.19</v>
       </c>
       <c r="D10" t="n">
         <v>1.899e-07</v>
@@ -4050,7 +4050,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-296.0500000000002</v>
+        <v>3322.173</v>
       </c>
       <c r="D11" t="n">
         <v>1.91233e-07</v>
@@ -4246,7 +4246,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-497.1500000000001</v>
+        <v>3708.864</v>
       </c>
       <c r="D2" t="n">
         <v>1.7404e-07</v>
@@ -4296,7 +4296,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-396.6900000000005</v>
+        <v>3504.058</v>
       </c>
       <c r="D3" t="n">
         <v>1.82955e-07</v>
@@ -4346,7 +4346,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-361.98</v>
+        <v>3442.693</v>
       </c>
       <c r="D4" t="n">
         <v>1.85643e-07</v>
@@ -4396,7 +4396,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-346.9000000000001</v>
+        <v>3394.1</v>
       </c>
       <c r="D5" t="n">
         <v>1.8734e-07</v>
@@ -4446,7 +4446,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-338.8599999999997</v>
+        <v>3351.124</v>
       </c>
       <c r="D6" t="n">
         <v>1.88693e-07</v>
@@ -4496,7 +4496,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-325.96</v>
+        <v>3312.95</v>
       </c>
       <c r="D7" t="n">
         <v>1.90111e-07</v>
@@ -4546,7 +4546,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-314.98</v>
+        <v>3273.829</v>
       </c>
       <c r="D8" t="n">
         <v>1.91563e-07</v>
@@ -4596,7 +4596,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-313.9400000000001</v>
+        <v>3232.236</v>
       </c>
       <c r="D9" t="n">
         <v>1.92749e-07</v>
@@ -4646,7 +4646,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-302.6700000000001</v>
+        <v>3195.427</v>
       </c>
       <c r="D10" t="n">
         <v>1.94136e-07</v>
@@ -4696,7 +4696,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-315.7999999999997</v>
+        <v>3138.272</v>
       </c>
       <c r="D11" t="n">
         <v>1.95373e-07</v>
@@ -4746,7 +4746,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-309.4000000000001</v>
+        <v>3100.293</v>
       </c>
       <c r="D12" t="n">
         <v>1.96646e-07</v>
@@ -4796,7 +4796,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-277.54</v>
+        <v>3092.473</v>
       </c>
       <c r="D13" t="n">
         <v>1.97745e-07</v>
@@ -4846,7 +4846,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-294.5899999999997</v>
+        <v>3039.591</v>
       </c>
       <c r="D14" t="n">
         <v>1.98762e-07</v>
@@ -4896,7 +4896,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-288.9499999999998</v>
+        <v>3006.895</v>
       </c>
       <c r="D15" t="n">
         <v>1.99886e-07</v>
@@ -4946,7 +4946,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-256.2600000000002</v>
+        <v>2998.568</v>
       </c>
       <c r="D16" t="n">
         <v>2.01107e-07</v>
@@ -4996,7 +4996,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-273.6300000000001</v>
+        <v>2947.304</v>
       </c>
       <c r="D17" t="n">
         <v>2.02057e-07</v>
@@ -5046,7 +5046,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-270.6599999999999</v>
+        <v>2916.959</v>
       </c>
       <c r="D18" t="n">
         <v>2.02991e-07</v>
@@ -5096,7 +5096,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-261.96</v>
+        <v>2888.634</v>
       </c>
       <c r="D19" t="n">
         <v>2.04096e-07</v>
@@ -5146,7 +5146,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-252.54</v>
+        <v>2860.76</v>
       </c>
       <c r="D20" t="n">
         <v>2.05255e-07</v>
@@ -5196,7 +5196,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-241.21</v>
+        <v>2833.797</v>
       </c>
       <c r="D21" t="n">
         <v>2.06397e-07</v>
@@ -5246,7 +5246,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-235.9699999999998</v>
+        <v>2807.645</v>
       </c>
       <c r="D22" t="n">
         <v>2.075e-07</v>
@@ -5442,7 +5442,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-646.7700000000004</v>
+        <v>4459.268</v>
       </c>
       <c r="D2" t="n">
         <v>1.48884e-07</v>
@@ -5492,7 +5492,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-437.29</v>
+        <v>3814.951</v>
       </c>
       <c r="D3" t="n">
         <v>1.73239e-07</v>
@@ -5542,7 +5542,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-402.73</v>
+        <v>3645.149</v>
       </c>
       <c r="D4" t="n">
         <v>1.79275e-07</v>
@@ -5592,7 +5592,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-380.4199999999996</v>
+        <v>3577.913</v>
       </c>
       <c r="D5" t="n">
         <v>1.81596e-07</v>
@@ -5642,7 +5642,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-346.2800000000002</v>
+        <v>3525.562</v>
       </c>
       <c r="D6" t="n">
         <v>1.84015e-07</v>
@@ -5692,7 +5692,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-335.6100000000001</v>
+        <v>3478.255</v>
       </c>
       <c r="D7" t="n">
         <v>1.85589e-07</v>
@@ -5742,7 +5742,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-331.1100000000001</v>
+        <v>3422.936</v>
       </c>
       <c r="D8" t="n">
         <v>1.87196e-07</v>
@@ -5792,7 +5792,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-316.52</v>
+        <v>3377.946</v>
       </c>
       <c r="D9" t="n">
         <v>1.88975e-07</v>
@@ -5842,7 +5842,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-308.8400000000001</v>
+        <v>3332.78</v>
       </c>
       <c r="D10" t="n">
         <v>1.90513e-07</v>
@@ -5892,7 +5892,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-318.1900000000001</v>
+        <v>3269.662</v>
       </c>
       <c r="D11" t="n">
         <v>1.92177e-07</v>
@@ -6088,7 +6088,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-442.3800000000001</v>
+        <v>3717.902</v>
       </c>
       <c r="D2" t="n">
         <v>1.75491e-07</v>
@@ -6138,7 +6138,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-374.9000000000001</v>
+        <v>3496.819</v>
       </c>
       <c r="D3" t="n">
         <v>1.83769e-07</v>
@@ -6188,7 +6188,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-344.0300000000002</v>
+        <v>3434.181</v>
       </c>
       <c r="D4" t="n">
         <v>1.86394e-07</v>
@@ -6238,7 +6238,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-352.1500000000001</v>
+        <v>3365.52</v>
       </c>
       <c r="D5" t="n">
         <v>1.88149e-07</v>
@@ -6288,7 +6288,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-317.3000000000002</v>
+        <v>3347.718</v>
       </c>
       <c r="D6" t="n">
         <v>1.89596e-07</v>
@@ -6338,7 +6338,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-302.0599999999999</v>
+        <v>3310.858</v>
       </c>
       <c r="D7" t="n">
         <v>1.91017e-07</v>
@@ -6388,7 +6388,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-298.8500000000004</v>
+        <v>3277.431</v>
       </c>
       <c r="D8" t="n">
         <v>1.92212e-07</v>
@@ -6438,7 +6438,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-313.2399999999998</v>
+        <v>3221.451</v>
       </c>
       <c r="D9" t="n">
         <v>1.93405e-07</v>
@@ -6488,7 +6488,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-288.8299999999999</v>
+        <v>3212.682</v>
       </c>
       <c r="D10" t="n">
         <v>1.94314e-07</v>
@@ -6538,7 +6538,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-277.3600000000001</v>
+        <v>3181.648</v>
       </c>
       <c r="D11" t="n">
         <v>1.95722e-07</v>
@@ -6588,7 +6588,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-287.6700000000001</v>
+        <v>3134.152</v>
       </c>
       <c r="D12" t="n">
         <v>1.96823e-07</v>
@@ -6638,7 +6638,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-282.02</v>
+        <v>3108.108</v>
       </c>
       <c r="D13" t="n">
         <v>1.97715e-07</v>
@@ -6688,7 +6688,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-254.0799999999999</v>
+        <v>3097.531</v>
       </c>
       <c r="D14" t="n">
         <v>1.98851e-07</v>
@@ -6738,7 +6738,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-264.77</v>
+        <v>3052.9</v>
       </c>
       <c r="D15" t="n">
         <v>1.99831e-07</v>
@@ -6788,7 +6788,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-242.3099999999999</v>
+        <v>3041.708</v>
       </c>
       <c r="D16" t="n">
         <v>2.00891e-07</v>
@@ -6838,7 +6838,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-236.7600000000002</v>
+        <v>3013.689</v>
       </c>
       <c r="D17" t="n">
         <v>2.01834e-07</v>
@@ -6888,7 +6888,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-248.9699999999998</v>
+        <v>2964.158</v>
       </c>
       <c r="D18" t="n">
         <v>2.02906e-07</v>
@@ -6938,7 +6938,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-240</v>
+        <v>2935.224</v>
       </c>
       <c r="D19" t="n">
         <v>2.04115e-07</v>
@@ -6988,7 +6988,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-237.8499999999999</v>
+        <v>2902.99</v>
       </c>
       <c r="D20" t="n">
         <v>2.05174e-07</v>
@@ -7038,7 +7038,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-230.1399999999999</v>
+        <v>2874.349</v>
       </c>
       <c r="D21" t="n">
         <v>2.06385e-07</v>
@@ -7088,7 +7088,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-236.3099999999999</v>
+        <v>2833.017</v>
       </c>
       <c r="D22" t="n">
         <v>2.07473e-07</v>
@@ -7284,7 +7284,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-705.1000000000004</v>
+        <v>4270.356</v>
       </c>
       <c r="D2" t="n">
         <v>1.52123e-07</v>
@@ -7334,7 +7334,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-486.6899999999996</v>
+        <v>3598.002</v>
       </c>
       <c r="D3" t="n">
         <v>1.76576e-07</v>
@@ -7384,7 +7384,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-411.7999999999997</v>
+        <v>3454.311</v>
       </c>
       <c r="D4" t="n">
         <v>1.8188e-07</v>
@@ -7434,7 +7434,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-399.8800000000001</v>
+        <v>3362.022</v>
       </c>
       <c r="D5" t="n">
         <v>1.83869e-07</v>
@@ -7484,7 +7484,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-362.1199999999999</v>
+        <v>3325.986</v>
       </c>
       <c r="D6" t="n">
         <v>1.8523e-07</v>
@@ -7534,7 +7534,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-368.5</v>
+        <v>3252.983</v>
       </c>
       <c r="D7" t="n">
         <v>1.86485e-07</v>
@@ -7584,7 +7584,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-327.96</v>
+        <v>3226.471</v>
       </c>
       <c r="D8" t="n">
         <v>1.87917e-07</v>
@@ -7634,7 +7634,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-338.6500000000001</v>
+        <v>3154.382</v>
       </c>
       <c r="D9" t="n">
         <v>1.89215e-07</v>
@@ -7684,7 +7684,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-325.04</v>
+        <v>3105.243</v>
       </c>
       <c r="D10" t="n">
         <v>1.9051e-07</v>
@@ -7734,7 +7734,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-311</v>
+        <v>3061.703</v>
       </c>
       <c r="D11" t="n">
         <v>1.91838e-07</v>
@@ -7930,7 +7930,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-493.6099999999997</v>
+        <v>3618.313</v>
       </c>
       <c r="D2" t="n">
         <v>1.73994e-07</v>
@@ -7980,7 +7980,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-386.9099999999999</v>
+        <v>3421.174</v>
       </c>
       <c r="D3" t="n">
         <v>1.82652e-07</v>
@@ -8030,7 +8030,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-383.71</v>
+        <v>3329.567</v>
       </c>
       <c r="D4" t="n">
         <v>1.85529e-07</v>
@@ -8080,7 +8080,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-339.3299999999999</v>
+        <v>3307.411</v>
       </c>
       <c r="D5" t="n">
         <v>1.87585e-07</v>
@@ -8130,7 +8130,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-360.48</v>
+        <v>3244.448</v>
       </c>
       <c r="D6" t="n">
         <v>1.88969e-07</v>
@@ -8180,7 +8180,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-344.9500000000003</v>
+        <v>3211.31</v>
       </c>
       <c r="D7" t="n">
         <v>1.90505e-07</v>
@@ -8230,7 +8230,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-347.9200000000001</v>
+        <v>3177.596</v>
       </c>
       <c r="D8" t="n">
         <v>1.91511e-07</v>
@@ -8280,7 +8280,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-333.4499999999998</v>
+        <v>3144.322</v>
       </c>
       <c r="D9" t="n">
         <v>1.9295e-07</v>
@@ -8330,7 +8330,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-314.9200000000001</v>
+        <v>3119.191</v>
       </c>
       <c r="D10" t="n">
         <v>1.94419e-07</v>
@@ -8380,7 +8380,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-302.71</v>
+        <v>3105.89</v>
       </c>
       <c r="D11" t="n">
         <v>1.95185e-07</v>
@@ -8430,7 +8430,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-309.5599999999999</v>
+        <v>3058.819</v>
       </c>
       <c r="D12" t="n">
         <v>1.96328e-07</v>
@@ -8480,7 +8480,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-303.48</v>
+        <v>3030.286</v>
       </c>
       <c r="D13" t="n">
         <v>1.97459e-07</v>
@@ -8530,7 +8530,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-305.6400000000003</v>
+        <v>3001.642</v>
       </c>
       <c r="D14" t="n">
         <v>1.98418e-07</v>
@@ -8580,7 +8580,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-288.9499999999998</v>
+        <v>2975.386</v>
       </c>
       <c r="D15" t="n">
         <v>1.99657e-07</v>
@@ -8630,7 +8630,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-279.8800000000001</v>
+        <v>2951.439</v>
       </c>
       <c r="D16" t="n">
         <v>2.00639e-07</v>
@@ -8680,7 +8680,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-279.0299999999997</v>
+        <v>2923.074</v>
       </c>
       <c r="D17" t="n">
         <v>2.01543e-07</v>
@@ -8730,7 +8730,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-275.1999999999998</v>
+        <v>2896.068</v>
       </c>
       <c r="D18" t="n">
         <v>2.02526e-07</v>
@@ -8780,7 +8780,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-265.9000000000001</v>
+        <v>2866.254</v>
       </c>
       <c r="D19" t="n">
         <v>2.03566e-07</v>
@@ -8830,7 +8830,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-263.2999999999997</v>
+        <v>2841.265</v>
       </c>
       <c r="D20" t="n">
         <v>2.04622e-07</v>
@@ -8880,7 +8880,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-252.2999999999997</v>
+        <v>2818.828</v>
       </c>
       <c r="D21" t="n">
         <v>2.05677e-07</v>
@@ -8930,7 +8930,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-260.4300000000003</v>
+        <v>2771.698</v>
       </c>
       <c r="D22" t="n">
         <v>2.06834e-07</v>
@@ -9126,7 +9126,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-552.7600000000002</v>
+        <v>3199.223</v>
       </c>
       <c r="D2" t="n">
         <v>1.8699e-07</v>
@@ -9176,7 +9176,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-352.4099999999999</v>
+        <v>2576.254</v>
       </c>
       <c r="D3" t="n">
         <v>2.14406e-07</v>
@@ -9226,7 +9226,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-283.5999999999999</v>
+        <v>2468.15</v>
       </c>
       <c r="D4" t="n">
         <v>2.19537e-07</v>
@@ -9276,7 +9276,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-266.4499999999998</v>
+        <v>2401.425</v>
       </c>
       <c r="D5" t="n">
         <v>2.21631e-07</v>
@@ -9326,7 +9326,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-254.9200000000001</v>
+        <v>2364.229</v>
       </c>
       <c r="D6" t="n">
         <v>2.22776e-07</v>
@@ -9376,7 +9376,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-259.3099999999999</v>
+        <v>2314.593</v>
       </c>
       <c r="D7" t="n">
         <v>2.23876e-07</v>
@@ -9426,7 +9426,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-240.0099999999998</v>
+        <v>2289.719</v>
       </c>
       <c r="D8" t="n">
         <v>2.25157e-07</v>
@@ -9476,7 +9476,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-231.9200000000001</v>
+        <v>2260.332</v>
       </c>
       <c r="D9" t="n">
         <v>2.26419e-07</v>
@@ -9526,7 +9526,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-227.3999999999996</v>
+        <v>2218.395</v>
       </c>
       <c r="D10" t="n">
         <v>2.27576e-07</v>
@@ -9576,7 +9576,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-229.7799999999997</v>
+        <v>2177.275</v>
       </c>
       <c r="D11" t="n">
         <v>2.28915e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 22.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 22.xlsx
@@ -438,7 +438,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -564,6 +564,9 @@
       <c r="B2" t="n">
         <v>3852.46</v>
       </c>
+      <c r="C2" t="n">
+        <v>4090.262894657085</v>
+      </c>
       <c r="D2" t="n">
         <v>1.71082e-07</v>
       </c>
@@ -614,6 +617,9 @@
       <c r="B3" t="n">
         <v>3790.98</v>
       </c>
+      <c r="C3" t="n">
+        <v>4030.562635142773</v>
+      </c>
       <c r="D3" t="n">
         <v>1.73367e-07</v>
       </c>
@@ -664,6 +670,9 @@
       <c r="B4" t="n">
         <v>3729.496</v>
       </c>
+      <c r="C4" t="n">
+        <v>3972.811527274077</v>
+      </c>
       <c r="D4" t="n">
         <v>1.75642e-07</v>
       </c>
@@ -714,6 +723,9 @@
       <c r="B5" t="n">
         <v>3624.505</v>
       </c>
+      <c r="C5" t="n">
+        <v>3885.530652444814</v>
+      </c>
       <c r="D5" t="n">
         <v>1.78341e-07</v>
       </c>
@@ -764,6 +776,9 @@
       <c r="B6" t="n">
         <v>3578.594</v>
       </c>
+      <c r="C6" t="n">
+        <v>3818.798003748499</v>
+      </c>
       <c r="D6" t="n">
         <v>1.81055e-07</v>
       </c>
@@ -814,6 +829,9 @@
       <c r="B7" t="n">
         <v>3467.432</v>
       </c>
+      <c r="C7" t="n">
+        <v>3725.312640525315</v>
+      </c>
       <c r="D7" t="n">
         <v>1.83885e-07</v>
       </c>
@@ -864,6 +882,9 @@
       <c r="B8" t="n">
         <v>3395.408</v>
       </c>
+      <c r="C8" t="n">
+        <v>3650.031368392822</v>
+      </c>
       <c r="D8" t="n">
         <v>1.86813e-07</v>
       </c>
@@ -914,6 +935,9 @@
       <c r="B9" t="n">
         <v>3319.295</v>
       </c>
+      <c r="C9" t="n">
+        <v>3573.094494966465</v>
+      </c>
       <c r="D9" t="n">
         <v>1.89274e-07</v>
       </c>
@@ -964,6 +988,9 @@
       <c r="B10" t="n">
         <v>3249.987</v>
       </c>
+      <c r="C10" t="n">
+        <v>3502.594500245536</v>
+      </c>
       <c r="D10" t="n">
         <v>1.91901e-07</v>
       </c>
@@ -1013,6 +1040,9 @@
       </c>
       <c r="B11" t="n">
         <v>3159.553</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3427.034621693911</v>
       </c>
       <c r="D11" t="n">
         <v>1.94336e-07</v>
@@ -1084,7 +1114,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -1210,6 +1240,9 @@
       <c r="B2" t="n">
         <v>3678.332</v>
       </c>
+      <c r="C2" t="n">
+        <v>3968.225752812883</v>
+      </c>
       <c r="D2" t="n">
         <v>1.7639e-07</v>
       </c>
@@ -1260,6 +1293,9 @@
       <c r="B3" t="n">
         <v>3506.666</v>
       </c>
+      <c r="C3" t="n">
+        <v>3778.899565411683</v>
+      </c>
       <c r="D3" t="n">
         <v>1.8282e-07</v>
       </c>
@@ -1310,6 +1346,9 @@
       <c r="B4" t="n">
         <v>3437.748</v>
       </c>
+      <c r="C4" t="n">
+        <v>3710.139676130584</v>
+      </c>
       <c r="D4" t="n">
         <v>1.85578e-07</v>
       </c>
@@ -1360,6 +1399,9 @@
       <c r="B5" t="n">
         <v>3359.498</v>
       </c>
+      <c r="C5" t="n">
+        <v>3647.864927045868</v>
+      </c>
       <c r="D5" t="n">
         <v>1.87738e-07</v>
       </c>
@@ -1410,6 +1452,9 @@
       <c r="B6" t="n">
         <v>3339.811</v>
       </c>
+      <c r="C6" t="n">
+        <v>3615.461943016778</v>
+      </c>
       <c r="D6" t="n">
         <v>1.89258e-07</v>
       </c>
@@ -1460,6 +1505,9 @@
       <c r="B7" t="n">
         <v>3304.196</v>
       </c>
+      <c r="C7" t="n">
+        <v>3575.814238413359</v>
+      </c>
       <c r="D7" t="n">
         <v>1.90869e-07</v>
       </c>
@@ -1510,6 +1558,9 @@
       <c r="B8" t="n">
         <v>3267.329</v>
       </c>
+      <c r="C8" t="n">
+        <v>3541.794970276042</v>
+      </c>
       <c r="D8" t="n">
         <v>1.92183e-07</v>
       </c>
@@ -1560,6 +1611,9 @@
       <c r="B9" t="n">
         <v>3212.279</v>
       </c>
+      <c r="C9" t="n">
+        <v>3495.449698781198</v>
+      </c>
       <c r="D9" t="n">
         <v>1.93504e-07</v>
       </c>
@@ -1610,6 +1664,9 @@
       <c r="B10" t="n">
         <v>3196.691</v>
       </c>
+      <c r="C10" t="n">
+        <v>3469.273617555638</v>
+      </c>
       <c r="D10" t="n">
         <v>1.94873e-07</v>
       </c>
@@ -1660,6 +1717,9 @@
       <c r="B11" t="n">
         <v>3160.866</v>
       </c>
+      <c r="C11" t="n">
+        <v>3434.022179130854</v>
+      </c>
       <c r="D11" t="n">
         <v>1.96086e-07</v>
       </c>
@@ -1710,6 +1770,9 @@
       <c r="B12" t="n">
         <v>3102.288</v>
       </c>
+      <c r="C12" t="n">
+        <v>3389.443520859414</v>
+      </c>
       <c r="D12" t="n">
         <v>1.97487e-07</v>
       </c>
@@ -1760,6 +1823,9 @@
       <c r="B13" t="n">
         <v>3091.035</v>
       </c>
+      <c r="C13" t="n">
+        <v>3365.79756946821</v>
+      </c>
       <c r="D13" t="n">
         <v>1.98728e-07</v>
       </c>
@@ -1810,6 +1876,9 @@
       <c r="B14" t="n">
         <v>3061.303</v>
       </c>
+      <c r="C14" t="n">
+        <v>3329.82043547082</v>
+      </c>
       <c r="D14" t="n">
         <v>2.00064e-07</v>
       </c>
@@ -1860,6 +1929,9 @@
       <c r="B15" t="n">
         <v>3006.722</v>
       </c>
+      <c r="C15" t="n">
+        <v>3288.308864460864</v>
+      </c>
       <c r="D15" t="n">
         <v>2.01331e-07</v>
       </c>
@@ -1910,6 +1982,9 @@
       <c r="B16" t="n">
         <v>2955.034</v>
       </c>
+      <c r="C16" t="n">
+        <v>3245.350364981935</v>
+      </c>
       <c r="D16" t="n">
         <v>2.02546e-07</v>
       </c>
@@ -1960,6 +2035,9 @@
       <c r="B17" t="n">
         <v>2955.911</v>
       </c>
+      <c r="C17" t="n">
+        <v>3228.147606304577</v>
+      </c>
       <c r="D17" t="n">
         <v>2.03775e-07</v>
       </c>
@@ -2010,6 +2088,9 @@
       <c r="B18" t="n">
         <v>2905.613</v>
       </c>
+      <c r="C18" t="n">
+        <v>3186.972887157414</v>
+      </c>
       <c r="D18" t="n">
         <v>2.05031e-07</v>
       </c>
@@ -2060,6 +2141,9 @@
       <c r="B19" t="n">
         <v>2872.563</v>
       </c>
+      <c r="C19" t="n">
+        <v>3154.171232638387</v>
+      </c>
       <c r="D19" t="n">
         <v>2.06361e-07</v>
       </c>
@@ -2110,6 +2194,9 @@
       <c r="B20" t="n">
         <v>2839.418</v>
       </c>
+      <c r="C20" t="n">
+        <v>3121.577599602536</v>
+      </c>
       <c r="D20" t="n">
         <v>2.07254e-07</v>
       </c>
@@ -2160,6 +2247,9 @@
       <c r="B21" t="n">
         <v>2813.507</v>
       </c>
+      <c r="C21" t="n">
+        <v>3089.628469015728</v>
+      </c>
       <c r="D21" t="n">
         <v>2.08796e-07</v>
       </c>
@@ -2209,6 +2299,9 @@
       </c>
       <c r="B22" t="n">
         <v>2779.263</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3055.909604077406</v>
       </c>
       <c r="D22" t="n">
         <v>2.09799e-07</v>
@@ -2280,7 +2373,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -2406,6 +2499,9 @@
       <c r="B2" t="n">
         <v>3744.922</v>
       </c>
+      <c r="C2" t="n">
+        <v>4031.956155607799</v>
+      </c>
       <c r="D2" t="n">
         <v>1.72399e-07</v>
       </c>
@@ -2456,6 +2552,9 @@
       <c r="B3" t="n">
         <v>3569.268</v>
       </c>
+      <c r="C3" t="n">
+        <v>3834.710110540431</v>
+      </c>
       <c r="D3" t="n">
         <v>1.79549e-07</v>
       </c>
@@ -2506,6 +2605,9 @@
       <c r="B4" t="n">
         <v>3493.123</v>
       </c>
+      <c r="C4" t="n">
+        <v>3762.534428908826</v>
+      </c>
       <c r="D4" t="n">
         <v>1.82536e-07</v>
       </c>
@@ -2556,6 +2658,9 @@
       <c r="B5" t="n">
         <v>3445.376</v>
       </c>
+      <c r="C5" t="n">
+        <v>3712.29802567827</v>
+      </c>
       <c r="D5" t="n">
         <v>1.8412e-07</v>
       </c>
@@ -2606,6 +2711,9 @@
       <c r="B6" t="n">
         <v>3406.698</v>
       </c>
+      <c r="C6" t="n">
+        <v>3667.455721979444</v>
+      </c>
       <c r="D6" t="n">
         <v>1.86066e-07</v>
       </c>
@@ -2656,6 +2764,9 @@
       <c r="B7" t="n">
         <v>3361.387</v>
       </c>
+      <c r="C7" t="n">
+        <v>3624.293919853878</v>
+      </c>
       <c r="D7" t="n">
         <v>1.87424e-07</v>
       </c>
@@ -2706,6 +2817,9 @@
       <c r="B8" t="n">
         <v>3319.906</v>
       </c>
+      <c r="C8" t="n">
+        <v>3585.360754930358</v>
+      </c>
       <c r="D8" t="n">
         <v>1.88632e-07</v>
       </c>
@@ -2756,6 +2870,9 @@
       <c r="B9" t="n">
         <v>3283.179</v>
       </c>
+      <c r="C9" t="n">
+        <v>3547.257791552163</v>
+      </c>
       <c r="D9" t="n">
         <v>1.90074e-07</v>
       </c>
@@ -2806,6 +2923,9 @@
       <c r="B10" t="n">
         <v>3245.033</v>
       </c>
+      <c r="C10" t="n">
+        <v>3509.922541528195</v>
+      </c>
       <c r="D10" t="n">
         <v>1.91118e-07</v>
       </c>
@@ -2856,6 +2976,9 @@
       <c r="B11" t="n">
         <v>3209.143</v>
       </c>
+      <c r="C11" t="n">
+        <v>3473.684627330663</v>
+      </c>
       <c r="D11" t="n">
         <v>1.92627e-07</v>
       </c>
@@ -2906,6 +3029,9 @@
       <c r="B12" t="n">
         <v>3150.149</v>
       </c>
+      <c r="C12" t="n">
+        <v>3428.825235842202</v>
+      </c>
       <c r="D12" t="n">
         <v>1.93583e-07</v>
       </c>
@@ -2956,6 +3082,9 @@
       <c r="B13" t="n">
         <v>3121.904</v>
       </c>
+      <c r="C13" t="n">
+        <v>3392.197551793963</v>
+      </c>
       <c r="D13" t="n">
         <v>1.94953e-07</v>
       </c>
@@ -3006,6 +3135,9 @@
       <c r="B14" t="n">
         <v>3085.339</v>
       </c>
+      <c r="C14" t="n">
+        <v>3358.183071526884</v>
+      </c>
       <c r="D14" t="n">
         <v>1.96063e-07</v>
       </c>
@@ -3056,6 +3188,9 @@
       <c r="B15" t="n">
         <v>3056.301</v>
       </c>
+      <c r="C15" t="n">
+        <v>3323.166320608543</v>
+      </c>
       <c r="D15" t="n">
         <v>1.9725e-07</v>
       </c>
@@ -3106,6 +3241,9 @@
       <c r="B16" t="n">
         <v>3021.043</v>
       </c>
+      <c r="C16" t="n">
+        <v>3288.763567519998</v>
+      </c>
       <c r="D16" t="n">
         <v>1.9827e-07</v>
       </c>
@@ -3156,6 +3294,9 @@
       <c r="B17" t="n">
         <v>2988.04</v>
       </c>
+      <c r="C17" t="n">
+        <v>3257.184915920018</v>
+      </c>
       <c r="D17" t="n">
         <v>1.99642e-07</v>
       </c>
@@ -3206,6 +3347,9 @@
       <c r="B18" t="n">
         <v>2955.594</v>
       </c>
+      <c r="C18" t="n">
+        <v>3222.038790391883</v>
+      </c>
       <c r="D18" t="n">
         <v>2.00614e-07</v>
       </c>
@@ -3256,6 +3400,9 @@
       <c r="B19" t="n">
         <v>2923.937</v>
       </c>
+      <c r="C19" t="n">
+        <v>3191.13708408033</v>
+      </c>
       <c r="D19" t="n">
         <v>2.01951e-07</v>
       </c>
@@ -3306,6 +3453,9 @@
       <c r="B20" t="n">
         <v>2889.878</v>
       </c>
+      <c r="C20" t="n">
+        <v>3159.62861734503</v>
+      </c>
       <c r="D20" t="n">
         <v>2.02908e-07</v>
       </c>
@@ -3356,6 +3506,9 @@
       <c r="B21" t="n">
         <v>2880.713</v>
       </c>
+      <c r="C21" t="n">
+        <v>3136.180107570375</v>
+      </c>
       <c r="D21" t="n">
         <v>2.03928e-07</v>
       </c>
@@ -3405,6 +3558,9 @@
       </c>
       <c r="B22" t="n">
         <v>2830.395</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3096.932913626113</v>
       </c>
       <c r="D22" t="n">
         <v>2.0524e-07</v>
@@ -3476,7 +3632,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -3602,6 +3758,9 @@
       <c r="B2" t="n">
         <v>4525.086</v>
       </c>
+      <c r="C2" t="n">
+        <v>4827.586851421003</v>
+      </c>
       <c r="D2" t="n">
         <v>1.48052e-07</v>
       </c>
@@ -3652,6 +3811,9 @@
       <c r="B3" t="n">
         <v>3853.317</v>
       </c>
+      <c r="C3" t="n">
+        <v>4112.830579310931</v>
+      </c>
       <c r="D3" t="n">
         <v>1.72127e-07</v>
       </c>
@@ -3702,6 +3864,9 @@
       <c r="B4" t="n">
         <v>3670.807</v>
       </c>
+      <c r="C4" t="n">
+        <v>3941.586149426752</v>
+      </c>
       <c r="D4" t="n">
         <v>1.78213e-07</v>
       </c>
@@ -3752,6 +3917,9 @@
       <c r="B5" t="n">
         <v>3602.979</v>
       </c>
+      <c r="C5" t="n">
+        <v>3869.246958823255</v>
+      </c>
       <c r="D5" t="n">
         <v>1.81295e-07</v>
       </c>
@@ -3802,6 +3970,9 @@
       <c r="B6" t="n">
         <v>3549.37</v>
       </c>
+      <c r="C6" t="n">
+        <v>3815.475477528914</v>
+      </c>
       <c r="D6" t="n">
         <v>1.83132e-07</v>
       </c>
@@ -3852,6 +4023,9 @@
       <c r="B7" t="n">
         <v>3496.687</v>
       </c>
+      <c r="C7" t="n">
+        <v>3766.797233325573</v>
+      </c>
       <c r="D7" t="n">
         <v>1.8503e-07</v>
       </c>
@@ -3902,6 +4076,9 @@
       <c r="B8" t="n">
         <v>3449.656</v>
       </c>
+      <c r="C8" t="n">
+        <v>3716.17981696578</v>
+      </c>
       <c r="D8" t="n">
         <v>1.86653e-07</v>
       </c>
@@ -3952,6 +4129,9 @@
       <c r="B9" t="n">
         <v>3403.369</v>
       </c>
+      <c r="C9" t="n">
+        <v>3671.56065674134</v>
+      </c>
       <c r="D9" t="n">
         <v>1.88258e-07</v>
       </c>
@@ -4002,6 +4182,9 @@
       <c r="B10" t="n">
         <v>3357.19</v>
       </c>
+      <c r="C10" t="n">
+        <v>3629.511760553408</v>
+      </c>
       <c r="D10" t="n">
         <v>1.899e-07</v>
       </c>
@@ -4051,6 +4234,9 @@
       </c>
       <c r="B11" t="n">
         <v>3322.173</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3589.094282790891</v>
       </c>
       <c r="D11" t="n">
         <v>1.91233e-07</v>
@@ -4122,7 +4308,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -4248,6 +4434,9 @@
       <c r="B2" t="n">
         <v>3708.864</v>
       </c>
+      <c r="C2" t="n">
+        <v>4005.195168909228</v>
+      </c>
       <c r="D2" t="n">
         <v>1.7404e-07</v>
       </c>
@@ -4298,6 +4487,9 @@
       <c r="B3" t="n">
         <v>3504.058</v>
       </c>
+      <c r="C3" t="n">
+        <v>3780.175898758577</v>
+      </c>
       <c r="D3" t="n">
         <v>1.82955e-07</v>
       </c>
@@ -4348,6 +4540,9 @@
       <c r="B4" t="n">
         <v>3442.693</v>
       </c>
+      <c r="C4" t="n">
+        <v>3710.396782634206</v>
+      </c>
       <c r="D4" t="n">
         <v>1.85643e-07</v>
       </c>
@@ -4398,6 +4593,9 @@
       <c r="B5" t="n">
         <v>3394.1</v>
       </c>
+      <c r="C5" t="n">
+        <v>3667.656994896587</v>
+      </c>
       <c r="D5" t="n">
         <v>1.8734e-07</v>
       </c>
@@ -4448,6 +4646,9 @@
       <c r="B6" t="n">
         <v>3351.124</v>
       </c>
+      <c r="C6" t="n">
+        <v>3623.717381881532</v>
+      </c>
       <c r="D6" t="n">
         <v>1.88693e-07</v>
       </c>
@@ -4498,6 +4699,9 @@
       <c r="B7" t="n">
         <v>3312.95</v>
       </c>
+      <c r="C7" t="n">
+        <v>3583.707515925887</v>
+      </c>
       <c r="D7" t="n">
         <v>1.90111e-07</v>
       </c>
@@ -4548,6 +4752,9 @@
       <c r="B8" t="n">
         <v>3273.829</v>
       </c>
+      <c r="C8" t="n">
+        <v>3542.414630927135</v>
+      </c>
       <c r="D8" t="n">
         <v>1.91563e-07</v>
       </c>
@@ -4598,6 +4805,9 @@
       <c r="B9" t="n">
         <v>3232.236</v>
       </c>
+      <c r="C9" t="n">
+        <v>3503.524845667792</v>
+      </c>
       <c r="D9" t="n">
         <v>1.92749e-07</v>
       </c>
@@ -4648,6 +4858,9 @@
       <c r="B10" t="n">
         <v>3195.427</v>
       </c>
+      <c r="C10" t="n">
+        <v>3467.076636717556</v>
+      </c>
       <c r="D10" t="n">
         <v>1.94136e-07</v>
       </c>
@@ -4698,6 +4911,9 @@
       <c r="B11" t="n">
         <v>3138.272</v>
       </c>
+      <c r="C11" t="n">
+        <v>3421.93313710722</v>
+      </c>
       <c r="D11" t="n">
         <v>1.95373e-07</v>
       </c>
@@ -4748,6 +4964,9 @@
       <c r="B12" t="n">
         <v>3100.293</v>
       </c>
+      <c r="C12" t="n">
+        <v>3388.43038022568</v>
+      </c>
       <c r="D12" t="n">
         <v>1.96646e-07</v>
       </c>
@@ -4798,6 +5017,9 @@
       <c r="B13" t="n">
         <v>3092.473</v>
       </c>
+      <c r="C13" t="n">
+        <v>3362.475211830905</v>
+      </c>
       <c r="D13" t="n">
         <v>1.97745e-07</v>
       </c>
@@ -4848,6 +5070,9 @@
       <c r="B14" t="n">
         <v>3039.591</v>
       </c>
+      <c r="C14" t="n">
+        <v>3322.892736555752</v>
+      </c>
       <c r="D14" t="n">
         <v>1.98762e-07</v>
       </c>
@@ -4898,6 +5123,9 @@
       <c r="B15" t="n">
         <v>3006.895</v>
       </c>
+      <c r="C15" t="n">
+        <v>3291.023842846892</v>
+      </c>
       <c r="D15" t="n">
         <v>1.99886e-07</v>
       </c>
@@ -4948,6 +5176,9 @@
       <c r="B16" t="n">
         <v>2998.568</v>
       </c>
+      <c r="C16" t="n">
+        <v>3268.187340512005</v>
+      </c>
       <c r="D16" t="n">
         <v>2.01107e-07</v>
       </c>
@@ -4998,6 +5229,9 @@
       <c r="B17" t="n">
         <v>2947.304</v>
       </c>
+      <c r="C17" t="n">
+        <v>3230.737486353717</v>
+      </c>
       <c r="D17" t="n">
         <v>2.02057e-07</v>
       </c>
@@ -5048,6 +5282,9 @@
       <c r="B18" t="n">
         <v>2916.959</v>
       </c>
+      <c r="C18" t="n">
+        <v>3199.131451394526</v>
+      </c>
       <c r="D18" t="n">
         <v>2.02991e-07</v>
       </c>
@@ -5098,6 +5335,9 @@
       <c r="B19" t="n">
         <v>2888.634</v>
       </c>
+      <c r="C19" t="n">
+        <v>3169.876054712648</v>
+      </c>
       <c r="D19" t="n">
         <v>2.04096e-07</v>
       </c>
@@ -5148,6 +5388,9 @@
       <c r="B20" t="n">
         <v>2860.76</v>
       </c>
+      <c r="C20" t="n">
+        <v>3139.84584264815</v>
+      </c>
       <c r="D20" t="n">
         <v>2.05255e-07</v>
       </c>
@@ -5198,6 +5441,9 @@
       <c r="B21" t="n">
         <v>2833.797</v>
       </c>
+      <c r="C21" t="n">
+        <v>3110.206739254788</v>
+      </c>
       <c r="D21" t="n">
         <v>2.06397e-07</v>
       </c>
@@ -5247,6 +5493,9 @@
       </c>
       <c r="B22" t="n">
         <v>2807.645</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3081.131173649205</v>
       </c>
       <c r="D22" t="n">
         <v>2.075e-07</v>
@@ -5318,7 +5567,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -5444,6 +5693,9 @@
       <c r="B2" t="n">
         <v>4459.268</v>
       </c>
+      <c r="C2" t="n">
+        <v>4787.322021152971</v>
+      </c>
       <c r="D2" t="n">
         <v>1.48884e-07</v>
       </c>
@@ -5494,6 +5746,9 @@
       <c r="B3" t="n">
         <v>3814.951</v>
       </c>
+      <c r="C3" t="n">
+        <v>4072.98696945737</v>
+      </c>
       <c r="D3" t="n">
         <v>1.73239e-07</v>
       </c>
@@ -5544,6 +5799,9 @@
       <c r="B4" t="n">
         <v>3645.149</v>
       </c>
+      <c r="C4" t="n">
+        <v>3909.829096771019</v>
+      </c>
       <c r="D4" t="n">
         <v>1.79275e-07</v>
       </c>
@@ -5594,6 +5852,9 @@
       <c r="B5" t="n">
         <v>3577.913</v>
       </c>
+      <c r="C5" t="n">
+        <v>3840.261940153929</v>
+      </c>
       <c r="D5" t="n">
         <v>1.81596e-07</v>
       </c>
@@ -5644,6 +5905,9 @@
       <c r="B6" t="n">
         <v>3525.562</v>
       </c>
+      <c r="C6" t="n">
+        <v>3787.226066572004</v>
+      </c>
       <c r="D6" t="n">
         <v>1.84015e-07</v>
       </c>
@@ -5694,6 +5958,9 @@
       <c r="B7" t="n">
         <v>3478.255</v>
       </c>
+      <c r="C7" t="n">
+        <v>3739.391339974596</v>
+      </c>
       <c r="D7" t="n">
         <v>1.85589e-07</v>
       </c>
@@ -5744,6 +6011,9 @@
       <c r="B8" t="n">
         <v>3422.936</v>
       </c>
+      <c r="C8" t="n">
+        <v>3687.342400478719</v>
+      </c>
       <c r="D8" t="n">
         <v>1.87196e-07</v>
       </c>
@@ -5794,6 +6064,9 @@
       <c r="B9" t="n">
         <v>3377.946</v>
       </c>
+      <c r="C9" t="n">
+        <v>3640.413680241331</v>
+      </c>
       <c r="D9" t="n">
         <v>1.88975e-07</v>
       </c>
@@ -5844,6 +6117,9 @@
       <c r="B10" t="n">
         <v>3332.78</v>
       </c>
+      <c r="C10" t="n">
+        <v>3593.983159880353</v>
+      </c>
       <c r="D10" t="n">
         <v>1.90513e-07</v>
       </c>
@@ -5893,6 +6169,9 @@
       </c>
       <c r="B11" t="n">
         <v>3269.662</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3544.910277757086</v>
       </c>
       <c r="D11" t="n">
         <v>1.92177e-07</v>
@@ -5964,7 +6243,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -6090,6 +6369,9 @@
       <c r="B2" t="n">
         <v>3717.902</v>
       </c>
+      <c r="C2" t="n">
+        <v>3994.537081286064</v>
+      </c>
       <c r="D2" t="n">
         <v>1.75491e-07</v>
       </c>
@@ -6140,6 +6422,9 @@
       <c r="B3" t="n">
         <v>3496.819</v>
       </c>
+      <c r="C3" t="n">
+        <v>3769.83121323671</v>
+      </c>
       <c r="D3" t="n">
         <v>1.83769e-07</v>
       </c>
@@ -6190,6 +6475,9 @@
       <c r="B4" t="n">
         <v>3434.181</v>
       </c>
+      <c r="C4" t="n">
+        <v>3702.996520353501</v>
+      </c>
       <c r="D4" t="n">
         <v>1.86394e-07</v>
       </c>
@@ -6240,6 +6528,9 @@
       <c r="B5" t="n">
         <v>3365.52</v>
       </c>
+      <c r="C5" t="n">
+        <v>3648.025919270994</v>
+      </c>
       <c r="D5" t="n">
         <v>1.88149e-07</v>
       </c>
@@ -6290,6 +6581,9 @@
       <c r="B6" t="n">
         <v>3347.718</v>
       </c>
+      <c r="C6" t="n">
+        <v>3616.800099194834</v>
+      </c>
       <c r="D6" t="n">
         <v>1.89596e-07</v>
       </c>
@@ -6340,6 +6634,9 @@
       <c r="B7" t="n">
         <v>3310.858</v>
       </c>
+      <c r="C7" t="n">
+        <v>3580.043011777872</v>
+      </c>
       <c r="D7" t="n">
         <v>1.91017e-07</v>
       </c>
@@ -6390,6 +6687,9 @@
       <c r="B8" t="n">
         <v>3277.431</v>
       </c>
+      <c r="C8" t="n">
+        <v>3547.87553039352</v>
+      </c>
       <c r="D8" t="n">
         <v>1.92212e-07</v>
       </c>
@@ -6440,6 +6740,9 @@
       <c r="B9" t="n">
         <v>3221.451</v>
       </c>
+      <c r="C9" t="n">
+        <v>3507.538417061768</v>
+      </c>
       <c r="D9" t="n">
         <v>1.93405e-07</v>
       </c>
@@ -6490,6 +6793,9 @@
       <c r="B10" t="n">
         <v>3212.682</v>
       </c>
+      <c r="C10" t="n">
+        <v>3481.526624760476</v>
+      </c>
       <c r="D10" t="n">
         <v>1.94314e-07</v>
       </c>
@@ -6540,6 +6846,9 @@
       <c r="B11" t="n">
         <v>3181.648</v>
       </c>
+      <c r="C11" t="n">
+        <v>3452.967335716866</v>
+      </c>
       <c r="D11" t="n">
         <v>1.95722e-07</v>
       </c>
@@ -6590,6 +6899,9 @@
       <c r="B12" t="n">
         <v>3134.152</v>
       </c>
+      <c r="C12" t="n">
+        <v>3414.154312366292</v>
+      </c>
       <c r="D12" t="n">
         <v>1.96823e-07</v>
       </c>
@@ -6640,6 +6952,9 @@
       <c r="B13" t="n">
         <v>3108.108</v>
       </c>
+      <c r="C13" t="n">
+        <v>3385.991367666909</v>
+      </c>
       <c r="D13" t="n">
         <v>1.97715e-07</v>
       </c>
@@ -6690,6 +7005,9 @@
       <c r="B14" t="n">
         <v>3097.531</v>
       </c>
+      <c r="C14" t="n">
+        <v>3365.020591424226</v>
+      </c>
       <c r="D14" t="n">
         <v>1.98851e-07</v>
       </c>
@@ -6740,6 +7058,9 @@
       <c r="B15" t="n">
         <v>3052.9</v>
       </c>
+      <c r="C15" t="n">
+        <v>3329.249471502608</v>
+      </c>
       <c r="D15" t="n">
         <v>1.99831e-07</v>
       </c>
@@ -6790,6 +7111,9 @@
       <c r="B16" t="n">
         <v>3041.708</v>
       </c>
+      <c r="C16" t="n">
+        <v>3307.048580793825</v>
+      </c>
       <c r="D16" t="n">
         <v>2.00891e-07</v>
       </c>
@@ -6840,6 +7164,9 @@
       <c r="B17" t="n">
         <v>3013.689</v>
       </c>
+      <c r="C17" t="n">
+        <v>3279.162396452301</v>
+      </c>
       <c r="D17" t="n">
         <v>2.01834e-07</v>
       </c>
@@ -6890,6 +7217,9 @@
       <c r="B18" t="n">
         <v>2964.158</v>
       </c>
+      <c r="C18" t="n">
+        <v>3241.435371289489</v>
+      </c>
       <c r="D18" t="n">
         <v>2.02906e-07</v>
       </c>
@@ -6940,6 +7270,9 @@
       <c r="B19" t="n">
         <v>2935.224</v>
       </c>
+      <c r="C19" t="n">
+        <v>3210.164291599909</v>
+      </c>
       <c r="D19" t="n">
         <v>2.04115e-07</v>
       </c>
@@ -6990,6 +7323,9 @@
       <c r="B20" t="n">
         <v>2902.99</v>
       </c>
+      <c r="C20" t="n">
+        <v>3179.83259499805</v>
+      </c>
       <c r="D20" t="n">
         <v>2.05174e-07</v>
       </c>
@@ -7040,6 +7376,9 @@
       <c r="B21" t="n">
         <v>2874.349</v>
       </c>
+      <c r="C21" t="n">
+        <v>3150.740097322521</v>
+      </c>
       <c r="D21" t="n">
         <v>2.06385e-07</v>
       </c>
@@ -7089,6 +7428,9 @@
       </c>
       <c r="B22" t="n">
         <v>2833.017</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3113.800367969926</v>
       </c>
       <c r="D22" t="n">
         <v>2.07473e-07</v>
@@ -7160,7 +7502,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -7286,6 +7628,9 @@
       <c r="B2" t="n">
         <v>4270.356</v>
       </c>
+      <c r="C2" t="n">
+        <v>4604.996165947747</v>
+      </c>
       <c r="D2" t="n">
         <v>1.52123e-07</v>
       </c>
@@ -7336,6 +7681,9 @@
       <c r="B3" t="n">
         <v>3598.002</v>
       </c>
+      <c r="C3" t="n">
+        <v>3878.345331930941</v>
+      </c>
       <c r="D3" t="n">
         <v>1.76576e-07</v>
       </c>
@@ -7386,6 +7734,9 @@
       <c r="B4" t="n">
         <v>3454.311</v>
       </c>
+      <c r="C4" t="n">
+        <v>3722.250347380781</v>
+      </c>
       <c r="D4" t="n">
         <v>1.8188e-07</v>
       </c>
@@ -7436,6 +7787,9 @@
       <c r="B5" t="n">
         <v>3362.022</v>
       </c>
+      <c r="C5" t="n">
+        <v>3645.300004754277</v>
+      </c>
       <c r="D5" t="n">
         <v>1.83869e-07</v>
       </c>
@@ -7486,6 +7840,9 @@
       <c r="B6" t="n">
         <v>3325.986</v>
       </c>
+      <c r="C6" t="n">
+        <v>3596.581181760527</v>
+      </c>
       <c r="D6" t="n">
         <v>1.8523e-07</v>
       </c>
@@ -7536,6 +7893,9 @@
       <c r="B7" t="n">
         <v>3252.983</v>
       </c>
+      <c r="C7" t="n">
+        <v>3537.972486813213</v>
+      </c>
       <c r="D7" t="n">
         <v>1.86485e-07</v>
       </c>
@@ -7586,6 +7946,9 @@
       <c r="B8" t="n">
         <v>3226.471</v>
       </c>
+      <c r="C8" t="n">
+        <v>3495.389718263189</v>
+      </c>
       <c r="D8" t="n">
         <v>1.87917e-07</v>
       </c>
@@ -7636,6 +7999,9 @@
       <c r="B9" t="n">
         <v>3154.382</v>
       </c>
+      <c r="C9" t="n">
+        <v>3436.751539878295</v>
+      </c>
       <c r="D9" t="n">
         <v>1.89215e-07</v>
       </c>
@@ -7686,6 +8052,9 @@
       <c r="B10" t="n">
         <v>3105.243</v>
       </c>
+      <c r="C10" t="n">
+        <v>3389.206789242181</v>
+      </c>
       <c r="D10" t="n">
         <v>1.9051e-07</v>
       </c>
@@ -7735,6 +8104,9 @@
       </c>
       <c r="B11" t="n">
         <v>3061.703</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3343.116295925606</v>
       </c>
       <c r="D11" t="n">
         <v>1.91838e-07</v>
@@ -7806,7 +8178,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -7932,6 +8304,9 @@
       <c r="B2" t="n">
         <v>3618.313</v>
       </c>
+      <c r="C2" t="n">
+        <v>3914.797408024064</v>
+      </c>
       <c r="D2" t="n">
         <v>1.73994e-07</v>
       </c>
@@ -7982,6 +8357,9 @@
       <c r="B3" t="n">
         <v>3421.174</v>
       </c>
+      <c r="C3" t="n">
+        <v>3698.038324900365</v>
+      </c>
       <c r="D3" t="n">
         <v>1.82652e-07</v>
       </c>
@@ -8032,6 +8410,9 @@
       <c r="B4" t="n">
         <v>3329.567</v>
       </c>
+      <c r="C4" t="n">
+        <v>3617.201951012219</v>
+      </c>
       <c r="D4" t="n">
         <v>1.85529e-07</v>
       </c>
@@ -8082,6 +8463,9 @@
       <c r="B5" t="n">
         <v>3307.411</v>
       </c>
+      <c r="C5" t="n">
+        <v>3580.416011061983</v>
+      </c>
       <c r="D5" t="n">
         <v>1.87585e-07</v>
       </c>
@@ -8132,6 +8516,9 @@
       <c r="B6" t="n">
         <v>3244.448</v>
       </c>
+      <c r="C6" t="n">
+        <v>3533.533665963866</v>
+      </c>
       <c r="D6" t="n">
         <v>1.88969e-07</v>
       </c>
@@ -8182,6 +8569,9 @@
       <c r="B7" t="n">
         <v>3211.31</v>
       </c>
+      <c r="C7" t="n">
+        <v>3497.84036361608</v>
+      </c>
       <c r="D7" t="n">
         <v>1.90505e-07</v>
       </c>
@@ -8232,6 +8622,9 @@
       <c r="B8" t="n">
         <v>3177.596</v>
       </c>
+      <c r="C8" t="n">
+        <v>3464.72602844258</v>
+      </c>
       <c r="D8" t="n">
         <v>1.91511e-07</v>
       </c>
@@ -8282,6 +8675,9 @@
       <c r="B9" t="n">
         <v>3144.322</v>
       </c>
+      <c r="C9" t="n">
+        <v>3431.27137733926</v>
+      </c>
       <c r="D9" t="n">
         <v>1.9295e-07</v>
       </c>
@@ -8332,6 +8728,9 @@
       <c r="B10" t="n">
         <v>3119.191</v>
       </c>
+      <c r="C10" t="n">
+        <v>3399.982667066321</v>
+      </c>
       <c r="D10" t="n">
         <v>1.94419e-07</v>
       </c>
@@ -8382,6 +8781,9 @@
       <c r="B11" t="n">
         <v>3105.89</v>
       </c>
+      <c r="C11" t="n">
+        <v>3378.503647629097</v>
+      </c>
       <c r="D11" t="n">
         <v>1.95185e-07</v>
       </c>
@@ -8432,6 +8834,9 @@
       <c r="B12" t="n">
         <v>3058.819</v>
       </c>
+      <c r="C12" t="n">
+        <v>3341.018566321077</v>
+      </c>
       <c r="D12" t="n">
         <v>1.96328e-07</v>
       </c>
@@ -8482,6 +8887,9 @@
       <c r="B13" t="n">
         <v>3030.286</v>
       </c>
+      <c r="C13" t="n">
+        <v>3314.135570047208</v>
+      </c>
       <c r="D13" t="n">
         <v>1.97459e-07</v>
       </c>
@@ -8532,6 +8940,9 @@
       <c r="B14" t="n">
         <v>3001.642</v>
       </c>
+      <c r="C14" t="n">
+        <v>3286.498425912858</v>
+      </c>
       <c r="D14" t="n">
         <v>1.98418e-07</v>
       </c>
@@ -8582,6 +8993,9 @@
       <c r="B15" t="n">
         <v>2975.386</v>
       </c>
+      <c r="C15" t="n">
+        <v>3258.085548034843</v>
+      </c>
       <c r="D15" t="n">
         <v>1.99657e-07</v>
       </c>
@@ -8632,6 +9046,9 @@
       <c r="B16" t="n">
         <v>2951.439</v>
       </c>
+      <c r="C16" t="n">
+        <v>3230.786273220484</v>
+      </c>
       <c r="D16" t="n">
         <v>2.00639e-07</v>
       </c>
@@ -8682,6 +9099,9 @@
       <c r="B17" t="n">
         <v>2923.074</v>
       </c>
+      <c r="C17" t="n">
+        <v>3202.990776849141</v>
+      </c>
       <c r="D17" t="n">
         <v>2.01543e-07</v>
       </c>
@@ -8732,6 +9152,9 @@
       <c r="B18" t="n">
         <v>2896.068</v>
       </c>
+      <c r="C18" t="n">
+        <v>3175.963552941086</v>
+      </c>
       <c r="D18" t="n">
         <v>2.02526e-07</v>
       </c>
@@ -8782,6 +9205,9 @@
       <c r="B19" t="n">
         <v>2866.254</v>
       </c>
+      <c r="C19" t="n">
+        <v>3146.316880704469</v>
+      </c>
       <c r="D19" t="n">
         <v>2.03566e-07</v>
       </c>
@@ -8832,6 +9258,9 @@
       <c r="B20" t="n">
         <v>2841.265</v>
       </c>
+      <c r="C20" t="n">
+        <v>3116.618457848635</v>
+      </c>
       <c r="D20" t="n">
         <v>2.04622e-07</v>
       </c>
@@ -8882,6 +9311,9 @@
       <c r="B21" t="n">
         <v>2818.828</v>
       </c>
+      <c r="C21" t="n">
+        <v>3090.392124261674</v>
+      </c>
       <c r="D21" t="n">
         <v>2.05677e-07</v>
       </c>
@@ -8931,6 +9363,9 @@
       </c>
       <c r="B22" t="n">
         <v>2771.698</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3055.610772737397</v>
       </c>
       <c r="D22" t="n">
         <v>2.06834e-07</v>
@@ -9002,7 +9437,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -9128,6 +9563,9 @@
       <c r="B2" t="n">
         <v>3199.223</v>
       </c>
+      <c r="C2" t="n">
+        <v>3616.655412082657</v>
+      </c>
       <c r="D2" t="n">
         <v>1.8699e-07</v>
       </c>
@@ -9178,6 +9616,9 @@
       <c r="B3" t="n">
         <v>2576.254</v>
       </c>
+      <c r="C3" t="n">
+        <v>2910.286943771685</v>
+      </c>
       <c r="D3" t="n">
         <v>2.14406e-07</v>
       </c>
@@ -9228,6 +9669,9 @@
       <c r="B4" t="n">
         <v>2468.15</v>
       </c>
+      <c r="C4" t="n">
+        <v>2784.805354161376</v>
+      </c>
       <c r="D4" t="n">
         <v>2.19537e-07</v>
       </c>
@@ -9278,6 +9722,9 @@
       <c r="B5" t="n">
         <v>2401.425</v>
       </c>
+      <c r="C5" t="n">
+        <v>2722.49049542128</v>
+      </c>
       <c r="D5" t="n">
         <v>2.21631e-07</v>
       </c>
@@ -9328,6 +9775,9 @@
       <c r="B6" t="n">
         <v>2364.229</v>
       </c>
+      <c r="C6" t="n">
+        <v>2685.15272299248</v>
+      </c>
       <c r="D6" t="n">
         <v>2.22776e-07</v>
       </c>
@@ -9378,6 +9828,9 @@
       <c r="B7" t="n">
         <v>2314.593</v>
       </c>
+      <c r="C7" t="n">
+        <v>2643.443739867774</v>
+      </c>
       <c r="D7" t="n">
         <v>2.23876e-07</v>
       </c>
@@ -9428,6 +9881,9 @@
       <c r="B8" t="n">
         <v>2289.719</v>
       </c>
+      <c r="C8" t="n">
+        <v>2612.543339712507</v>
+      </c>
       <c r="D8" t="n">
         <v>2.25157e-07</v>
       </c>
@@ -9478,6 +9934,9 @@
       <c r="B9" t="n">
         <v>2260.332</v>
       </c>
+      <c r="C9" t="n">
+        <v>2578.227742134532</v>
+      </c>
       <c r="D9" t="n">
         <v>2.26419e-07</v>
       </c>
@@ -9528,6 +9987,9 @@
       <c r="B10" t="n">
         <v>2218.395</v>
       </c>
+      <c r="C10" t="n">
+        <v>2542.928529547422</v>
+      </c>
       <c r="D10" t="n">
         <v>2.27576e-07</v>
       </c>
@@ -9577,6 +10039,9 @@
       </c>
       <c r="B11" t="n">
         <v>2177.275</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2505.212470414701</v>
       </c>
       <c r="D11" t="n">
         <v>2.28915e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 22.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 22.xlsx
@@ -565,7 +565,7 @@
         <v>3852.46</v>
       </c>
       <c r="C2" t="n">
-        <v>4090.262894657085</v>
+        <v>16762.72134376082</v>
       </c>
       <c r="D2" t="n">
         <v>1.71082e-07</v>
@@ -598,10 +598,7 @@
         <v>-38869.91105651398</v>
       </c>
       <c r="Y2" t="n">
-        <v>788.250215773583</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2340.447322745747</v>
+        <v>-12009.27749018883</v>
       </c>
       <c r="AA2" t="n">
         <v>5.776946517833533e-08</v>
@@ -618,7 +615,7 @@
         <v>3790.98</v>
       </c>
       <c r="C3" t="n">
-        <v>4030.562635142773</v>
+        <v>17611.64864232294</v>
       </c>
       <c r="D3" t="n">
         <v>1.73367e-07</v>
@@ -651,10 +648,7 @@
         <v>-40922.63006373644</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.375691008376404e-10</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>4730.196575854054</v>
+        <v>-12942.62939399698</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000007e-08</v>
@@ -671,7 +665,7 @@
         <v>3729.496</v>
       </c>
       <c r="C4" t="n">
-        <v>3972.811527274077</v>
+        <v>18204.00660752121</v>
       </c>
       <c r="D4" t="n">
         <v>1.75642e-07</v>
@@ -704,10 +698,7 @@
         <v>-42718.90590584213</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.036172081155364e-09</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>4652.823575540586</v>
+        <v>-13618.0366537451</v>
       </c>
       <c r="AA4" t="n">
         <v>1.00000000000816e-08</v>
@@ -724,7 +715,7 @@
         <v>3624.505</v>
       </c>
       <c r="C5" t="n">
-        <v>3885.530652444814</v>
+        <v>18280.51125372568</v>
       </c>
       <c r="D5" t="n">
         <v>1.78341e-07</v>
@@ -757,10 +748,7 @@
         <v>-38923.4625149877</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.463323541956249e-10</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>4555.875472880276</v>
+        <v>-13781.22321997678</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000084e-08</v>
@@ -777,7 +765,7 @@
         <v>3578.594</v>
       </c>
       <c r="C6" t="n">
-        <v>3818.798003748499</v>
+        <v>18872.41236415569</v>
       </c>
       <c r="D6" t="n">
         <v>1.81055e-07</v>
@@ -810,10 +798,7 @@
         <v>-44884.11049018749</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.96279307198882e-12</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4457.927960395239</v>
+        <v>-14469.43937253481</v>
       </c>
       <c r="AA6" t="n">
         <v>1e-08</v>
@@ -830,7 +815,7 @@
         <v>3467.432</v>
       </c>
       <c r="C7" t="n">
-        <v>3725.312640525315</v>
+        <v>18847.44784152995</v>
       </c>
       <c r="D7" t="n">
         <v>1.83885e-07</v>
@@ -863,10 +848,7 @@
         <v>-40093.91730232955</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.876750246228913e-09</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>4354.72800904437</v>
+        <v>-14534.64537070957</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000004574e-08</v>
@@ -883,7 +865,7 @@
         <v>3395.408</v>
       </c>
       <c r="C8" t="n">
-        <v>3650.031368392822</v>
+        <v>19179.79506452292</v>
       </c>
       <c r="D8" t="n">
         <v>1.86813e-07</v>
@@ -916,10 +898,7 @@
         <v>-40789.46133594657</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.302249062980872e-10</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>4259.853162524257</v>
+        <v>-14961.42013734135</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000216e-08</v>
@@ -936,7 +915,7 @@
         <v>3319.295</v>
       </c>
       <c r="C9" t="n">
-        <v>3573.094494966465</v>
+        <v>19502.90231836707</v>
       </c>
       <c r="D9" t="n">
         <v>1.89274e-07</v>
@@ -969,10 +948,7 @@
         <v>-40564.55818076397</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.111873164219927e-08</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4162.922824612825</v>
+        <v>-15370.03990342079</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000001537e-08</v>
@@ -989,7 +965,7 @@
         <v>3249.987</v>
       </c>
       <c r="C10" t="n">
-        <v>3502.594500245536</v>
+        <v>19532.11053671688</v>
       </c>
       <c r="D10" t="n">
         <v>1.91901e-07</v>
@@ -1022,10 +998,7 @@
         <v>-41298.62569820891</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.08708518102713e-08</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4073.216394573936</v>
+        <v>-15482.10525970526</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000018961e-08</v>
@@ -1042,7 +1015,7 @@
         <v>3159.553</v>
       </c>
       <c r="C11" t="n">
-        <v>3427.034621693911</v>
+        <v>20126.74074463428</v>
       </c>
       <c r="D11" t="n">
         <v>1.94336e-07</v>
@@ -1075,10 +1048,7 @@
         <v>-37209.95171431376</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.311748625133803e-09</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3987.893471212805</v>
+        <v>-16160.52151310872</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000003197e-08</v>
@@ -1241,7 +1211,7 @@
         <v>3678.332</v>
       </c>
       <c r="C2" t="n">
-        <v>3968.225752812883</v>
+        <v>17178.59172520608</v>
       </c>
       <c r="D2" t="n">
         <v>1.7639e-07</v>
@@ -1274,10 +1244,7 @@
         <v>-39534.14506715898</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.244253294594379e-09</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>4625.580325676739</v>
+        <v>-12590.83188893691</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000961e-08</v>
@@ -1294,7 +1261,7 @@
         <v>3506.666</v>
       </c>
       <c r="C3" t="n">
-        <v>3778.899565411683</v>
+        <v>17650.40421536832</v>
       </c>
       <c r="D3" t="n">
         <v>1.8282e-07</v>
@@ -1327,10 +1294,7 @@
         <v>-40617.94172694472</v>
       </c>
       <c r="Y3" t="n">
-        <v>7.377204449657842e-09</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>4433.80859511773</v>
+        <v>-13270.65176497906</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000001458e-08</v>
@@ -1347,7 +1311,7 @@
         <v>3437.748</v>
       </c>
       <c r="C4" t="n">
-        <v>3710.139676130584</v>
+        <v>18216.4440487463</v>
       </c>
       <c r="D4" t="n">
         <v>1.85578e-07</v>
@@ -1380,10 +1344,7 @@
         <v>-41596.08989601236</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.252944243450047e-10</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>4350.238132513493</v>
+        <v>-13930.11970787088</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000144e-08</v>
@@ -1400,7 +1361,7 @@
         <v>3359.498</v>
       </c>
       <c r="C5" t="n">
-        <v>3647.864927045868</v>
+        <v>18294.14132330861</v>
       </c>
       <c r="D5" t="n">
         <v>1.87738e-07</v>
@@ -1433,10 +1394,7 @@
         <v>-36761.96567934959</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.306075202763503e-10</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>4286.768509053111</v>
+        <v>-14070.50073823249</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000012766e-08</v>
@@ -1453,7 +1411,7 @@
         <v>3339.811</v>
       </c>
       <c r="C6" t="n">
-        <v>3615.461943016778</v>
+        <v>18382.91267497253</v>
       </c>
       <c r="D6" t="n">
         <v>1.89258e-07</v>
@@ -1486,10 +1444,7 @@
         <v>-41540.41709532502</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.584899300526974e-11</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4235.722519837079</v>
+        <v>-14207.9332976625</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000001277e-08</v>
@@ -1506,7 +1461,7 @@
         <v>3304.196</v>
       </c>
       <c r="C7" t="n">
-        <v>3575.814238413359</v>
+        <v>18616.13191270517</v>
       </c>
       <c r="D7" t="n">
         <v>1.90869e-07</v>
@@ -1539,10 +1494,7 @@
         <v>-41222.57852142974</v>
       </c>
       <c r="Y7" t="n">
-        <v>5.117943078847159e-10</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>4188.927113410116</v>
+        <v>-14490.42807419259</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000007216e-08</v>
@@ -1559,7 +1511,7 @@
         <v>3267.329</v>
       </c>
       <c r="C8" t="n">
-        <v>3541.794970276042</v>
+        <v>18767.35979133991</v>
       </c>
       <c r="D8" t="n">
         <v>1.92183e-07</v>
@@ -1592,10 +1544,7 @@
         <v>-40809.44726858166</v>
       </c>
       <c r="Y8" t="n">
-        <v>8.618493665111624e-10</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>4144.905958139941</v>
+        <v>-14683.85719704233</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000082e-08</v>
@@ -1612,7 +1561,7 @@
         <v>3212.279</v>
       </c>
       <c r="C9" t="n">
-        <v>3495.449698781198</v>
+        <v>19143.29880477925</v>
       </c>
       <c r="D9" t="n">
         <v>1.93504e-07</v>
@@ -1645,10 +1594,7 @@
         <v>-37476.77544811717</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.55756940921727e-09</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4099.248886566271</v>
+        <v>-15106.15503688249</v>
       </c>
       <c r="AA9" t="n">
         <v>1.00000000001205e-08</v>
@@ -1665,7 +1611,7 @@
         <v>3196.691</v>
       </c>
       <c r="C10" t="n">
-        <v>3469.273617555638</v>
+        <v>19219.35438277976</v>
       </c>
       <c r="D10" t="n">
         <v>1.94873e-07</v>
@@ -1698,10 +1644,7 @@
         <v>-41104.67547778001</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.916430614249844e-09</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4053.947623021833</v>
+        <v>-15224.30628468823</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000001917e-08</v>
@@ -1718,7 +1661,7 @@
         <v>3160.866</v>
       </c>
       <c r="C11" t="n">
-        <v>3434.022179130854</v>
+        <v>19433.1322818119</v>
       </c>
       <c r="D11" t="n">
         <v>1.96086e-07</v>
@@ -1751,10 +1694,7 @@
         <v>-41096.08193323449</v>
       </c>
       <c r="Y11" t="n">
-        <v>6.032241603430068e-10</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4008.970006005633</v>
+        <v>-15479.75380662041</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000006e-08</v>
@@ -1771,7 +1711,7 @@
         <v>3102.288</v>
       </c>
       <c r="C12" t="n">
-        <v>3389.443520859414</v>
+        <v>19598.56058759388</v>
       </c>
       <c r="D12" t="n">
         <v>1.97487e-07</v>
@@ -1804,10 +1744,7 @@
         <v>-36516.36614768529</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.039679267589776e-09</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3964.680842632226</v>
+        <v>-15688.92166808935</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000000819e-08</v>
@@ -1824,7 +1761,7 @@
         <v>3091.035</v>
       </c>
       <c r="C13" t="n">
-        <v>3365.79756946821</v>
+        <v>17592.97475242421</v>
       </c>
       <c r="D13" t="n">
         <v>1.98728e-07</v>
@@ -1857,10 +1794,7 @@
         <v>-39970.97906726342</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.247265051907677e-10</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3921.678424993902</v>
+        <v>-13686.58412680334</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000091e-08</v>
@@ -1877,7 +1811,7 @@
         <v>3061.303</v>
       </c>
       <c r="C14" t="n">
-        <v>3329.82043547082</v>
+        <v>17895.34271133819</v>
       </c>
       <c r="D14" t="n">
         <v>2.00064e-07</v>
@@ -1910,10 +1844,7 @@
         <v>-40569.3225769932</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.275191088860601e-14</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3877.756669921092</v>
+        <v>-14034.13506337038</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000015e-08</v>
@@ -1930,7 +1861,7 @@
         <v>3006.722</v>
       </c>
       <c r="C15" t="n">
-        <v>3288.308864460864</v>
+        <v>17819.47652689226</v>
       </c>
       <c r="D15" t="n">
         <v>2.01331e-07</v>
@@ -1963,10 +1894,7 @@
         <v>-35870.75606967674</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.899316326970643e-09</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3834.879772348723</v>
+        <v>-13994.58631086483</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000000042e-08</v>
@@ -1983,7 +1911,7 @@
         <v>2955.034</v>
       </c>
       <c r="C16" t="n">
-        <v>3245.350364981935</v>
+        <v>17951.17745254374</v>
       </c>
       <c r="D16" t="n">
         <v>2.02546e-07</v>
@@ -2016,10 +1944,7 @@
         <v>-32450.8659486324</v>
       </c>
       <c r="Y16" t="n">
-        <v>6.575769629793456e-10</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3793.124220174062</v>
+        <v>-14166.44589795853</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000565e-08</v>
@@ -2036,7 +1961,7 @@
         <v>2955.911</v>
       </c>
       <c r="C17" t="n">
-        <v>3228.147606304577</v>
+        <v>18213.50164667621</v>
       </c>
       <c r="D17" t="n">
         <v>2.03775e-07</v>
@@ -2069,10 +1994,7 @@
         <v>-38472.16568915868</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.19493814588955e-09</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3750.503077605235</v>
+        <v>-14470.43966408234</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000007e-08</v>
@@ -2089,7 +2011,7 @@
         <v>2905.613</v>
       </c>
       <c r="C18" t="n">
-        <v>3186.972887157414</v>
+        <v>18455.74877932922</v>
       </c>
       <c r="D18" t="n">
         <v>2.05031e-07</v>
@@ -2122,10 +2044,7 @@
         <v>-34815.30717000522</v>
       </c>
       <c r="Y18" t="n">
-        <v>3.582871598968226e-10</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3707.690031135591</v>
+        <v>-14755.01075259957</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000000023e-08</v>
@@ -2142,7 +2061,7 @@
         <v>2872.563</v>
       </c>
       <c r="C19" t="n">
-        <v>3154.171232638387</v>
+        <v>18175.57600144989</v>
       </c>
       <c r="D19" t="n">
         <v>2.06361e-07</v>
@@ -2175,10 +2094,7 @@
         <v>-33694.90035323985</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.408941785946461e-11</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3666.209999928599</v>
+        <v>-14507.9095387553</v>
       </c>
       <c r="AA19" t="n">
         <v>1.00000000000037e-08</v>
@@ -2195,7 +2111,7 @@
         <v>2839.418</v>
       </c>
       <c r="C20" t="n">
-        <v>3121.577599602536</v>
+        <v>18789.01668016996</v>
       </c>
       <c r="D20" t="n">
         <v>2.07254e-07</v>
@@ -2228,10 +2144,7 @@
         <v>-33980.12533270143</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.435818496161628e-10</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3626.471516064093</v>
+        <v>-15163.48891764489</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000036e-08</v>
@@ -2248,7 +2161,7 @@
         <v>2813.507</v>
       </c>
       <c r="C21" t="n">
-        <v>3089.628469015728</v>
+        <v>18779.42722414999</v>
       </c>
       <c r="D21" t="n">
         <v>2.08796e-07</v>
@@ -2281,10 +2194,7 @@
         <v>-32959.18410124019</v>
       </c>
       <c r="Y21" t="n">
-        <v>7.518278689948309e-10</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3584.932522063923</v>
+        <v>-15194.61862009939</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000001987e-08</v>
@@ -2301,7 +2211,7 @@
         <v>2779.263</v>
       </c>
       <c r="C22" t="n">
-        <v>3055.909604077406</v>
+        <v>18561.90354441896</v>
       </c>
       <c r="D22" t="n">
         <v>2.09799e-07</v>
@@ -2334,10 +2244,7 @@
         <v>-32345.46584861688</v>
       </c>
       <c r="Y22" t="n">
-        <v>5.277796362196904e-09</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3543.812075902712</v>
+        <v>-15007.04658922585</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000289e-08</v>
@@ -2500,7 +2407,7 @@
         <v>3744.922</v>
       </c>
       <c r="C2" t="n">
-        <v>4031.956155607799</v>
+        <v>17433.47616039691</v>
       </c>
       <c r="D2" t="n">
         <v>1.72399e-07</v>
@@ -2533,10 +2440,7 @@
         <v>-36235.15867410284</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.370441551673691e-10</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>4693.538148331047</v>
+        <v>-12746.05723045209</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000001e-08</v>
@@ -2553,7 +2457,7 @@
         <v>3569.268</v>
       </c>
       <c r="C3" t="n">
-        <v>3834.710110540431</v>
+        <v>18073.44203920749</v>
       </c>
       <c r="D3" t="n">
         <v>1.79549e-07</v>
@@ -2586,10 +2490,7 @@
         <v>-38815.23297486068</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.326280667072054e-09</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>4491.923364118757</v>
+        <v>-13616.19604194711</v>
       </c>
       <c r="AA3" t="n">
         <v>1.00000000000053e-08</v>
@@ -2606,7 +2507,7 @@
         <v>3493.123</v>
       </c>
       <c r="C4" t="n">
-        <v>3762.534428908826</v>
+        <v>18728.4986400753</v>
       </c>
       <c r="D4" t="n">
         <v>1.82536e-07</v>
@@ -2639,10 +2540,7 @@
         <v>-39633.70168602013</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.456479343354473e-08</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>4407.761219687009</v>
+        <v>-14370.77329925803</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000297e-08</v>
@@ -2659,7 +2557,7 @@
         <v>3445.376</v>
       </c>
       <c r="C5" t="n">
-        <v>3712.29802567827</v>
+        <v>19346.3526665433</v>
       </c>
       <c r="D5" t="n">
         <v>1.8412e-07</v>
@@ -2692,10 +2590,7 @@
         <v>-40164.32289764511</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.021853569404719e-08</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>4347.078069917857</v>
+        <v>-15052.21860497423</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000305e-08</v>
@@ -2712,7 +2607,7 @@
         <v>3406.698</v>
       </c>
       <c r="C6" t="n">
-        <v>3667.455721979444</v>
+        <v>18772.24860854682</v>
       </c>
       <c r="D6" t="n">
         <v>1.86066e-07</v>
@@ -2745,10 +2640,7 @@
         <v>-41086.84302222927</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.963394350270732e-09</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4292.763830766055</v>
+        <v>-14525.35842894117</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000182e-08</v>
@@ -2765,7 +2657,7 @@
         <v>3361.387</v>
       </c>
       <c r="C7" t="n">
-        <v>3624.293919853878</v>
+        <v>19270.93151961961</v>
       </c>
       <c r="D7" t="n">
         <v>1.87424e-07</v>
@@ -2798,10 +2690,7 @@
         <v>-40906.77792795659</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.086095934796582e-09</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>4241.652248228808</v>
+        <v>-15076.51678353808</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000184e-08</v>
@@ -2818,7 +2707,7 @@
         <v>3319.906</v>
       </c>
       <c r="C8" t="n">
-        <v>3585.360754930358</v>
+        <v>19741.86085404527</v>
       </c>
       <c r="D8" t="n">
         <v>1.88632e-07</v>
@@ -2851,10 +2740,7 @@
         <v>-41112.09358396035</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.001618958464682e-09</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>4192.374254727407</v>
+        <v>-15596.18728497487</v>
       </c>
       <c r="AA8" t="n">
         <v>1.00000000000034e-08</v>
@@ -2871,7 +2757,7 @@
         <v>3283.179</v>
       </c>
       <c r="C9" t="n">
-        <v>3547.257791552163</v>
+        <v>19541.94491706638</v>
       </c>
       <c r="D9" t="n">
         <v>1.90074e-07</v>
@@ -2904,10 +2790,7 @@
         <v>-40843.30632908228</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.828934291583226e-09</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4144.157110079499</v>
+        <v>-15436.40267627311</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000324e-08</v>
@@ -2924,7 +2807,7 @@
         <v>3245.033</v>
       </c>
       <c r="C10" t="n">
-        <v>3509.922541528195</v>
+        <v>20589.98202312</v>
       </c>
       <c r="D10" t="n">
         <v>1.91118e-07</v>
@@ -2957,10 +2840,7 @@
         <v>-41044.51981480025</v>
       </c>
       <c r="Y10" t="n">
-        <v>3.642114611136962e-09</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4096.364819230179</v>
+        <v>-16538.0318746667</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000343e-08</v>
@@ -2977,7 +2857,7 @@
         <v>3209.143</v>
       </c>
       <c r="C11" t="n">
-        <v>3473.684627330663</v>
+        <v>19648.86231223374</v>
       </c>
       <c r="D11" t="n">
         <v>1.92627e-07</v>
@@ -3010,10 +2890,7 @@
         <v>-41148.00692236799</v>
       </c>
       <c r="Y11" t="n">
-        <v>6.102817101340699e-10</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4050.705572598322</v>
+        <v>-15628.19115638496</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000003967e-08</v>
@@ -3030,7 +2907,7 @@
         <v>3150.149</v>
       </c>
       <c r="C12" t="n">
-        <v>3428.825235842202</v>
+        <v>20438.03588254349</v>
       </c>
       <c r="D12" t="n">
         <v>1.93583e-07</v>
@@ -3063,10 +2940,7 @@
         <v>-37217.95747578702</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.839090205752015e-08</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>4005.107665360809</v>
+        <v>-16465.3287539415</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000000054e-08</v>
@@ -3083,7 +2957,7 @@
         <v>3121.904</v>
       </c>
       <c r="C13" t="n">
-        <v>3392.197551793963</v>
+        <v>20304.00215661324</v>
       </c>
       <c r="D13" t="n">
         <v>1.94953e-07</v>
@@ -3116,10 +2990,7 @@
         <v>-37867.55414078048</v>
       </c>
       <c r="Y13" t="n">
-        <v>9.05080574630993e-09</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3959.623991028577</v>
+        <v>-16372.25975532306</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000142e-08</v>
@@ -3136,7 +3007,7 @@
         <v>3085.339</v>
       </c>
       <c r="C14" t="n">
-        <v>3358.183071526884</v>
+        <v>20517.98204926869</v>
       </c>
       <c r="D14" t="n">
         <v>1.96063e-07</v>
@@ -3169,10 +3040,7 @@
         <v>-37413.04763397378</v>
       </c>
       <c r="Y14" t="n">
-        <v>7.782032172183475e-10</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3915.607949259376</v>
+        <v>-16626.18229703102</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000020272e-08</v>
@@ -3189,7 +3057,7 @@
         <v>3056.301</v>
       </c>
       <c r="C15" t="n">
-        <v>3323.166320608543</v>
+        <v>20720.68181829381</v>
       </c>
       <c r="D15" t="n">
         <v>1.9725e-07</v>
@@ -3222,10 +3090,7 @@
         <v>-37504.01101230338</v>
       </c>
       <c r="Y15" t="n">
-        <v>8.556457137991386e-10</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3871.722882687917</v>
+        <v>-16870.41057303899</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000000318e-08</v>
@@ -3242,7 +3107,7 @@
         <v>3021.043</v>
       </c>
       <c r="C16" t="n">
-        <v>3288.763567519998</v>
+        <v>21142.56430733369</v>
       </c>
       <c r="D16" t="n">
         <v>1.9827e-07</v>
@@ -3275,10 +3140,7 @@
         <v>-37528.9224004475</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.323400534726482e-09</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3828.637181266008</v>
+        <v>-17332.60233035217</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000302e-08</v>
@@ -3295,7 +3157,7 @@
         <v>2988.04</v>
       </c>
       <c r="C17" t="n">
-        <v>3257.184915920018</v>
+        <v>21360.65069671385</v>
       </c>
       <c r="D17" t="n">
         <v>1.99642e-07</v>
@@ -3328,10 +3190,7 @@
         <v>-37242.38901594248</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.272349103142619e-08</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3786.329487144363</v>
+        <v>-17595.24215301298</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000006625e-08</v>
@@ -3348,7 +3207,7 @@
         <v>2955.594</v>
       </c>
       <c r="C18" t="n">
-        <v>3222.038790391883</v>
+        <v>21300.05081695053</v>
       </c>
       <c r="D18" t="n">
         <v>2.00614e-07</v>
@@ -3381,10 +3240,7 @@
         <v>-37505.71823373426</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.961663329049757e-10</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3746.125570984323</v>
+        <v>-17567.27402608954</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000000267e-08</v>
@@ -3401,7 +3257,7 @@
         <v>2923.937</v>
       </c>
       <c r="C19" t="n">
-        <v>3191.13708408033</v>
+        <v>21050.83630242472</v>
       </c>
       <c r="D19" t="n">
         <v>2.01951e-07</v>
@@ -3434,10 +3290,7 @@
         <v>-36863.70579542115</v>
       </c>
       <c r="Y19" t="n">
-        <v>7.567410631462515e-09</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3705.096468878992</v>
+        <v>-17353.84341616225</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000014656e-08</v>
@@ -3454,7 +3307,7 @@
         <v>2889.878</v>
       </c>
       <c r="C20" t="n">
-        <v>3159.62861734503</v>
+        <v>21407.84398187147</v>
       </c>
       <c r="D20" t="n">
         <v>2.02908e-07</v>
@@ -3487,10 +3340,7 @@
         <v>-36932.04206809559</v>
       </c>
       <c r="Y20" t="n">
-        <v>6.264038407816971e-09</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3665.14807273726</v>
+        <v>-17749.56745756546</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000332e-08</v>
@@ -3507,7 +3357,7 @@
         <v>2880.713</v>
       </c>
       <c r="C21" t="n">
-        <v>3136.180107570375</v>
+        <v>22114.39269725067</v>
       </c>
       <c r="D21" t="n">
         <v>2.03928e-07</v>
@@ -3540,10 +3390,7 @@
         <v>-41245.70124435767</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.276296621604266e-09</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3625.031257930533</v>
+        <v>-18501.30716549545</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000000082e-08</v>
@@ -3560,7 +3407,7 @@
         <v>2830.395</v>
       </c>
       <c r="C22" t="n">
-        <v>3096.932913626113</v>
+        <v>21493.94193832034</v>
       </c>
       <c r="D22" t="n">
         <v>2.0524e-07</v>
@@ -3593,10 +3440,7 @@
         <v>-36398.70661123101</v>
       </c>
       <c r="Y22" t="n">
-        <v>6.594935833323153e-10</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3584.938918758713</v>
+        <v>-17910.29195515395</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000062e-08</v>
@@ -3759,7 +3603,7 @@
         <v>4525.086</v>
       </c>
       <c r="C2" t="n">
-        <v>4827.586851421003</v>
+        <v>15656.61540444441</v>
       </c>
       <c r="D2" t="n">
         <v>1.48052e-07</v>
@@ -3792,10 +3636,7 @@
         <v>-38585.07460894478</v>
       </c>
       <c r="Y2" t="n">
-        <v>1073.340318774666</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2380.480950607625</v>
+        <v>-10116.61561482674</v>
       </c>
       <c r="AA2" t="n">
         <v>3.617301330012724e-07</v>
@@ -3812,7 +3653,7 @@
         <v>3853.317</v>
       </c>
       <c r="C3" t="n">
-        <v>4112.830579310931</v>
+        <v>17013.93435651969</v>
       </c>
       <c r="D3" t="n">
         <v>1.72127e-07</v>
@@ -3845,10 +3686,7 @@
         <v>-41718.39668810336</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.050785003349686e-09</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>4805.057663809637</v>
+        <v>-12277.74202515786</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000005e-08</v>
@@ -3865,7 +3703,7 @@
         <v>3670.807</v>
       </c>
       <c r="C4" t="n">
-        <v>3941.586149426752</v>
+        <v>16992.14147825495</v>
       </c>
       <c r="D4" t="n">
         <v>1.78213e-07</v>
@@ -3898,10 +3736,7 @@
         <v>-38984.17810447094</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.613962061907532e-10</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>4633.811805503475</v>
+        <v>-12435.22822470342</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000004e-08</v>
@@ -3918,7 +3753,7 @@
         <v>3602.979</v>
       </c>
       <c r="C5" t="n">
-        <v>3869.246958823255</v>
+        <v>17052.21320944822</v>
       </c>
       <c r="D5" t="n">
         <v>1.81295e-07</v>
@@ -3951,10 +3786,7 @@
         <v>-40188.99471371515</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.080062898592666e-10</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>4548.456229770773</v>
+        <v>-12583.79577560307</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000052e-08</v>
@@ -3971,7 +3803,7 @@
         <v>3549.37</v>
       </c>
       <c r="C6" t="n">
-        <v>3815.475477528914</v>
+        <v>17993.6752386236</v>
       </c>
       <c r="D6" t="n">
         <v>1.83132e-07</v>
@@ -4004,10 +3836,7 @@
         <v>-41046.50829060654</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.060273260654305e-08</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4481.83669330781</v>
+        <v>-13601.3198452614</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000009808e-08</v>
@@ -4024,7 +3853,7 @@
         <v>3496.687</v>
       </c>
       <c r="C7" t="n">
-        <v>3766.797233325573</v>
+        <v>17889.75652666233</v>
       </c>
       <c r="D7" t="n">
         <v>1.8503e-07</v>
@@ -4057,10 +3886,7 @@
         <v>-41075.08273355191</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.994339978598567e-09</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>4420.373114729879</v>
+        <v>-13552.22255904215</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000015099e-08</v>
@@ -4077,7 +3903,7 @@
         <v>3449.656</v>
       </c>
       <c r="C8" t="n">
-        <v>3716.17981696578</v>
+        <v>18326.71556386225</v>
       </c>
       <c r="D8" t="n">
         <v>1.86653e-07</v>
@@ -4110,10 +3936,7 @@
         <v>-41552.92251922782</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.917301806367308e-08</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>4359.515578070504</v>
+        <v>-14049.58425781038</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000368e-08</v>
@@ -4130,7 +3953,7 @@
         <v>3403.369</v>
       </c>
       <c r="C9" t="n">
-        <v>3671.56065674134</v>
+        <v>18581.16983778165</v>
       </c>
       <c r="D9" t="n">
         <v>1.88258e-07</v>
@@ -4163,10 +3986,7 @@
         <v>-41807.91473405976</v>
       </c>
       <c r="Y9" t="n">
-        <v>7.272425296825485e-09</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4302.387579045705</v>
+        <v>-14357.93347438549</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000001809e-08</v>
@@ -4183,7 +4003,7 @@
         <v>3357.19</v>
       </c>
       <c r="C10" t="n">
-        <v>3629.511760553408</v>
+        <v>18404.1287312228</v>
       </c>
       <c r="D10" t="n">
         <v>1.899e-07</v>
@@ -4216,10 +4036,7 @@
         <v>-41365.48015405237</v>
       </c>
       <c r="Y10" t="n">
-        <v>3.786705163748536e-09</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4248.92922349523</v>
+        <v>-14227.47608340165</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000004836e-08</v>
@@ -4236,7 +4053,7 @@
         <v>3322.173</v>
       </c>
       <c r="C11" t="n">
-        <v>3589.094282790891</v>
+        <v>18490.72986319557</v>
       </c>
       <c r="D11" t="n">
         <v>1.91233e-07</v>
@@ -4269,10 +4086,7 @@
         <v>-42023.61822488459</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.501267779284147e-08</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4198.953644447599</v>
+        <v>-14358.6087282308</v>
       </c>
       <c r="AA11" t="n">
         <v>1.00000000000075e-08</v>
@@ -4435,7 +4249,7 @@
         <v>3708.864</v>
       </c>
       <c r="C2" t="n">
-        <v>4005.195168909228</v>
+        <v>16859.17418661887</v>
       </c>
       <c r="D2" t="n">
         <v>1.7404e-07</v>
@@ -4468,10 +4282,7 @@
         <v>-35423.97564794312</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.521657633262843e-08</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>4653.890839873927</v>
+        <v>-12201.00024669468</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000054e-08</v>
@@ -4488,7 +4299,7 @@
         <v>3504.058</v>
       </c>
       <c r="C3" t="n">
-        <v>3780.175898758577</v>
+        <v>17931.98671312774</v>
       </c>
       <c r="D3" t="n">
         <v>1.82955e-07</v>
@@ -4521,10 +4332,7 @@
         <v>-39193.99875693533</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.910658385666193e-09</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>4428.909836046425</v>
+        <v>-13553.26387638284</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000407e-08</v>
@@ -4541,7 +4349,7 @@
         <v>3442.693</v>
       </c>
       <c r="C4" t="n">
-        <v>3710.396782634206</v>
+        <v>18363.02620476793</v>
       </c>
       <c r="D4" t="n">
         <v>1.85643e-07</v>
@@ -4574,10 +4382,7 @@
         <v>-40420.98541322634</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.229554545332458e-10</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>4352.02768845258</v>
+        <v>-14071.88135985862</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000844e-08</v>
@@ -4594,7 +4399,7 @@
         <v>3394.1</v>
       </c>
       <c r="C5" t="n">
-        <v>3667.656994896587</v>
+        <v>18444.33769605657</v>
       </c>
       <c r="D5" t="n">
         <v>1.8734e-07</v>
@@ -4627,10 +4432,7 @@
         <v>-40590.77826771026</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.760496163544514e-09</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>4296.716262856918</v>
+        <v>-14206.96074599679</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000816e-08</v>
@@ -4647,7 +4449,7 @@
         <v>3351.124</v>
       </c>
       <c r="C6" t="n">
-        <v>3623.717381881532</v>
+        <v>18610.56612825512</v>
       </c>
       <c r="D6" t="n">
         <v>1.88693e-07</v>
@@ -4680,10 +4482,7 @@
         <v>-40766.21594067842</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.185417571141088e-10</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4244.709705821757</v>
+        <v>-14421.22575205034</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000715e-08</v>
@@ -4700,7 +4499,7 @@
         <v>3312.95</v>
       </c>
       <c r="C7" t="n">
-        <v>3583.707515925887</v>
+        <v>19247.28952973059</v>
       </c>
       <c r="D7" t="n">
         <v>1.90111e-07</v>
@@ -4733,10 +4532,7 @@
         <v>-41526.57298806445</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.617339558873035e-08</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>4192.791121687596</v>
+        <v>-15113.24827717772</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000001757e-08</v>
@@ -4753,7 +4549,7 @@
         <v>3273.829</v>
       </c>
       <c r="C8" t="n">
-        <v>3542.414630927135</v>
+        <v>19518.26055464274</v>
       </c>
       <c r="D8" t="n">
         <v>1.91563e-07</v>
@@ -4786,10 +4582,7 @@
         <v>-41860.97354407657</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.847126196992954e-10</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>4142.230575826401</v>
+        <v>-15433.52414942042</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000057e-08</v>
@@ -4806,7 +4599,7 @@
         <v>3232.236</v>
       </c>
       <c r="C9" t="n">
-        <v>3503.524845667792</v>
+        <v>19547.32487573399</v>
       </c>
       <c r="D9" t="n">
         <v>1.92749e-07</v>
@@ -4839,10 +4632,7 @@
         <v>-41250.46562680621</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.991278277557005e-08</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4093.828928492236</v>
+        <v>-15503.25495221962</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000001947e-08</v>
@@ -4859,7 +4649,7 @@
         <v>3195.427</v>
       </c>
       <c r="C10" t="n">
-        <v>3467.076636717556</v>
+        <v>18940.01614588763</v>
       </c>
       <c r="D10" t="n">
         <v>1.94136e-07</v>
@@ -4892,10 +4682,7 @@
         <v>-41277.83624842841</v>
       </c>
       <c r="Y10" t="n">
-        <v>7.891125767703922e-09</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4047.154068088556</v>
+        <v>-14928.6917169584</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000006667e-08</v>
@@ -4912,7 +4699,7 @@
         <v>3138.272</v>
       </c>
       <c r="C11" t="n">
-        <v>3421.93313710722</v>
+        <v>19940.82187245779</v>
       </c>
       <c r="D11" t="n">
         <v>1.95373e-07</v>
@@ -4945,10 +4732,7 @@
         <v>-36879.85482537232</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.299733213975684e-09</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4001.816873409182</v>
+        <v>-15984.51285098034</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000005228e-08</v>
@@ -4965,7 +4749,7 @@
         <v>3100.293</v>
       </c>
       <c r="C12" t="n">
-        <v>3388.43038022568</v>
+        <v>19776.95599775253</v>
       </c>
       <c r="D12" t="n">
         <v>1.96646e-07</v>
@@ -4998,10 +4782,7 @@
         <v>-37032.87724548585</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.265069957050443e-11</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3958.889677470831</v>
+        <v>-15857.74848808257</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000000027e-08</v>
@@ -5018,7 +4799,7 @@
         <v>3092.473</v>
       </c>
       <c r="C13" t="n">
-        <v>3362.475211830905</v>
+        <v>20153.78919155247</v>
       </c>
       <c r="D13" t="n">
         <v>1.97745e-07</v>
@@ -5051,10 +4832,7 @@
         <v>-41640.33620342238</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.168556271462451e-08</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3917.910732737846</v>
+        <v>-16276.19466051754</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000023e-08</v>
@@ -5071,7 +4849,7 @@
         <v>3039.591</v>
       </c>
       <c r="C14" t="n">
-        <v>3322.892736555752</v>
+        <v>20507.93243878609</v>
       </c>
       <c r="D14" t="n">
         <v>1.98762e-07</v>
@@ -5104,10 +4882,7 @@
         <v>-37119.70767182198</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.648870650044301e-10</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3877.639945750469</v>
+        <v>-16669.90270508538</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000000102e-08</v>
@@ -5124,7 +4899,7 @@
         <v>3006.895</v>
       </c>
       <c r="C15" t="n">
-        <v>3291.023842846892</v>
+        <v>20806.71854590625</v>
       </c>
       <c r="D15" t="n">
         <v>1.99886e-07</v>
@@ -5157,10 +4932,7 @@
         <v>-36871.4112509617</v>
       </c>
       <c r="Y15" t="n">
-        <v>3.043708393811753e-10</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3837.930304753713</v>
+        <v>-17007.59803920083</v>
       </c>
       <c r="AA15" t="n">
         <v>1.00000000000016e-08</v>
@@ -5177,7 +4949,7 @@
         <v>2998.568</v>
       </c>
       <c r="C16" t="n">
-        <v>3268.187340512005</v>
+        <v>20224.56537628107</v>
       </c>
       <c r="D16" t="n">
         <v>2.01107e-07</v>
@@ -5210,10 +4982,7 @@
         <v>-41045.80255470653</v>
       </c>
       <c r="Y16" t="n">
-        <v>3.395595330295504e-11</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3799.431494836769</v>
+        <v>-16453.24230507854</v>
       </c>
       <c r="AA16" t="n">
         <v>1e-08</v>
@@ -5230,7 +4999,7 @@
         <v>2947.304</v>
       </c>
       <c r="C17" t="n">
-        <v>3230.737486353717</v>
+        <v>21023.38696193562</v>
       </c>
       <c r="D17" t="n">
         <v>2.02057e-07</v>
@@ -5263,10 +5032,7 @@
         <v>-37345.71976115601</v>
       </c>
       <c r="Y17" t="n">
-        <v>8.747000056007439e-11</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3761.326044031936</v>
+        <v>-17295.96478129525</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000002902e-08</v>
@@ -5283,7 +5049,7 @@
         <v>2916.959</v>
       </c>
       <c r="C18" t="n">
-        <v>3199.131451394526</v>
+        <v>21478.76999734617</v>
       </c>
       <c r="D18" t="n">
         <v>2.02991e-07</v>
@@ -5316,10 +5082,7 @@
         <v>-36912.85957093524</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.857883550239786e-10</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3723.576550417546</v>
+        <v>-17788.5787030679</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000001416e-08</v>
@@ -5336,7 +5099,7 @@
         <v>2888.634</v>
       </c>
       <c r="C19" t="n">
-        <v>3169.876054712648</v>
+        <v>21463.82119076572</v>
       </c>
       <c r="D19" t="n">
         <v>2.04096e-07</v>
@@ -5369,10 +5132,7 @@
         <v>-36789.86004587459</v>
       </c>
       <c r="Y19" t="n">
-        <v>5.615926122380126e-09</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3685.61143786212</v>
+        <v>-17808.25129084387</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000000003e-08</v>
@@ -5389,7 +5149,7 @@
         <v>2860.76</v>
       </c>
       <c r="C20" t="n">
-        <v>3139.84584264815</v>
+        <v>19118.81012097231</v>
       </c>
       <c r="D20" t="n">
         <v>2.05255e-07</v>
@@ -5422,10 +5182,7 @@
         <v>-36383.08632855428</v>
       </c>
       <c r="Y20" t="n">
-        <v>7.181368074988119e-09</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3648.260515367372</v>
+        <v>-15463.92325350446</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000405e-08</v>
@@ -5442,7 +5199,7 @@
         <v>2833.797</v>
       </c>
       <c r="C21" t="n">
-        <v>3110.206739254788</v>
+        <v>19645.19405258245</v>
       </c>
       <c r="D21" t="n">
         <v>2.06397e-07</v>
@@ -5475,10 +5232,7 @@
         <v>-36425.82521801424</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.532190754060749e-09</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3610.871663855977</v>
+        <v>-16033.34867810195</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000001747e-08</v>
@@ -5495,7 +5249,7 @@
         <v>2807.645</v>
       </c>
       <c r="C22" t="n">
-        <v>3081.131173649205</v>
+        <v>19459.77808548769</v>
       </c>
       <c r="D22" t="n">
         <v>2.075e-07</v>
@@ -5528,10 +5282,7 @@
         <v>-35833.96723458635</v>
       </c>
       <c r="Y22" t="n">
-        <v>3.959365931943967e-10</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3574.213531026992</v>
+        <v>-15877.98862677041</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000061e-08</v>
@@ -5694,7 +5445,7 @@
         <v>4459.268</v>
       </c>
       <c r="C2" t="n">
-        <v>4787.322021152971</v>
+        <v>15692.81648798441</v>
       </c>
       <c r="D2" t="n">
         <v>1.48884e-07</v>
@@ -5727,10 +5478,7 @@
         <v>-34424.68344287606</v>
       </c>
       <c r="Y2" t="n">
-        <v>1055.080731106669</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2293.908302385268</v>
+        <v>-10185.315465711</v>
       </c>
       <c r="AA2" t="n">
         <v>2.835846168589033e-07</v>
@@ -5747,7 +5495,7 @@
         <v>3814.951</v>
       </c>
       <c r="C3" t="n">
-        <v>4072.98696945737</v>
+        <v>17007.22586714866</v>
       </c>
       <c r="D3" t="n">
         <v>1.73239e-07</v>
@@ -5780,10 +5528,7 @@
         <v>-40963.23885384059</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.623045504896294e-09</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>4753.384423106874</v>
+        <v>-12308.02571700081</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000001e-08</v>
@@ -5800,7 +5545,7 @@
         <v>3645.149</v>
       </c>
       <c r="C4" t="n">
-        <v>3909.829096771019</v>
+        <v>17280.71595039013</v>
       </c>
       <c r="D4" t="n">
         <v>1.79275e-07</v>
@@ -5833,10 +5578,7 @@
         <v>-38971.58159006686</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.249716657774193e-13</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>4590.643252646193</v>
+        <v>-12763.24756608484</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000002e-08</v>
@@ -5853,7 +5595,7 @@
         <v>3577.913</v>
       </c>
       <c r="C5" t="n">
-        <v>3840.261940153929</v>
+        <v>17236.94752537961</v>
       </c>
       <c r="D5" t="n">
         <v>1.81596e-07</v>
@@ -5886,10 +5628,7 @@
         <v>-39914.77040381361</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.602638798140937e-09</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>4510.666258300266</v>
+        <v>-12792.49244931558</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000017e-08</v>
@@ -5906,7 +5645,7 @@
         <v>3525.562</v>
       </c>
       <c r="C6" t="n">
-        <v>3787.226066572004</v>
+        <v>17171.92589339534</v>
       </c>
       <c r="D6" t="n">
         <v>1.84015e-07</v>
@@ -5939,10 +5678,7 @@
         <v>-40424.1852491955</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.169127569493476e-10</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4443.624127221153</v>
+        <v>-12794.59320636131</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000002368e-08</v>
@@ -5959,7 +5695,7 @@
         <v>3478.255</v>
       </c>
       <c r="C7" t="n">
-        <v>3739.391339974596</v>
+        <v>18062.69662475288</v>
       </c>
       <c r="D7" t="n">
         <v>1.85589e-07</v>
@@ -5992,10 +5728,7 @@
         <v>-40989.63622504757</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.488492394900494e-10</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>4381.919398490669</v>
+        <v>-13753.33204981305</v>
       </c>
       <c r="AA7" t="n">
         <v>1.00000000000195e-08</v>
@@ -6012,7 +5745,7 @@
         <v>3422.936</v>
       </c>
       <c r="C8" t="n">
-        <v>3687.342400478719</v>
+        <v>18671.76250836431</v>
       </c>
       <c r="D8" t="n">
         <v>1.87196e-07</v>
@@ -6045,10 +5778,7 @@
         <v>-41023.95344322815</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.089663676532676e-09</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>4320.782336644716</v>
+        <v>-14425.47367825146</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000002041e-08</v>
@@ -6065,7 +5795,7 @@
         <v>3377.946</v>
       </c>
       <c r="C9" t="n">
-        <v>3640.413680241331</v>
+        <v>18328.26898184936</v>
       </c>
       <c r="D9" t="n">
         <v>1.88975e-07</v>
@@ -6098,10 +5828,7 @@
         <v>-41162.87044068253</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.34267778668352e-10</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4261.567840336447</v>
+        <v>-14129.87801093012</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000184e-08</v>
@@ -6118,7 +5845,7 @@
         <v>3332.78</v>
       </c>
       <c r="C10" t="n">
-        <v>3593.983159880353</v>
+        <v>18761.01527901002</v>
       </c>
       <c r="D10" t="n">
         <v>1.90513e-07</v>
@@ -6151,10 +5878,7 @@
         <v>-41216.36672372974</v>
       </c>
       <c r="Y10" t="n">
-        <v>3.533449238697481e-10</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4205.152332984519</v>
+        <v>-14618.83002678724</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000001e-08</v>
@@ -6171,7 +5895,7 @@
         <v>3269.662</v>
       </c>
       <c r="C11" t="n">
-        <v>3544.910277757086</v>
+        <v>18771.10842741022</v>
       </c>
       <c r="D11" t="n">
         <v>1.92177e-07</v>
@@ -6204,10 +5928,7 @@
         <v>-36846.71880798282</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.123019456708511e-09</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4152.477972393427</v>
+        <v>-14678.11596855144</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000001e-08</v>
@@ -6370,7 +6091,7 @@
         <v>3717.902</v>
       </c>
       <c r="C2" t="n">
-        <v>3994.537081286064</v>
+        <v>17298.76981510926</v>
       </c>
       <c r="D2" t="n">
         <v>1.75491e-07</v>
@@ -6403,10 +6124,7 @@
         <v>-40301.79480221806</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.235926572917609e-10</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>4630.804069233268</v>
+        <v>-12684.69703535846</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000034e-08</v>
@@ -6423,7 +6141,7 @@
         <v>3496.819</v>
       </c>
       <c r="C3" t="n">
-        <v>3769.83121323671</v>
+        <v>17870.26606802267</v>
       </c>
       <c r="D3" t="n">
         <v>1.83769e-07</v>
@@ -6456,10 +6174,7 @@
         <v>-39451.08615926488</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.108028271526496e-09</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>4417.453442020096</v>
+        <v>-13510.22476825578</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000004962e-08</v>
@@ -6476,7 +6191,7 @@
         <v>3434.181</v>
       </c>
       <c r="C4" t="n">
-        <v>3702.996520353501</v>
+        <v>17993.3832421794</v>
       </c>
       <c r="D4" t="n">
         <v>1.86394e-07</v>
@@ -6509,10 +6224,7 @@
         <v>-40680.18506933431</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.29061613257218e-09</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>4341.507534985692</v>
+        <v>-13714.54493157621</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000843e-08</v>
@@ -6529,7 +6241,7 @@
         <v>3365.52</v>
       </c>
       <c r="C5" t="n">
-        <v>3648.025919270994</v>
+        <v>18547.6147647679</v>
       </c>
       <c r="D5" t="n">
         <v>1.88149e-07</v>
@@ -6562,10 +6274,7 @@
         <v>-37035.44504081913</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.156242664486849e-10</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>4287.261472372335</v>
+        <v>-14330.30254698398</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000538e-08</v>
@@ -6582,7 +6291,7 @@
         <v>3347.718</v>
       </c>
       <c r="C6" t="n">
-        <v>3616.800099194834</v>
+        <v>18583.74293860061</v>
       </c>
       <c r="D6" t="n">
         <v>1.89596e-07</v>
@@ -6615,10 +6324,7 @@
         <v>-41565.98529472275</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.702110812891749e-09</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4236.770548968717</v>
+        <v>-14412.57920340374</v>
       </c>
       <c r="AA6" t="n">
         <v>1.00000000000441e-08</v>
@@ -6635,7 +6341,7 @@
         <v>3310.858</v>
       </c>
       <c r="C7" t="n">
-        <v>3580.043011777872</v>
+        <v>18222.50224547637</v>
       </c>
       <c r="D7" t="n">
         <v>1.91017e-07</v>
@@ -6668,10 +6374,7 @@
         <v>-41291.75285344612</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.017413315847881e-08</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>4191.244207467593</v>
+        <v>-14087.74217340988</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000018746e-08</v>
@@ -6688,7 +6391,7 @@
         <v>3277.431</v>
       </c>
       <c r="C8" t="n">
-        <v>3547.87553039352</v>
+        <v>19085.34526741799</v>
       </c>
       <c r="D8" t="n">
         <v>1.92212e-07</v>
@@ -6721,10 +6424,7 @@
         <v>-41786.27346587367</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.135560371762622e-08</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>4150.409573333377</v>
+        <v>-15001.62286046612</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000000954e-08</v>
@@ -6741,7 +6441,7 @@
         <v>3221.451</v>
       </c>
       <c r="C9" t="n">
-        <v>3507.538417061768</v>
+        <v>19082.67065279108</v>
       </c>
       <c r="D9" t="n">
         <v>1.93405e-07</v>
@@ -6774,10 +6474,7 @@
         <v>-37016.40395681278</v>
       </c>
       <c r="Y9" t="n">
-        <v>9.005111509448654e-09</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4109.546372580284</v>
+        <v>-15035.14954452399</v>
       </c>
       <c r="AA9" t="n">
         <v>1.00000000000022e-08</v>
@@ -6794,7 +6491,7 @@
         <v>3212.682</v>
       </c>
       <c r="C10" t="n">
-        <v>3481.526624760476</v>
+        <v>19408.63254573068</v>
       </c>
       <c r="D10" t="n">
         <v>1.94314e-07</v>
@@ -6827,10 +6524,7 @@
         <v>-41782.15808609482</v>
       </c>
       <c r="Y10" t="n">
-        <v>8.968435402752091e-09</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>4069.647770720112</v>
+        <v>-15398.11274403772</v>
       </c>
       <c r="AA10" t="n">
         <v>1.00000000000632e-08</v>
@@ -6847,7 +6541,7 @@
         <v>3181.648</v>
       </c>
       <c r="C11" t="n">
-        <v>3452.967335716866</v>
+        <v>19368.36377713305</v>
       </c>
       <c r="D11" t="n">
         <v>1.95722e-07</v>
@@ -6880,10 +6574,7 @@
         <v>-41345.47078662629</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.649035460946066e-08</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4030.907290418277</v>
+        <v>-15396.04870574269</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000046e-08</v>
@@ -6900,7 +6591,7 @@
         <v>3134.152</v>
       </c>
       <c r="C12" t="n">
-        <v>3414.154312366292</v>
+        <v>19708.17469266281</v>
       </c>
       <c r="D12" t="n">
         <v>1.96823e-07</v>
@@ -6933,10 +6624,7 @@
         <v>-37364.12935134943</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.284098864596018e-08</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3993.970859178094</v>
+        <v>-15774.40024706769</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000001263e-08</v>
@@ -6953,7 +6641,7 @@
         <v>3108.108</v>
       </c>
       <c r="C13" t="n">
-        <v>3385.991367666909</v>
+        <v>19483.30249361706</v>
       </c>
       <c r="D13" t="n">
         <v>1.97715e-07</v>
@@ -6986,10 +6674,7 @@
         <v>-37195.10094076003</v>
       </c>
       <c r="Y13" t="n">
-        <v>8.622869047033051e-09</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3957.811488573836</v>
+        <v>-15576.10487997691</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000000254e-08</v>
@@ -7006,7 +6691,7 @@
         <v>3097.531</v>
       </c>
       <c r="C14" t="n">
-        <v>3365.020591424226</v>
+        <v>20319.68607151042</v>
       </c>
       <c r="D14" t="n">
         <v>1.98851e-07</v>
@@ -7039,10 +6724,7 @@
         <v>-41572.93156759319</v>
       </c>
       <c r="Y14" t="n">
-        <v>5.380529307457898e-09</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3921.772438603268</v>
+        <v>-16458.53333404898</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000001409e-08</v>
@@ -7059,7 +6741,7 @@
         <v>3052.9</v>
       </c>
       <c r="C15" t="n">
-        <v>3329.249471502608</v>
+        <v>18046.73568728316</v>
       </c>
       <c r="D15" t="n">
         <v>1.99831e-07</v>
@@ -7092,10 +6774,7 @@
         <v>-36859.36792161804</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.31898092160703e-08</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3886.490196109462</v>
+        <v>-14180.19321575473</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000000254e-08</v>
@@ -7112,7 +6791,7 @@
         <v>3041.708</v>
       </c>
       <c r="C16" t="n">
-        <v>3307.048580793825</v>
+        <v>18182.96444994674</v>
       </c>
       <c r="D16" t="n">
         <v>2.00891e-07</v>
@@ -7145,10 +6824,7 @@
         <v>-40623.66442183763</v>
       </c>
       <c r="Y16" t="n">
-        <v>3.887219174510559e-10</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3850.310176161137</v>
+        <v>-14351.21722856801</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000003e-08</v>
@@ -7165,7 +6841,7 @@
         <v>3013.689</v>
       </c>
       <c r="C17" t="n">
-        <v>3279.162396452301</v>
+        <v>18251.19810446264</v>
       </c>
       <c r="D17" t="n">
         <v>2.01834e-07</v>
@@ -7198,10 +6874,7 @@
         <v>-40396.95267118809</v>
       </c>
       <c r="Y17" t="n">
-        <v>3.847306411100364e-13</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3813.412746061818</v>
+        <v>-14451.35626594341</v>
       </c>
       <c r="AA17" t="n">
         <v>1.000000000000934e-08</v>
@@ -7218,7 +6891,7 @@
         <v>2964.158</v>
       </c>
       <c r="C18" t="n">
-        <v>3241.435371289489</v>
+        <v>18457.25516669433</v>
       </c>
       <c r="D18" t="n">
         <v>2.02906e-07</v>
@@ -7251,10 +6924,7 @@
         <v>-36189.51110608188</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.319893135992098e-10</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3775.852345068222</v>
+        <v>-14694.71305320193</v>
       </c>
       <c r="AA18" t="n">
         <v>1.000000000002044e-08</v>
@@ -7271,7 +6941,7 @@
         <v>2935.224</v>
       </c>
       <c r="C19" t="n">
-        <v>3210.164291599909</v>
+        <v>18525.203415754</v>
       </c>
       <c r="D19" t="n">
         <v>2.04115e-07</v>
@@ -7304,10 +6974,7 @@
         <v>-35593.80162284902</v>
       </c>
       <c r="Y19" t="n">
-        <v>6.150625741378004e-10</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3736.967588206503</v>
+        <v>-14798.66810652058</v>
       </c>
       <c r="AA19" t="n">
         <v>1.000000000000714e-08</v>
@@ -7324,7 +6991,7 @@
         <v>2902.99</v>
       </c>
       <c r="C20" t="n">
-        <v>3179.83259499805</v>
+        <v>18678.66792182613</v>
       </c>
       <c r="D20" t="n">
         <v>2.05174e-07</v>
@@ -7357,10 +7024,7 @@
         <v>-35380.25998478269</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.772094132424919e-11</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3699.112071811785</v>
+        <v>-14987.63810782906</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000000024e-08</v>
@@ -7377,7 +7041,7 @@
         <v>2874.349</v>
       </c>
       <c r="C21" t="n">
-        <v>3150.740097322521</v>
+        <v>18994.86696333056</v>
       </c>
       <c r="D21" t="n">
         <v>2.06385e-07</v>
@@ -7410,10 +7074,7 @@
         <v>-34508.16578125785</v>
       </c>
       <c r="Y21" t="n">
-        <v>3.085022071799043e-10</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3661.643515416152</v>
+        <v>-15343.83427948432</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000001086e-08</v>
@@ -7430,7 +7091,7 @@
         <v>2833.017</v>
       </c>
       <c r="C22" t="n">
-        <v>3113.800367969926</v>
+        <v>19054.56926690727</v>
       </c>
       <c r="D22" t="n">
         <v>2.07473e-07</v>
@@ -7463,10 +7124,7 @@
         <v>-31263.07622818363</v>
       </c>
       <c r="Y22" t="n">
-        <v>5.122970399824468e-10</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3624.657915364857</v>
+        <v>-15437.90380218466</v>
       </c>
       <c r="AA22" t="n">
         <v>1.00000000000025e-08</v>
@@ -7629,7 +7287,7 @@
         <v>4270.356</v>
       </c>
       <c r="C2" t="n">
-        <v>4604.996165947747</v>
+        <v>16750.17507069128</v>
       </c>
       <c r="D2" t="n">
         <v>1.52123e-07</v>
@@ -7662,10 +7320,7 @@
         <v>-31236.51774651871</v>
       </c>
       <c r="Y2" t="n">
-        <v>934.1838519358612</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2385.730023543495</v>
+        <v>-11402.10451384991</v>
       </c>
       <c r="AA2" t="n">
         <v>5.80745350768789e-08</v>
@@ -7682,7 +7337,7 @@
         <v>3598.002</v>
       </c>
       <c r="C3" t="n">
-        <v>3878.345331930941</v>
+        <v>18561.71144696731</v>
       </c>
       <c r="D3" t="n">
         <v>1.76576e-07</v>
@@ -7715,10 +7370,7 @@
         <v>-36215.34938611357</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.272320891073169e-09</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>4524.855126340347</v>
+        <v>-14038.52602173104</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000235e-08</v>
@@ -7735,7 +7387,7 @@
         <v>3454.311</v>
       </c>
       <c r="C4" t="n">
-        <v>3722.250347380781</v>
+        <v>20094.49746315726</v>
       </c>
       <c r="D4" t="n">
         <v>1.8188e-07</v>
@@ -7768,10 +7420,7 @@
         <v>-39782.66938161801</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.204547895892845e-10</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>4358.934873678555</v>
+        <v>-15774.07221267237</v>
       </c>
       <c r="AA4" t="n">
         <v>1.00000000000358e-08</v>
@@ -7788,7 +7437,7 @@
         <v>3362.022</v>
       </c>
       <c r="C5" t="n">
-        <v>3645.300004754277</v>
+        <v>20178.09800120163</v>
       </c>
       <c r="D5" t="n">
         <v>1.83869e-07</v>
@@ -7821,10 +7470,7 @@
         <v>-37610.76231594136</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.426656367275097e-10</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>4276.393863301896</v>
+        <v>-15938.57131706065</v>
       </c>
       <c r="AA5" t="n">
         <v>1.00000000000093e-08</v>
@@ -7841,7 +7487,7 @@
         <v>3325.986</v>
       </c>
       <c r="C6" t="n">
-        <v>3596.581181760527</v>
+        <v>20731.91781475172</v>
       </c>
       <c r="D6" t="n">
         <v>1.8523e-07</v>
@@ -7874,10 +7520,7 @@
         <v>-42398.09056029002</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.687449380712621e-09</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4207.704869634666</v>
+        <v>-16559.59798860348</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000369e-08</v>
@@ -7894,7 +7537,7 @@
         <v>3252.983</v>
       </c>
       <c r="C7" t="n">
-        <v>3537.972486813213</v>
+        <v>21191.38851388785</v>
       </c>
       <c r="D7" t="n">
         <v>1.86485e-07</v>
@@ -7927,10 +7570,7 @@
         <v>-38723.29491528345</v>
       </c>
       <c r="Y7" t="n">
-        <v>9.464932124904462e-10</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>4143.848226298488</v>
+        <v>-17080.84319227009</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000707e-08</v>
@@ -7947,7 +7587,7 @@
         <v>3226.471</v>
       </c>
       <c r="C8" t="n">
-        <v>3495.389718263189</v>
+        <v>21894.61538694935</v>
       </c>
       <c r="D8" t="n">
         <v>1.87917e-07</v>
@@ -7980,10 +7620,7 @@
         <v>-44019.34813406553</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.854478355294012e-10</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>4080.674369677742</v>
+        <v>-17850.64156213618</v>
       </c>
       <c r="AA8" t="n">
         <v>1.000000000004136e-08</v>
@@ -8000,7 +7637,7 @@
         <v>3154.382</v>
       </c>
       <c r="C9" t="n">
-        <v>3436.751539878295</v>
+        <v>22319.85268892796</v>
       </c>
       <c r="D9" t="n">
         <v>1.89215e-07</v>
@@ -8033,10 +7670,7 @@
         <v>-39527.86271113251</v>
       </c>
       <c r="Y9" t="n">
-        <v>8.888881286838853e-11</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4019.159256258269</v>
+        <v>-18335.3259137202</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000784e-08</v>
@@ -8053,7 +7687,7 @@
         <v>3105.243</v>
       </c>
       <c r="C10" t="n">
-        <v>3389.206789242181</v>
+        <v>22781.66628949427</v>
       </c>
       <c r="D10" t="n">
         <v>1.9051e-07</v>
@@ -8086,10 +7720,7 @@
         <v>-39530.00364594071</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.195807746173208e-09</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3958.81546257119</v>
+        <v>-18855.9122834962</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000004721e-08</v>
@@ -8106,7 +7737,7 @@
         <v>3061.703</v>
       </c>
       <c r="C11" t="n">
-        <v>3343.116295925606</v>
+        <v>23276.31082580312</v>
       </c>
       <c r="D11" t="n">
         <v>1.91838e-07</v>
@@ -8139,10 +7770,7 @@
         <v>-40091.09987426962</v>
       </c>
       <c r="Y11" t="n">
-        <v>8.500939757938179e-13</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3902.332604730684</v>
+        <v>-19408.36242138267</v>
       </c>
       <c r="AA11" t="n">
         <v>1e-08</v>
@@ -8305,7 +7933,7 @@
         <v>3618.313</v>
       </c>
       <c r="C2" t="n">
-        <v>3914.797408024064</v>
+        <v>19209.85167560868</v>
       </c>
       <c r="D2" t="n">
         <v>1.73994e-07</v>
@@ -8338,10 +7966,7 @@
         <v>-37438.65193121058</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.02175536139579e-10</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>4546.412649936276</v>
+        <v>-14646.86878329669</v>
       </c>
       <c r="AA2" t="n">
         <v>1.000000000000494e-08</v>
@@ -8358,7 +7983,7 @@
         <v>3421.174</v>
       </c>
       <c r="C3" t="n">
-        <v>3698.038324900365</v>
+        <v>20259.45118502019</v>
       </c>
       <c r="D3" t="n">
         <v>1.82652e-07</v>
@@ -8391,10 +8016,7 @@
         <v>-41405.88197391653</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.434593854780971e-09</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>4329.940258969168</v>
+        <v>-15975.03385689815</v>
       </c>
       <c r="AA3" t="n">
         <v>1.00000000000021e-08</v>
@@ -8411,7 +8033,7 @@
         <v>3329.567</v>
       </c>
       <c r="C4" t="n">
-        <v>3617.201951012219</v>
+        <v>20133.70979325523</v>
       </c>
       <c r="D4" t="n">
         <v>1.85529e-07</v>
@@ -8444,10 +8066,7 @@
         <v>-38183.28783422406</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.14876472356141e-10</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>4249.136279704687</v>
+        <v>-15932.43508801284</v>
       </c>
       <c r="AA4" t="n">
         <v>1e-08</v>
@@ -8464,7 +8083,7 @@
         <v>3307.411</v>
       </c>
       <c r="C5" t="n">
-        <v>3580.416011061983</v>
+        <v>20540.09188743956</v>
       </c>
       <c r="D5" t="n">
         <v>1.87585e-07</v>
@@ -8497,10 +8116,7 @@
         <v>-42711.43636522233</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.024843145068984e-09</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>4193.692545303805</v>
+        <v>-16403.09533500718</v>
       </c>
       <c r="AA5" t="n">
         <v>1.00000000000157e-08</v>
@@ -8517,7 +8133,7 @@
         <v>3244.448</v>
       </c>
       <c r="C6" t="n">
-        <v>3533.533665963866</v>
+        <v>20813.90868022711</v>
       </c>
       <c r="D6" t="n">
         <v>1.88969e-07</v>
@@ -8550,10 +8166,7 @@
         <v>-38282.81836715888</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.880066108315514e-09</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4145.208135336991</v>
+        <v>-16722.77970885898</v>
       </c>
       <c r="AA6" t="n">
         <v>1.000000000000003e-08</v>
@@ -8570,7 +8183,7 @@
         <v>3211.31</v>
       </c>
       <c r="C7" t="n">
-        <v>3497.84036361608</v>
+        <v>19929.48018978333</v>
       </c>
       <c r="D7" t="n">
         <v>1.90505e-07</v>
@@ -8603,10 +8216,7 @@
         <v>-38231.144362366</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.145084303727157e-09</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>4100.652651665622</v>
+        <v>-15868.84222760694</v>
       </c>
       <c r="AA7" t="n">
         <v>1.000000000000176e-08</v>
@@ -8623,7 +8233,7 @@
         <v>3177.596</v>
       </c>
       <c r="C8" t="n">
-        <v>3464.72602844258</v>
+        <v>20755.46936229208</v>
       </c>
       <c r="D8" t="n">
         <v>1.91511e-07</v>
@@ -8656,10 +8266,7 @@
         <v>-38216.49275971144</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.515083079458712e-10</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>4058.707393125731</v>
+        <v>-16740.02652939804</v>
       </c>
       <c r="AA8" t="n">
         <v>1.00000000000002e-08</v>
@@ -8676,7 +8283,7 @@
         <v>3144.322</v>
       </c>
       <c r="C9" t="n">
-        <v>3431.27137733926</v>
+        <v>20754.60013540714</v>
       </c>
       <c r="D9" t="n">
         <v>1.9295e-07</v>
@@ -8709,10 +8316,7 @@
         <v>-38188.37004848402</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.833478426214852e-10</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>4018.348495702831</v>
+        <v>-16780.18396126778</v>
       </c>
       <c r="AA9" t="n">
         <v>1.000000000000001e-08</v>
@@ -8729,7 +8333,7 @@
         <v>3119.191</v>
       </c>
       <c r="C10" t="n">
-        <v>3399.982667066321</v>
+        <v>21145.3996593113</v>
       </c>
       <c r="D10" t="n">
         <v>1.94419e-07</v>
@@ -8762,10 +8366,7 @@
         <v>-38699.49919989831</v>
       </c>
       <c r="Y10" t="n">
-        <v>9.68213434659183e-10</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3979.448659800326</v>
+        <v>-17216.87958884501</v>
       </c>
       <c r="AA10" t="n">
         <v>1.000000000000085e-08</v>
@@ -8782,7 +8383,7 @@
         <v>3105.89</v>
       </c>
       <c r="C11" t="n">
-        <v>3378.503647629097</v>
+        <v>21351.70272623582</v>
       </c>
       <c r="D11" t="n">
         <v>1.95185e-07</v>
@@ -8815,10 +8416,7 @@
         <v>-42607.68993200607</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.606741513217921e-09</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3942.416923180658</v>
+        <v>-17453.37936643058</v>
       </c>
       <c r="AA11" t="n">
         <v>1.000000000000684e-08</v>
@@ -8835,7 +8433,7 @@
         <v>3058.819</v>
       </c>
       <c r="C12" t="n">
-        <v>3341.018566321077</v>
+        <v>21048.66834257342</v>
       </c>
       <c r="D12" t="n">
         <v>1.96328e-07</v>
@@ -8868,10 +8466,7 @@
         <v>-38767.25062149622</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.178383808251198e-09</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3906.229744126156</v>
+        <v>-17180.60844609416</v>
       </c>
       <c r="AA12" t="n">
         <v>1.000000000000049e-08</v>
@@ -8888,7 +8483,7 @@
         <v>3030.286</v>
       </c>
       <c r="C13" t="n">
-        <v>3314.135570047208</v>
+        <v>20868.7981602454</v>
       </c>
       <c r="D13" t="n">
         <v>1.97459e-07</v>
@@ -8921,10 +8516,7 @@
         <v>-38598.69676550315</v>
       </c>
       <c r="Y13" t="n">
-        <v>5.377195440529159e-10</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3871.158020146187</v>
+        <v>-17031.09940888571</v>
       </c>
       <c r="AA13" t="n">
         <v>1.000000000001256e-08</v>
@@ -8941,7 +8533,7 @@
         <v>3001.642</v>
       </c>
       <c r="C14" t="n">
-        <v>3286.498425912858</v>
+        <v>21386.87962211859</v>
       </c>
       <c r="D14" t="n">
         <v>1.98418e-07</v>
@@ -8974,10 +8566,7 @@
         <v>-38582.03856828791</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.169718704593535e-10</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3835.989998949466</v>
+        <v>-17585.65474642561</v>
       </c>
       <c r="AA14" t="n">
         <v>1.000000000017186e-08</v>
@@ -8994,7 +8583,7 @@
         <v>2975.386</v>
       </c>
       <c r="C15" t="n">
-        <v>3258.085548034843</v>
+        <v>21356.68746250319</v>
       </c>
       <c r="D15" t="n">
         <v>1.99657e-07</v>
@@ -9027,10 +8616,7 @@
         <v>-38317.35342556189</v>
       </c>
       <c r="Y15" t="n">
-        <v>5.163221658958326e-11</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3801.152867077442</v>
+        <v>-17590.28505348837</v>
       </c>
       <c r="AA15" t="n">
         <v>1.000000000000045e-08</v>
@@ -9047,7 +8633,7 @@
         <v>2951.439</v>
       </c>
       <c r="C16" t="n">
-        <v>3230.786273220484</v>
+        <v>21837.03996518297</v>
       </c>
       <c r="D16" t="n">
         <v>2.00639e-07</v>
@@ -9080,10 +8666,7 @@
         <v>-38702.06183167682</v>
       </c>
       <c r="Y16" t="n">
-        <v>4.324637531563735e-12</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3765.866408940889</v>
+        <v>-18108.71966291594</v>
       </c>
       <c r="AA16" t="n">
         <v>1.000000000000082e-08</v>
@@ -9100,7 +8683,7 @@
         <v>2923.074</v>
       </c>
       <c r="C17" t="n">
-        <v>3202.990776849141</v>
+        <v>21725.66786250145</v>
       </c>
       <c r="D17" t="n">
         <v>2.01543e-07</v>
@@ -9133,10 +8716,7 @@
         <v>-38150.21430726999</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.985192077426656e-08</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3730.377770053432</v>
+        <v>-18024.55451420399</v>
       </c>
       <c r="AA17" t="n">
         <v>1.00000000000952e-08</v>
@@ -9153,7 +8733,7 @@
         <v>2896.068</v>
       </c>
       <c r="C18" t="n">
-        <v>3175.963552941086</v>
+        <v>22331.77074832673</v>
       </c>
       <c r="D18" t="n">
         <v>2.02526e-07</v>
@@ -9186,10 +8766,7 @@
         <v>-38798.01367035966</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.0944098674368e-14</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3696.0770156904</v>
+        <v>-18668.87010106155</v>
       </c>
       <c r="AA18" t="n">
         <v>1e-08</v>
@@ -9206,7 +8783,7 @@
         <v>2866.254</v>
       </c>
       <c r="C19" t="n">
-        <v>3146.316880704469</v>
+        <v>21965.74750353389</v>
       </c>
       <c r="D19" t="n">
         <v>2.03566e-07</v>
@@ -9239,10 +8816,7 @@
         <v>-38375.93558057064</v>
       </c>
       <c r="Y19" t="n">
-        <v>4.382033804628565e-11</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3659.739763347086</v>
+        <v>-18331.95665977916</v>
       </c>
       <c r="AA19" t="n">
         <v>1.00000000000003e-08</v>
@@ -9259,7 +8833,7 @@
         <v>2841.265</v>
       </c>
       <c r="C20" t="n">
-        <v>3116.618457848635</v>
+        <v>22117.27410749023</v>
       </c>
       <c r="D20" t="n">
         <v>2.04622e-07</v>
@@ -9292,10 +8866,7 @@
         <v>-38286.0299618542</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.270549332805959e-09</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3623.718649918355</v>
+        <v>-18516.77711270294</v>
       </c>
       <c r="AA20" t="n">
         <v>1.000000000001719e-08</v>
@@ -9312,7 +8883,7 @@
         <v>2818.828</v>
       </c>
       <c r="C21" t="n">
-        <v>3090.392124261674</v>
+        <v>22381.1541903402</v>
       </c>
       <c r="D21" t="n">
         <v>2.05677e-07</v>
@@ -9345,10 +8916,7 @@
         <v>-37899.95117546595</v>
       </c>
       <c r="Y21" t="n">
-        <v>9.953075358001483e-09</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3589.402565469917</v>
+        <v>-18815.37372289217</v>
       </c>
       <c r="AA21" t="n">
         <v>1.000000000000005e-08</v>
@@ -9365,7 +8933,7 @@
         <v>2771.698</v>
       </c>
       <c r="C22" t="n">
-        <v>3055.610772737397</v>
+        <v>20499.85573350843</v>
       </c>
       <c r="D22" t="n">
         <v>2.06834e-07</v>
@@ -9398,10 +8966,7 @@
         <v>-34370.34040002357</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.31220898286965e-10</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3554.157447565878</v>
+        <v>-16944.1642197531</v>
       </c>
       <c r="AA22" t="n">
         <v>1.000000000000035e-08</v>
@@ -9564,7 +9129,7 @@
         <v>3199.223</v>
       </c>
       <c r="C2" t="n">
-        <v>3616.655412082657</v>
+        <v>19341.77124546102</v>
       </c>
       <c r="D2" t="n">
         <v>1.8699e-07</v>
@@ -9597,10 +9162,7 @@
         <v>-30076.12992159559</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.548767816972464e-08</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>3931.3295098559</v>
+        <v>-15165.32132155623</v>
       </c>
       <c r="AA2" t="n">
         <v>1.00000000000951e-08</v>
@@ -9617,7 +9179,7 @@
         <v>2576.254</v>
       </c>
       <c r="C3" t="n">
-        <v>2910.286943771685</v>
+        <v>21484.28728165369</v>
       </c>
       <c r="D3" t="n">
         <v>2.14406e-07</v>
@@ -9650,10 +9212,7 @@
         <v>-30940.69225926958</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.064013584503895e-11</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3330.341443771282</v>
+        <v>-18078.00370750142</v>
       </c>
       <c r="AA3" t="n">
         <v>1.000000000000087e-08</v>
@@ -9670,7 +9229,7 @@
         <v>2468.15</v>
       </c>
       <c r="C4" t="n">
-        <v>2784.805354161376</v>
+        <v>22272.22868536629</v>
       </c>
       <c r="D4" t="n">
         <v>2.19537e-07</v>
@@ -9703,10 +9262,7 @@
         <v>-35044.1838767528</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.600304056244478e-11</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3198.773498650586</v>
+        <v>-19025.84812916466</v>
       </c>
       <c r="AA4" t="n">
         <v>1.000000000000259e-08</v>
@@ -9723,7 +9279,7 @@
         <v>2401.425</v>
       </c>
       <c r="C5" t="n">
-        <v>2722.49049542128</v>
+        <v>22811.32050137167</v>
       </c>
       <c r="D5" t="n">
         <v>2.21631e-07</v>
@@ -9756,10 +9312,7 @@
         <v>-32359.74514723961</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.624150959028984e-12</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3137.91765451105</v>
+        <v>-19637.47354422342</v>
       </c>
       <c r="AA5" t="n">
         <v>1.000000000000114e-08</v>
@@ -9776,7 +9329,7 @@
         <v>2364.229</v>
       </c>
       <c r="C6" t="n">
-        <v>2685.15272299248</v>
+        <v>1407.035256746369</v>
       </c>
       <c r="D6" t="n">
         <v>2.22776e-07</v>
@@ -9809,16 +9362,13 @@
         <v>-32436.80238746237</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.237155215073255e-14</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3090.404222545536</v>
+        <v>18.71204569916711</v>
       </c>
       <c r="AA6" t="n">
-        <v>1e-08</v>
+        <v>2.064860631009888e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8261010053753834</v>
+        <v>0.8983691703940806</v>
       </c>
     </row>
     <row r="7">
@@ -9829,7 +9379,7 @@
         <v>2314.593</v>
       </c>
       <c r="C7" t="n">
-        <v>2643.443739867774</v>
+        <v>1392.100183179602</v>
       </c>
       <c r="D7" t="n">
         <v>2.23876e-07</v>
@@ -9862,16 +9412,13 @@
         <v>-29990.2279741978</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.873052751754583e-08</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3045.549785816086</v>
+        <v>2.76600503601751</v>
       </c>
       <c r="AA7" t="n">
-        <v>1e-08</v>
+        <v>1.903001563399983e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.8263297711641212</v>
+        <v>0.9006146102061595</v>
       </c>
     </row>
     <row r="8">
@@ -9882,7 +9429,7 @@
         <v>2289.719</v>
       </c>
       <c r="C8" t="n">
-        <v>2612.543339712507</v>
+        <v>1094.45589240911</v>
       </c>
       <c r="D8" t="n">
         <v>2.25157e-07</v>
@@ -9915,16 +9462,13 @@
         <v>-32245.91517107652</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.072263196839266e-11</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3000.177687131686</v>
+        <v>235.3242257176125</v>
       </c>
       <c r="AA8" t="n">
-        <v>1e-08</v>
+        <v>1.17221511210875e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.82661497162223</v>
+        <v>0.9574110077926478</v>
       </c>
     </row>
     <row r="9">
@@ -9935,7 +9479,7 @@
         <v>2260.332</v>
       </c>
       <c r="C9" t="n">
-        <v>2578.227742134532</v>
+        <v>1367.427855629953</v>
       </c>
       <c r="D9" t="n">
         <v>2.26419e-07</v>
@@ -9968,16 +9512,13 @@
         <v>-32172.30905325947</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.575618300636622e-12</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2955.778520537724</v>
+        <v>23.96543605451302</v>
       </c>
       <c r="AA9" t="n">
-        <v>1e-08</v>
+        <v>2.051323473979569e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8269476360445552</v>
+        <v>0.8955796997812072</v>
       </c>
     </row>
     <row r="10">
@@ -9988,7 +9529,7 @@
         <v>2218.395</v>
       </c>
       <c r="C10" t="n">
-        <v>2542.928529547422</v>
+        <v>1066.500150010346</v>
       </c>
       <c r="D10" t="n">
         <v>2.27576e-07</v>
@@ -10021,16 +9562,13 @@
         <v>-31717.81379658414</v>
       </c>
       <c r="Y10" t="n">
-        <v>4.067180711400814e-10</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2913.40211426387</v>
+        <v>221.8679590132398</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.000000000000055e-08</v>
+        <v>6.485697992095258e-10</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.8272829612088458</v>
+        <v>0.9967120936795565</v>
       </c>
     </row>
     <row r="11">
@@ -10041,7 +9579,7 @@
         <v>2177.275</v>
       </c>
       <c r="C11" t="n">
-        <v>2505.212470414701</v>
+        <v>982.0595483972554</v>
       </c>
       <c r="D11" t="n">
         <v>2.28915e-07</v>
@@ -10074,16 +9612,13 @@
         <v>-29321.32910393714</v>
       </c>
       <c r="Y11" t="n">
-        <v>9.396591062440979e-10</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2873.572204780687</v>
+        <v>437.9666243479142</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.000000000000047e-08</v>
+        <v>4.870980732479922e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.8276196827158498</v>
+        <v>0.885548744375428</v>
       </c>
     </row>
   </sheetData>
